--- a/Plannings 2026 S14.xlsx
+++ b/Plannings 2026 S14.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{150E33BF-47F0-4B68-8AA0-FBA696D166AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{150E33BF-47F0-4B68-8AA0-FBA696D166AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05A385D4-9949-4BBB-BE7E-6087CBA21D57}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,377 +17,452 @@
     <sheet name="Résultats par salarié" sheetId="2" r:id="rId2"/>
     <sheet name="Informations" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="149">
+  <si>
+    <t>Mars-2026</t>
+  </si>
+  <si>
+    <t>Avril-2026</t>
+  </si>
+  <si>
+    <t>Sem 14</t>
+  </si>
+  <si>
+    <t>P25 // EDF // LEAGUES</t>
+  </si>
+  <si>
+    <t>EDF // LEAGUES</t>
+  </si>
+  <si>
+    <t>C. PADEL // EVENT EQUANS // LEAGUES</t>
+  </si>
+  <si>
+    <t>EDF</t>
+  </si>
+  <si>
+    <t>P250 // EDF // ANNIV</t>
+  </si>
+  <si>
+    <t>ANNIV</t>
+  </si>
+  <si>
+    <t>Nom / Prénom</t>
+  </si>
+  <si>
+    <t>30 Lu</t>
+  </si>
+  <si>
+    <t>31 Ma</t>
+  </si>
+  <si>
+    <t>1 Me</t>
+  </si>
+  <si>
+    <t>2 Je</t>
+  </si>
+  <si>
+    <t>3 Ve</t>
+  </si>
+  <si>
+    <t>4 Sa</t>
+  </si>
+  <si>
+    <t>5 Di</t>
+  </si>
+  <si>
+    <t>BONILLO Matthieu</t>
+  </si>
+  <si>
+    <t>EDF-C</t>
+  </si>
+  <si>
+    <t>09:00/13:00</t>
+  </si>
+  <si>
+    <t>BOULARDET Lucas</t>
+  </si>
+  <si>
+    <t>VDC</t>
+  </si>
+  <si>
+    <t>18:00/22:00</t>
+  </si>
+  <si>
+    <t>CARRERE Peïo</t>
+  </si>
+  <si>
+    <t>ENT-M</t>
+  </si>
+  <si>
+    <t>17:30/20:15</t>
+  </si>
+  <si>
+    <t>09:45/16:00</t>
+  </si>
+  <si>
+    <t>09:45/15:30</t>
+  </si>
+  <si>
+    <t>09:45/11:45</t>
+  </si>
+  <si>
+    <t>08:45/17:30</t>
+  </si>
+  <si>
+    <t>L-REG</t>
+  </si>
+  <si>
+    <t>20:15/21:30</t>
+  </si>
+  <si>
+    <t>16:30/18:15</t>
+  </si>
+  <si>
+    <t>11:45/19:00</t>
+  </si>
+  <si>
+    <t>L-ARB</t>
+  </si>
+  <si>
+    <t>21:30/22:30</t>
+  </si>
+  <si>
+    <t>18:15/20:45</t>
+  </si>
+  <si>
+    <t>CASTELLON Pascaline</t>
+  </si>
+  <si>
+    <t>20:00/24:00</t>
+  </si>
+  <si>
+    <t>COHAT Linda</t>
+  </si>
+  <si>
+    <t>CONRAD David</t>
+  </si>
+  <si>
+    <t>11:00/18:15</t>
+  </si>
+  <si>
+    <t>11:30/14:30</t>
+  </si>
+  <si>
+    <t>16:00/22:00</t>
+  </si>
+  <si>
+    <t>11:00/17:30</t>
+  </si>
+  <si>
+    <t>CRUZEL Quentin</t>
+  </si>
+  <si>
+    <t>17:30/22:30</t>
+  </si>
+  <si>
+    <t>18:15/24:00</t>
+  </si>
+  <si>
+    <t>13:45/15:45</t>
+  </si>
+  <si>
+    <t>13:30/17:30</t>
+  </si>
+  <si>
+    <t>15:45/22:45</t>
+  </si>
+  <si>
+    <t>17:30/23:40</t>
+  </si>
+  <si>
+    <t>DE NOUEL Maxime</t>
+  </si>
+  <si>
+    <t>C-PAD</t>
+  </si>
+  <si>
+    <t>PAD-A</t>
+  </si>
+  <si>
+    <t>CUP-R</t>
+  </si>
+  <si>
+    <t>08:45/12:15</t>
+  </si>
+  <si>
+    <t>13:00/15:00</t>
+  </si>
+  <si>
+    <t>07:30/14:00</t>
+  </si>
+  <si>
+    <t>CUP-L</t>
+  </si>
+  <si>
+    <t>12:15/13:00</t>
+  </si>
+  <si>
+    <t>13:00/14:15</t>
+  </si>
+  <si>
+    <t>15:00/17:00</t>
+  </si>
+  <si>
+    <t>13:00/18:30</t>
+  </si>
+  <si>
+    <t>14:15/17:15</t>
+  </si>
+  <si>
+    <t>17:00/20:30</t>
+  </si>
+  <si>
+    <t>14:15/16:45</t>
+  </si>
+  <si>
+    <t>16:45/18:30</t>
+  </si>
+  <si>
+    <t>DIVIEN Yohan</t>
+  </si>
+  <si>
+    <t>DONAER Nicolas</t>
+  </si>
+  <si>
+    <t>COMMD</t>
+  </si>
+  <si>
+    <t>EDF-B</t>
+  </si>
+  <si>
+    <t>EV-LO</t>
+  </si>
+  <si>
+    <t>16:15/17:15</t>
+  </si>
+  <si>
+    <t>14:15/15:45</t>
+  </si>
+  <si>
+    <t>18:30/23:30</t>
+  </si>
+  <si>
+    <t>17:15/19:15</t>
+  </si>
+  <si>
+    <t>15:45/17:15</t>
+  </si>
+  <si>
+    <t>19:15/00:30+</t>
+  </si>
+  <si>
+    <t>19:15/24:00</t>
+  </si>
+  <si>
+    <t>17:15/18:45</t>
+  </si>
+  <si>
+    <t>19:30/21:30</t>
+  </si>
+  <si>
+    <t>DOVINA Théo</t>
+  </si>
+  <si>
+    <t>HEBERT Jean Baptiste</t>
+  </si>
+  <si>
+    <t>JARGUEL Thomas</t>
+  </si>
+  <si>
+    <t>KABUNDA NDEKE Marvyn</t>
+  </si>
+  <si>
+    <t>LABEFODE Thomas</t>
+  </si>
+  <si>
+    <t>MOSTEFA Yanis</t>
+  </si>
+  <si>
+    <t>09:30/10:15</t>
+  </si>
+  <si>
+    <t>10:15/12:15</t>
+  </si>
+  <si>
+    <t>12:15/12:45</t>
+  </si>
+  <si>
+    <t>ORDONEZ GOMEZ Oceane</t>
+  </si>
+  <si>
+    <t>19:30/22:30</t>
+  </si>
+  <si>
+    <t>18:30/20:30</t>
+  </si>
+  <si>
+    <t>PEREZ Loic</t>
+  </si>
+  <si>
+    <t>VIS-M</t>
+  </si>
+  <si>
+    <t>18:00/24:00</t>
+  </si>
+  <si>
+    <t>14:00/16:00</t>
+  </si>
+  <si>
+    <t>13:45/17:45</t>
+  </si>
+  <si>
+    <t>14:30/15:30</t>
+  </si>
+  <si>
+    <t>09:00/09:30</t>
+  </si>
+  <si>
+    <t> </t>
+  </si>
+  <si>
+    <t>16:00/17:15</t>
+  </si>
+  <si>
+    <t>17:45/20:15</t>
+  </si>
+  <si>
+    <t>15:30/16:30</t>
+  </si>
+  <si>
+    <t>09:30/12:30</t>
+  </si>
+  <si>
+    <t>EV-RE</t>
+  </si>
+  <si>
+    <t>20:15/21:45</t>
+  </si>
+  <si>
+    <t>16:30/21:00</t>
+  </si>
+  <si>
+    <t>21:00/24:00</t>
+  </si>
+  <si>
+    <t>15:45/17:45</t>
+  </si>
+  <si>
+    <t>22:30/24:00</t>
+  </si>
+  <si>
+    <t>PISTORE Remi</t>
+  </si>
+  <si>
+    <t>PUJOL Mathieu</t>
+  </si>
+  <si>
+    <t>09:45/18:00</t>
+  </si>
+  <si>
+    <t>17:30/18:45</t>
+  </si>
+  <si>
+    <t>09:45/14:00</t>
+  </si>
+  <si>
+    <t>07:30/08:45</t>
+  </si>
+  <si>
+    <t>EDF-A</t>
+  </si>
+  <si>
+    <t>18:45/22:45</t>
+  </si>
+  <si>
+    <t>08:45/09:45</t>
+  </si>
+  <si>
+    <t>09:45/17:30</t>
+  </si>
+  <si>
+    <t>RABII Mehdi</t>
+  </si>
+  <si>
+    <t>17:45/21:45</t>
+  </si>
+  <si>
+    <t>SANGARNE Enzo</t>
+  </si>
+  <si>
+    <t>13:45/17:30</t>
+  </si>
+  <si>
+    <t>SEIGNE Kevin</t>
+  </si>
+  <si>
+    <t>TINGUY Florian</t>
+  </si>
+  <si>
+    <t>TOPPAN Mattis</t>
+  </si>
+  <si>
+    <t>17:30/00:30+</t>
+  </si>
+  <si>
+    <t>15:00/22:20</t>
+  </si>
+  <si>
+    <t>VASSANT Tiffany</t>
+  </si>
   <si>
     <t>Planning des salariés du 30/03/2026 au 05/04/2026</t>
   </si>
   <si>
-    <t>Mars-2026</t>
-  </si>
-  <si>
-    <t>Avril-2026</t>
-  </si>
-  <si>
-    <t>Sem 14</t>
-  </si>
-  <si>
-    <t>Nom / Prénom</t>
-  </si>
-  <si>
-    <t>30 Lu</t>
-  </si>
-  <si>
-    <t>31 Ma</t>
-  </si>
-  <si>
-    <t>1 Me</t>
-  </si>
-  <si>
-    <t>2 Je</t>
-  </si>
-  <si>
-    <t>3 Ve</t>
-  </si>
-  <si>
-    <t>4 Sa</t>
-  </si>
-  <si>
-    <t>5 Di</t>
-  </si>
-  <si>
-    <t>BONILLO Matthieu</t>
-  </si>
-  <si>
-    <t>EDF-C</t>
-  </si>
-  <si>
-    <t>09:00/13:00</t>
-  </si>
-  <si>
-    <t>BOULARDET Lucas</t>
-  </si>
-  <si>
-    <t>VDC</t>
-  </si>
-  <si>
-    <t>18:00/22:00</t>
-  </si>
-  <si>
-    <t>CARRERE Peïo</t>
-  </si>
-  <si>
-    <t>L-REG</t>
-  </si>
-  <si>
-    <t>17:30/20:15</t>
-  </si>
-  <si>
-    <t>09:45/16:00</t>
-  </si>
-  <si>
-    <t>09:45/15:30</t>
-  </si>
-  <si>
-    <t>11:45/19:00</t>
-  </si>
-  <si>
-    <t>08:45/17:30</t>
-  </si>
-  <si>
-    <t>20:15/21:30</t>
-  </si>
-  <si>
-    <t>16:30/18:15</t>
-  </si>
-  <si>
-    <t>L-ARB</t>
-  </si>
-  <si>
-    <t>21:30/22:30</t>
-  </si>
-  <si>
-    <t>18:15/20:45</t>
-  </si>
-  <si>
-    <t>CASTELLON Pascaline</t>
-  </si>
-  <si>
-    <t>20:00/24:00</t>
-  </si>
-  <si>
-    <t>COHAT Linda</t>
-  </si>
-  <si>
-    <t>CONRAD David</t>
-  </si>
-  <si>
-    <t>16:00/22:00</t>
-  </si>
-  <si>
-    <t>CRUZEL Quentin</t>
-  </si>
-  <si>
-    <t>ANNIV</t>
-  </si>
-  <si>
-    <t>17:30/22:30</t>
-  </si>
-  <si>
-    <t>18:15/24:00</t>
-  </si>
-  <si>
-    <t>13:45/15:45</t>
-  </si>
-  <si>
-    <t>13:30/17:30</t>
-  </si>
-  <si>
-    <t>15:45/22:45</t>
-  </si>
-  <si>
-    <t>17:30/23:40</t>
-  </si>
-  <si>
-    <t>DE NOUEL Maxime</t>
-  </si>
-  <si>
-    <t>CUP-L</t>
-  </si>
-  <si>
-    <t>C-PAD</t>
-  </si>
-  <si>
-    <t>CUP-R</t>
-  </si>
-  <si>
-    <t>08:45/12:15</t>
-  </si>
-  <si>
-    <t>07:30/14:00</t>
-  </si>
-  <si>
-    <t>PAD-A</t>
-  </si>
-  <si>
-    <t>13:00/14:15</t>
-  </si>
-  <si>
-    <t>14:15/15:45</t>
-  </si>
-  <si>
-    <t>14:15/16:45</t>
-  </si>
-  <si>
-    <t>17:00/20:30</t>
-  </si>
-  <si>
-    <t>DIVIEN Yohan</t>
-  </si>
-  <si>
-    <t>DONAER Nicolas</t>
-  </si>
-  <si>
-    <t>COMMD</t>
-  </si>
-  <si>
-    <t>EDF-B</t>
-  </si>
-  <si>
-    <t>EV-LO</t>
-  </si>
-  <si>
-    <t>16:15/17:15</t>
-  </si>
-  <si>
-    <t>18:30/23:30</t>
-  </si>
-  <si>
-    <t>17:15/19:15</t>
-  </si>
-  <si>
-    <t>15:45/17:15</t>
-  </si>
-  <si>
-    <t>19:15/00:30+</t>
-  </si>
-  <si>
-    <t>19:15/24:00</t>
-  </si>
-  <si>
-    <t>17:15/18:45</t>
-  </si>
-  <si>
-    <t>19:30/21:30</t>
-  </si>
-  <si>
-    <t>DOVINA Théo</t>
+    <t>Jour de référence : 05/04/2026</t>
+  </si>
+  <si>
+    <t>Du 30/03/2026 au 05/04/2026</t>
+  </si>
+  <si>
+    <t>COMMERCIAL DEDIES</t>
+  </si>
+  <si>
+    <t>ARBITRAGE</t>
+  </si>
+  <si>
+    <t>ANNIVERSAIRE</t>
+  </si>
+  <si>
+    <t>FORMATION</t>
   </si>
   <si>
     <t>FREIXEDAS-BERENGUER Maxime</t>
   </si>
   <si>
-    <t>HEBERT Jean Baptiste</t>
-  </si>
-  <si>
-    <t>JARGUEL Thomas</t>
-  </si>
-  <si>
-    <t>KABUNDA NDEKE Marvyn</t>
-  </si>
-  <si>
-    <t>LABEFODE Thomas</t>
-  </si>
-  <si>
     <t>MADESCLAIR Jean-Marc</t>
   </si>
   <si>
-    <t>MOSTEFA Yanis</t>
-  </si>
-  <si>
-    <t>09:30/10:15</t>
-  </si>
-  <si>
-    <t>10:15/12:15</t>
-  </si>
-  <si>
-    <t>12:15/12:45</t>
-  </si>
-  <si>
-    <t>ORDONEZ GOMEZ Oceane</t>
-  </si>
-  <si>
-    <t>19:30/22:30</t>
-  </si>
-  <si>
-    <t>18:30/20:30</t>
-  </si>
-  <si>
-    <t>PEREZ Loic</t>
-  </si>
-  <si>
-    <t>ENT-M</t>
-  </si>
-  <si>
-    <t>18:00/24:00</t>
-  </si>
-  <si>
-    <t>14:00/16:00</t>
-  </si>
-  <si>
-    <t>13:45/17:45</t>
-  </si>
-  <si>
-    <t>15:30/16:30</t>
-  </si>
-  <si>
-    <t>09:00/09:30</t>
-  </si>
-  <si>
-    <t>EV-RE</t>
-  </si>
-  <si>
-    <t>16:00/17:15</t>
-  </si>
-  <si>
-    <t>16:30/21:00</t>
-  </si>
-  <si>
-    <t>09:30/12:30</t>
-  </si>
-  <si>
-    <t>21:00/24:00</t>
-  </si>
-  <si>
-    <t>15:45/17:45</t>
-  </si>
-  <si>
-    <t>22:30/24:00</t>
-  </si>
-  <si>
-    <t>PISTORE Remi</t>
-  </si>
-  <si>
-    <t>PUJOL Mathieu</t>
-  </si>
-  <si>
-    <t>09:45/18:00</t>
-  </si>
-  <si>
-    <t>17:30/18:45</t>
-  </si>
-  <si>
-    <t>09:45/14:00</t>
-  </si>
-  <si>
-    <t>07:30/08:45</t>
-  </si>
-  <si>
-    <t>EDF-A</t>
-  </si>
-  <si>
-    <t>18:45/22:45</t>
-  </si>
-  <si>
-    <t>08:45/09:45</t>
-  </si>
-  <si>
-    <t>09:45/17:30</t>
-  </si>
-  <si>
-    <t>RABII Mehdi</t>
-  </si>
-  <si>
-    <t>17:45/21:45</t>
-  </si>
-  <si>
-    <t>SANGARNE Enzo</t>
-  </si>
-  <si>
-    <t>13:45/17:30</t>
-  </si>
-  <si>
-    <t>SEIGNE Kevin</t>
-  </si>
-  <si>
-    <t>TINGUY Florian</t>
-  </si>
-  <si>
-    <t>TOPPAN Mattis</t>
-  </si>
-  <si>
-    <t>17:30/00:30+</t>
-  </si>
-  <si>
-    <t>15:00/22:20</t>
-  </si>
-  <si>
-    <t>VASSANT Tiffany</t>
-  </si>
-  <si>
-    <t>Jour de référence : 05/04/2026</t>
-  </si>
-  <si>
-    <t>Du 30/03/2026 au 05/04/2026</t>
-  </si>
-  <si>
-    <t>COMMERCIAL DEDIES</t>
-  </si>
-  <si>
-    <t>ARBITRAGE</t>
-  </si>
-  <si>
-    <t>ANNIVERSAIRE</t>
-  </si>
-  <si>
-    <t>FORMATION</t>
-  </si>
-  <si>
     <t>Société</t>
   </si>
   <si>
@@ -410,57 +485,6 @@
   </si>
   <si>
     <t>19/03/2026 12:22</t>
-  </si>
-  <si>
-    <t>13:00/15:00</t>
-  </si>
-  <si>
-    <t>12:15/13:00</t>
-  </si>
-  <si>
-    <t>13:00/18:30</t>
-  </si>
-  <si>
-    <t>14:15/17:15</t>
-  </si>
-  <si>
-    <t>16:45/18:30</t>
-  </si>
-  <si>
-    <t>15:00/17:00</t>
-  </si>
-  <si>
-    <t>P25 // EDF // LEAGUES</t>
-  </si>
-  <si>
-    <t>EDF // LEAGUES</t>
-  </si>
-  <si>
-    <t>C. PADEL // EVENT EQUANS // LEAGUES</t>
-  </si>
-  <si>
-    <t>EDF</t>
-  </si>
-  <si>
-    <t>P250 // EDF // ANNIV</t>
-  </si>
-  <si>
-    <t>20:15/21:45</t>
-  </si>
-  <si>
-    <t>17:45/20:15</t>
-  </si>
-  <si>
-    <t>11:00/18:15</t>
-  </si>
-  <si>
-    <t>11:30/14:30</t>
-  </si>
-  <si>
-    <t>11:00/17:30</t>
-  </si>
-  <si>
-    <t>09:45/11:45</t>
   </si>
 </sst>
 </file>
@@ -470,7 +494,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -507,51 +531,12 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
     </font>
     <font>
       <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
@@ -568,8 +553,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -623,8 +613,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -925,11 +921,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -940,29 +956,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1000,49 +995,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1078,34 +1031,34 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1114,13 +1067,10 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1129,11 +1079,98 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3960,50 +3997,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6637,327 +6630,327 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H93"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="36" t="s">
+    <row r="1" spans="1:8">
+      <c r="B1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="B2" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="36" t="s">
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="C3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="D3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="F3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="G3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="H3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="12" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="D4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="48" t="s">
+      <c r="E4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="16"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="28"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="49" t="s">
+      <c r="F4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="19"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="G4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15" t="s">
+      <c r="H4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="28"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18" t="s">
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="19"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="65" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
+      <c r="H5" s="9"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A6" s="49"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="12"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="9"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A8" s="49"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="12"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="53"/>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="68" t="s">
-        <v>145</v>
+        <v>27</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>28</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="50" t="s">
-        <v>19</v>
+      <c r="H10" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="53"/>
+      <c r="B11" s="29" t="s">
+        <v>30</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11" s="20"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="B12" s="52" t="s">
-        <v>25</v>
+      <c r="H11" s="13"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="53"/>
+      <c r="B12" s="31" t="s">
+        <v>31</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="67" t="s">
-        <v>23</v>
+        <v>32</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>33</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="H12" s="20"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
-      <c r="B13" s="50" t="s">
-        <v>27</v>
+      <c r="H12" s="13"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="53"/>
+      <c r="B13" s="29" t="s">
+        <v>34</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="50" t="s">
-        <v>19</v>
+      <c r="E13" s="29" t="s">
+        <v>30</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="20"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
-      <c r="B14" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="19"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="16"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="26"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
-        <v>33</v>
+      <c r="H13" s="13"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A14" s="49"/>
+      <c r="B14" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="12"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="9"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A16" s="49"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A17" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="50"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="52"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="48" t="s">
+        <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="62"/>
+    <row r="19" spans="1:8">
+      <c r="A19" s="54"/>
       <c r="B19" s="1" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="62"/>
+    <row r="20" spans="1:8">
+      <c r="A20" s="54"/>
       <c r="B20" s="1"/>
       <c r="C20" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -6965,11 +6958,11 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A21" s="49"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -6977,1087 +6970,1099 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="H22" s="59" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="33"/>
+    <row r="22" spans="1:8">
+      <c r="A22" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="53"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F23" s="1"/>
-      <c r="G23" s="55" t="s">
-        <v>39</v>
-      </c>
-      <c r="H23" s="58" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="33"/>
+      <c r="G23" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="53"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H24" s="22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="61" t="s">
-        <v>45</v>
+        <v>21</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A25" s="49"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>53</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E26" s="61" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="E26" s="40" t="s">
+        <v>53</v>
       </c>
       <c r="F26" s="1"/>
-      <c r="G26" s="41" t="s">
-        <v>46</v>
+      <c r="G26" s="20" t="s">
+        <v>55</v>
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="45"/>
-      <c r="B27" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="60" t="s">
-        <v>47</v>
+    <row r="27" spans="1:8">
+      <c r="A27" s="55"/>
+      <c r="B27" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>56</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E27" s="60" t="s">
-        <v>47</v>
+        <v>57</v>
+      </c>
+      <c r="E27" s="39" t="s">
+        <v>56</v>
       </c>
       <c r="F27" s="1"/>
-      <c r="G27" s="42" t="s">
-        <v>48</v>
+      <c r="G27" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="45"/>
+    <row r="28" spans="1:8">
+      <c r="A28" s="55"/>
       <c r="B28" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="61" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="D28" s="40" t="s">
+        <v>53</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F28" s="1"/>
-      <c r="G28" s="42"/>
+      <c r="G28" s="21"/>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="45"/>
+    <row r="29" spans="1:8">
+      <c r="A29" s="55"/>
       <c r="B29" s="1" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="60" t="s">
-        <v>134</v>
+        <v>61</v>
+      </c>
+      <c r="D29" s="39" t="s">
+        <v>62</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="F29" s="1"/>
-      <c r="G29" s="42"/>
+      <c r="G29" s="21"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="45"/>
-      <c r="B30" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" s="61" t="s">
-        <v>45</v>
+    <row r="30" spans="1:8">
+      <c r="A30" s="55"/>
+      <c r="B30" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="40" t="s">
+        <v>53</v>
       </c>
       <c r="F30" s="1"/>
-      <c r="G30" s="42"/>
+      <c r="G30" s="21"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="45"/>
-      <c r="B31" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="C31" s="60" t="s">
-        <v>132</v>
-      </c>
-      <c r="D31" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="60" t="s">
-        <v>52</v>
+    <row r="31" spans="1:8">
+      <c r="A31" s="55"/>
+      <c r="B31" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" s="39" t="s">
+        <v>66</v>
       </c>
       <c r="F31" s="1"/>
-      <c r="G31" s="42"/>
+      <c r="G31" s="21"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="45"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="60"/>
-      <c r="D32" s="47"/>
+    <row r="32" spans="1:8">
+      <c r="A32" s="55"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="26"/>
       <c r="E32" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F32" s="1"/>
-      <c r="G32" s="42"/>
+      <c r="G32" s="21"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="45"/>
-      <c r="B33" s="42"/>
-      <c r="C33" s="60"/>
-      <c r="D33" s="47"/>
+    <row r="33" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A33" s="55"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="26"/>
       <c r="E33" s="1" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="F33" s="1"/>
-      <c r="G33" s="42"/>
+      <c r="G33" s="21"/>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" s="16"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="28"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="19"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="39" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="E36" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="F36" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="15"/>
-      <c r="H36" s="16"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="33"/>
-      <c r="B37" s="40" t="s">
-        <v>59</v>
+    <row r="34" spans="1:8">
+      <c r="A34" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="9"/>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A35" s="49"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="12"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="8"/>
+      <c r="D36" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F36" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" s="8"/>
+      <c r="H36" s="9"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="53"/>
+      <c r="B37" s="19" t="s">
+        <v>73</v>
       </c>
       <c r="C37" s="1"/>
-      <c r="D37" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="E37" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="F37" s="47" t="s">
-        <v>61</v>
+      <c r="D37" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F37" s="26" t="s">
+        <v>76</v>
       </c>
       <c r="G37" s="1"/>
-      <c r="H37" s="20"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="33"/>
-      <c r="B38" s="46" t="s">
-        <v>13</v>
+      <c r="H37" s="13"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="53"/>
+      <c r="B38" s="25" t="s">
+        <v>18</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E38" s="42"/>
+        <v>21</v>
+      </c>
+      <c r="E38" s="21"/>
       <c r="F38" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G38" s="1"/>
-      <c r="H38" s="20"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="33"/>
-      <c r="B39" s="47" t="s">
-        <v>61</v>
+      <c r="H38" s="13"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="53"/>
+      <c r="B39" s="26" t="s">
+        <v>76</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E39" s="42"/>
+        <v>77</v>
+      </c>
+      <c r="E39" s="21"/>
       <c r="F39" s="1" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G39" s="1"/>
-      <c r="H39" s="20"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="33"/>
+      <c r="H39" s="13"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="53"/>
       <c r="B40" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C40" s="1"/>
-      <c r="D40" s="46" t="s">
-        <v>57</v>
-      </c>
-      <c r="E40" s="42"/>
+      <c r="D40" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" s="21"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="H40" s="20"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="33"/>
+      <c r="H40" s="13"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="53"/>
       <c r="B41" s="1" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C41" s="1"/>
-      <c r="D41" s="47" t="s">
-        <v>65</v>
-      </c>
-      <c r="E41" s="42"/>
+      <c r="D41" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="21"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-      <c r="H41" s="20"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="33"/>
+      <c r="H41" s="13"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="53"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42" s="42"/>
+      <c r="D42" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="21"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="20"/>
-    </row>
-    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="28"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="51" t="s">
-        <v>66</v>
-      </c>
-      <c r="E43" s="44"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="19"/>
-    </row>
-    <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B44" s="24"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="26"/>
-    </row>
-    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="B45" s="24"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="26"/>
-    </row>
-    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B46" s="24"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="26"/>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="B47" s="30"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="32"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="15"/>
-      <c r="H48" s="16"/>
-    </row>
-    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="28"/>
-      <c r="B49" s="18"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="G49" s="18"/>
-      <c r="H49" s="19"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="33"/>
+      <c r="H42" s="13"/>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A43" s="49"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="E43" s="23"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="12"/>
+    </row>
+    <row r="44" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A44" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" s="50"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="52"/>
+    </row>
+    <row r="45" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A45" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="50"/>
+      <c r="C45" s="51"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="52"/>
+    </row>
+    <row r="46" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A46" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B46" s="50"/>
+      <c r="C46" s="51"/>
+      <c r="D46" s="51"/>
+      <c r="E46" s="51"/>
+      <c r="F46" s="51"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="52"/>
+    </row>
+    <row r="47" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A47" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B47" s="57"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="58"/>
+      <c r="H47" s="59"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" s="8"/>
+      <c r="H48" s="9"/>
+    </row>
+    <row r="49" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A49" s="49"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="G49" s="11"/>
+      <c r="H49" s="12"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="53"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="20" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="33"/>
+      <c r="H51" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="53"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
-      <c r="H52" s="56" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="33"/>
+      <c r="H52" s="35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="53"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
-      <c r="H53" s="58" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="33"/>
+      <c r="H53" s="37" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="53"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-      <c r="H54" s="22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="33"/>
+      <c r="H54" s="15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="53"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
-      <c r="H55" s="20" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="33"/>
+      <c r="H55" s="13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="53"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
-      <c r="H56" s="56" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="28"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-      <c r="H57" s="57" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="B58" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="C58" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="D58" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="E58" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="16"/>
-    </row>
-    <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="28"/>
-      <c r="B59" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="C59" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="D59" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="E59" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="19"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="B60" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" s="65" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F60" s="15"/>
-      <c r="G60" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="H60" s="16"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="33"/>
+      <c r="H56" s="35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A57" s="49"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="36" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="B58" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C58" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="E58" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="9"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="49"/>
+      <c r="B59" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C59" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D59" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="12"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="68" t="s">
+        <v>95</v>
+      </c>
+      <c r="F60" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" s="9"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="53"/>
       <c r="B61" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C61" s="66" t="s">
-        <v>84</v>
-      </c>
-      <c r="D61" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F61" s="1"/>
-      <c r="G61" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="H61" s="20"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="33"/>
+        <v>96</v>
+      </c>
+      <c r="C61" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="D61" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="E61" s="69" t="s">
+        <v>99</v>
+      </c>
+      <c r="F61" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="G61" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="H61" s="13"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="53"/>
       <c r="B62" s="1"/>
       <c r="C62" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E62" s="41" t="s">
-        <v>88</v>
-      </c>
-      <c r="F62" s="1"/>
-      <c r="G62" s="46" t="s">
-        <v>57</v>
-      </c>
-      <c r="H62" s="20"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="33"/>
+        <v>21</v>
+      </c>
+      <c r="E62" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="F62" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="G62" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H62" s="13"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="53"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E63" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="F63" s="1"/>
-      <c r="G63" s="47" t="s">
-        <v>91</v>
-      </c>
-      <c r="H63" s="20"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="33"/>
+        <v>103</v>
+      </c>
+      <c r="E63" s="71" t="s">
+        <v>104</v>
+      </c>
+      <c r="F63" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="G63" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="H63" s="13"/>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="53"/>
       <c r="B64" s="1"/>
-      <c r="C64" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="D64" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F64" s="1"/>
-      <c r="G64" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="H64" s="20"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="33"/>
+      <c r="C64" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E64" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="F64" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="G64" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" s="13"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="53"/>
       <c r="B65" s="1"/>
-      <c r="C65" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="D65" s="52" t="s">
-        <v>140</v>
-      </c>
-      <c r="E65" s="1" t="s">
+      <c r="C65" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D65" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="E65" s="66" t="s">
+        <v>108</v>
+      </c>
+      <c r="F65" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="G65" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="H65" s="13"/>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="53"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66" s="31"/>
+      <c r="E66" s="64" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="G66" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="H66" s="13"/>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="53"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="F65" s="1"/>
-      <c r="G65" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="H65" s="20"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="33"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="D66" s="52"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="H66" s="20"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="33"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="52" t="s">
-        <v>79</v>
-      </c>
-      <c r="D67" s="52"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="55" t="s">
-        <v>93</v>
-      </c>
-      <c r="H67" s="20"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="33"/>
+      <c r="D67" s="31"/>
+      <c r="E67" s="66" t="s">
+        <v>109</v>
+      </c>
+      <c r="F67" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="G67" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="H67" s="13"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="53"/>
       <c r="B68" s="1"/>
       <c r="C68" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D68" s="52"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="55"/>
-      <c r="H68" s="20"/>
-    </row>
-    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="28"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D69" s="51"/>
-      <c r="E69" s="18"/>
-      <c r="F69" s="18"/>
-      <c r="G69" s="63"/>
-      <c r="H69" s="19"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" s="15"/>
-      <c r="H70" s="16"/>
-    </row>
-    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="35"/>
+        <v>21</v>
+      </c>
+      <c r="D68" s="31"/>
+      <c r="E68" s="66" t="s">
+        <v>101</v>
+      </c>
+      <c r="F68" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="G68" s="34"/>
+      <c r="H68" s="13"/>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="49"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D69" s="30"/>
+      <c r="E69" s="66" t="s">
+        <v>101</v>
+      </c>
+      <c r="F69" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="G69" s="41"/>
+      <c r="H69" s="12"/>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="B70" s="8"/>
+      <c r="C70" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" s="8"/>
+      <c r="H70" s="9"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="61"/>
       <c r="B71" s="1"/>
-      <c r="C71" s="47" t="s">
-        <v>61</v>
+      <c r="C71" s="26" t="s">
+        <v>76</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
-      <c r="F71" s="47" t="s">
-        <v>61</v>
+      <c r="F71" s="26" t="s">
+        <v>76</v>
       </c>
       <c r="G71" s="1"/>
-      <c r="H71" s="20"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="B72" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" s="15"/>
-      <c r="D72" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E72" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F72" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G72" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H72" s="16"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="33"/>
+      <c r="H71" s="13"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H72" s="9"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="53"/>
       <c r="B73" s="1" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H73" s="20"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="33"/>
+        <v>117</v>
+      </c>
+      <c r="H73" s="13"/>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="53"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
-      <c r="E74" s="41" t="s">
-        <v>58</v>
+      <c r="E74" s="20" t="s">
+        <v>72</v>
       </c>
       <c r="F74" s="1"/>
-      <c r="G74" s="46" t="s">
-        <v>101</v>
-      </c>
-      <c r="H74" s="20"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="33"/>
+      <c r="G74" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="H74" s="13"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="53"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
-      <c r="E75" s="42" t="s">
-        <v>102</v>
+      <c r="E75" s="21" t="s">
+        <v>119</v>
       </c>
       <c r="F75" s="1"/>
-      <c r="G75" s="47" t="s">
-        <v>103</v>
-      </c>
-      <c r="H75" s="20"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="33"/>
+      <c r="G75" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="H75" s="13"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="53"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
-      <c r="E76" s="42"/>
+      <c r="E76" s="21"/>
       <c r="F76" s="1"/>
       <c r="G76" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H76" s="20"/>
-    </row>
-    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="28"/>
-      <c r="B77" s="18"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="44"/>
-      <c r="F77" s="18"/>
-      <c r="G77" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="H77" s="19"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="B78" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="C78" s="15"/>
-      <c r="D78" s="15"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="15"/>
-      <c r="G78" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="H78" s="16"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="33"/>
-      <c r="B79" s="52" t="s">
-        <v>79</v>
+        <v>21</v>
+      </c>
+      <c r="H76" s="13"/>
+    </row>
+    <row r="77" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A77" s="49"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="23"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="H77" s="12"/>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="B78" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="H78" s="9"/>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="53"/>
+      <c r="B79" s="31" t="s">
+        <v>92</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
-      <c r="G79" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="H79" s="20"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="33"/>
-      <c r="B80" s="52"/>
+      <c r="G79" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="H79" s="13"/>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="53"/>
+      <c r="B80" s="31"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H80" s="20"/>
-    </row>
-    <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="28"/>
-      <c r="B81" s="51"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="H81" s="19"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="B82" s="15"/>
-      <c r="C82" s="15"/>
-      <c r="D82" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E82" s="15"/>
-      <c r="F82" s="15"/>
-      <c r="G82" s="15"/>
-      <c r="H82" s="16"/>
-    </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="28"/>
-      <c r="B83" s="18"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="49" t="s">
-        <v>108</v>
-      </c>
-      <c r="E83" s="18"/>
-      <c r="F83" s="18"/>
-      <c r="G83" s="18"/>
-      <c r="H83" s="19"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="B84" s="15"/>
-      <c r="C84" s="15"/>
-      <c r="D84" s="15"/>
-      <c r="E84" s="15"/>
-      <c r="F84" s="15"/>
-      <c r="G84" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="H84" s="16"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="33"/>
+        <v>21</v>
+      </c>
+      <c r="H80" s="13"/>
+    </row>
+    <row r="81" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A81" s="49"/>
+      <c r="B81" s="30"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="H81" s="12"/>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E82" s="8"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="9"/>
+    </row>
+    <row r="83" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A83" s="49"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="12"/>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H84" s="9"/>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="53"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
-      <c r="G85" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="H85" s="20"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="33"/>
+      <c r="G85" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" s="13"/>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="53"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
-      <c r="G86" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="H86" s="20"/>
-    </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="28"/>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="H87" s="19"/>
-    </row>
-    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="B88" s="24"/>
-      <c r="C88" s="25"/>
-      <c r="D88" s="25"/>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="26"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="34" t="s">
-        <v>111</v>
+      <c r="G86" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H86" s="13"/>
+    </row>
+    <row r="87" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A87" s="49"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="11"/>
+      <c r="G87" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="H87" s="12"/>
+    </row>
+    <row r="88" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A88" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B88" s="50"/>
+      <c r="C88" s="51"/>
+      <c r="D88" s="51"/>
+      <c r="E88" s="51"/>
+      <c r="F88" s="51"/>
+      <c r="G88" s="51"/>
+      <c r="H88" s="52"/>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="60" t="s">
+        <v>128</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
       <c r="D89" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E89" s="1"/>
       <c r="F89" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G89" s="1"/>
-      <c r="H89" s="20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="28"/>
-      <c r="B90" s="18"/>
-      <c r="C90" s="18"/>
-      <c r="D90" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="E90" s="18"/>
-      <c r="F90" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="G90" s="18"/>
-      <c r="H90" s="19" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="B91" s="15"/>
-      <c r="C91" s="15"/>
-      <c r="D91" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="15"/>
-      <c r="F91" s="15"/>
-      <c r="G91" s="15"/>
-      <c r="H91" s="16"/>
-    </row>
-    <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="28"/>
-      <c r="B92" s="18"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="49" t="s">
-        <v>108</v>
-      </c>
-      <c r="E92" s="18"/>
-      <c r="F92" s="18"/>
-      <c r="G92" s="18"/>
-      <c r="H92" s="19"/>
-    </row>
-    <row r="93" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="29"/>
-      <c r="C93" s="29"/>
-      <c r="D93" s="29"/>
-      <c r="E93" s="29"/>
-      <c r="F93" s="29"/>
-      <c r="G93" s="29"/>
-      <c r="H93" s="29"/>
+      <c r="H89" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A90" s="49"/>
+      <c r="B90" s="11"/>
+      <c r="C90" s="11"/>
+      <c r="D90" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E90" s="11"/>
+      <c r="F90" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="G90" s="11"/>
+      <c r="H90" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91" s="8"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="9"/>
+    </row>
+    <row r="92" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A92" s="49"/>
+      <c r="B92" s="11"/>
+      <c r="C92" s="11"/>
+      <c r="D92" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E92" s="11"/>
+      <c r="F92" s="11"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="12"/>
+    </row>
+    <row r="93" spans="1:8" ht="6.75" customHeight="1">
+      <c r="B93" s="56"/>
+      <c r="C93" s="56"/>
+      <c r="D93" s="56"/>
+      <c r="E93" s="56"/>
+      <c r="F93" s="56"/>
+      <c r="G93" s="56"/>
+      <c r="H93" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B44:H44"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A26:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A43"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="B17:H17"/>
     <mergeCell ref="A91:A92"/>
     <mergeCell ref="B93:H93"/>
     <mergeCell ref="B88:H88"/>
@@ -8072,6 +8077,22 @@
     <mergeCell ref="A60:A69"/>
     <mergeCell ref="A70:A71"/>
     <mergeCell ref="A72:A77"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A26:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A43"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B17:H17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="34" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -8082,533 +8103,533 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="7">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="7">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="7">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="62" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5" s="63" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="72">
+        <v>0</v>
+      </c>
+      <c r="C7" s="72">
+        <v>0</v>
+      </c>
+      <c r="D7" s="72">
+        <v>0</v>
+      </c>
+      <c r="E7" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="72">
+        <v>0</v>
+      </c>
+      <c r="C8" s="72">
+        <v>0</v>
+      </c>
+      <c r="D8" s="72">
+        <v>0</v>
+      </c>
+      <c r="E8" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="72">
+        <v>0</v>
+      </c>
+      <c r="C9" s="72">
         <v>4.1667000000000003E-2</v>
       </c>
-      <c r="D9" s="7">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="7">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="7">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="7">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="7">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="D9" s="72">
+        <v>0</v>
+      </c>
+      <c r="E9" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="72">
+        <v>0</v>
+      </c>
+      <c r="C10" s="72">
+        <v>0</v>
+      </c>
+      <c r="D10" s="72">
+        <v>0</v>
+      </c>
+      <c r="E10" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="72">
+        <v>0</v>
+      </c>
+      <c r="C11" s="72">
+        <v>0</v>
+      </c>
+      <c r="D11" s="72">
+        <v>0</v>
+      </c>
+      <c r="E11" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="72">
+        <v>0</v>
+      </c>
+      <c r="C12" s="72">
+        <v>0</v>
+      </c>
+      <c r="D12" s="72">
+        <v>0</v>
+      </c>
+      <c r="E12" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="72">
+        <v>0</v>
+      </c>
+      <c r="C13" s="72">
+        <v>0</v>
+      </c>
+      <c r="D13" s="72">
         <v>0.24166699999999999</v>
       </c>
-      <c r="E13" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="7">
-        <v>0</v>
-      </c>
-      <c r="C14" s="7">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="7">
-        <v>0</v>
-      </c>
-      <c r="C15" s="7">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7">
-        <v>0</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="7">
+      <c r="E13" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="72">
+        <v>0</v>
+      </c>
+      <c r="C14" s="72">
+        <v>0</v>
+      </c>
+      <c r="D14" s="72">
+        <v>0</v>
+      </c>
+      <c r="E14" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="72">
+        <v>0</v>
+      </c>
+      <c r="C15" s="72">
+        <v>0</v>
+      </c>
+      <c r="D15" s="72">
+        <v>0</v>
+      </c>
+      <c r="E15" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="72">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="72">
         <v>8.3334000000000005E-2</v>
       </c>
-      <c r="D16" s="7">
-        <v>0</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="7">
-        <v>0</v>
-      </c>
-      <c r="C17" s="7">
-        <v>0</v>
-      </c>
-      <c r="D17" s="7">
-        <v>0</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="7">
-        <v>0</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0</v>
-      </c>
-      <c r="D18" s="7">
-        <v>0</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="7">
-        <v>0</v>
-      </c>
-      <c r="C19" s="7">
-        <v>0</v>
-      </c>
-      <c r="D19" s="7">
-        <v>0</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="7">
-        <v>0</v>
-      </c>
-      <c r="C20" s="7">
-        <v>0</v>
-      </c>
-      <c r="D20" s="7">
-        <v>0</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="7">
-        <v>0</v>
-      </c>
-      <c r="C21" s="7">
-        <v>0</v>
-      </c>
-      <c r="D21" s="7">
-        <v>0</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" s="7">
-        <v>0</v>
-      </c>
-      <c r="C22" s="7">
-        <v>0</v>
-      </c>
-      <c r="D22" s="7">
-        <v>0</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="7">
-        <v>0</v>
-      </c>
-      <c r="C23" s="7">
-        <v>0</v>
-      </c>
-      <c r="D23" s="7">
-        <v>0</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="7">
-        <v>0</v>
-      </c>
-      <c r="C24" s="7">
-        <v>0</v>
-      </c>
-      <c r="D24" s="7">
+      <c r="D16" s="72">
+        <v>0</v>
+      </c>
+      <c r="E16" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="72">
+        <v>0</v>
+      </c>
+      <c r="C17" s="72">
+        <v>0</v>
+      </c>
+      <c r="D17" s="72">
+        <v>0</v>
+      </c>
+      <c r="E17" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="72">
+        <v>0</v>
+      </c>
+      <c r="C18" s="72">
+        <v>0</v>
+      </c>
+      <c r="D18" s="72">
+        <v>0</v>
+      </c>
+      <c r="E18" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="72">
+        <v>0</v>
+      </c>
+      <c r="C19" s="72">
+        <v>0</v>
+      </c>
+      <c r="D19" s="72">
+        <v>0</v>
+      </c>
+      <c r="E19" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="72">
+        <v>0</v>
+      </c>
+      <c r="C20" s="72">
+        <v>0</v>
+      </c>
+      <c r="D20" s="72">
+        <v>0</v>
+      </c>
+      <c r="E20" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="72">
+        <v>0</v>
+      </c>
+      <c r="C21" s="72">
+        <v>0</v>
+      </c>
+      <c r="D21" s="72">
+        <v>0</v>
+      </c>
+      <c r="E21" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="72">
+        <v>0</v>
+      </c>
+      <c r="C22" s="72">
+        <v>0</v>
+      </c>
+      <c r="D22" s="72">
+        <v>0</v>
+      </c>
+      <c r="E22" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="72">
+        <v>0</v>
+      </c>
+      <c r="C23" s="72">
+        <v>0</v>
+      </c>
+      <c r="D23" s="72">
+        <v>0</v>
+      </c>
+      <c r="E23" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="72">
+        <v>0</v>
+      </c>
+      <c r="C24" s="72">
+        <v>0</v>
+      </c>
+      <c r="D24" s="72">
         <v>0.25</v>
       </c>
-      <c r="E24" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="7">
-        <v>0</v>
-      </c>
-      <c r="C25" s="7">
+      <c r="E24" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="72">
+        <v>0</v>
+      </c>
+      <c r="C25" s="72">
         <v>0.45833400000000002</v>
       </c>
-      <c r="D25" s="7">
-        <v>0</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" s="7">
-        <v>0</v>
-      </c>
-      <c r="C26" s="7">
+      <c r="D25" s="72">
+        <v>0</v>
+      </c>
+      <c r="E25" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="72">
+        <v>0</v>
+      </c>
+      <c r="C26" s="72">
         <v>0.16666700000000001</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="72">
         <v>8.3334000000000005E-2</v>
       </c>
-      <c r="E26" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B27" s="7">
-        <v>0</v>
-      </c>
-      <c r="C27" s="7">
-        <v>0</v>
-      </c>
-      <c r="D27" s="7">
-        <v>0</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B28" s="7">
-        <v>0</v>
-      </c>
-      <c r="C28" s="7">
-        <v>0</v>
-      </c>
-      <c r="D28" s="7">
-        <v>0</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B29" s="7">
-        <v>0</v>
-      </c>
-      <c r="C29" s="7">
+      <c r="E26" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="72">
+        <v>0</v>
+      </c>
+      <c r="C27" s="72">
+        <v>0</v>
+      </c>
+      <c r="D27" s="72">
+        <v>0</v>
+      </c>
+      <c r="E27" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="72">
+        <v>0</v>
+      </c>
+      <c r="C28" s="72">
+        <v>0</v>
+      </c>
+      <c r="D28" s="72">
+        <v>0</v>
+      </c>
+      <c r="E28" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="72">
+        <v>0</v>
+      </c>
+      <c r="C29" s="72">
         <v>0.125</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="72">
         <v>0.159723</v>
       </c>
-      <c r="E29" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B30" s="7">
-        <v>0</v>
-      </c>
-      <c r="C30" s="7">
-        <v>0</v>
-      </c>
-      <c r="D30" s="7">
-        <v>0</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B31" s="7">
-        <v>0</v>
-      </c>
-      <c r="C31" s="7">
-        <v>0</v>
-      </c>
-      <c r="D31" s="7">
-        <v>0</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B32" s="7">
-        <v>0</v>
-      </c>
-      <c r="C32" s="7">
-        <v>0</v>
-      </c>
-      <c r="D32" s="7">
-        <v>0</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="B33" s="7">
-        <v>0</v>
-      </c>
-      <c r="C33" s="7">
-        <v>0</v>
-      </c>
-      <c r="D33" s="7">
-        <v>0</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B34" s="7">
-        <v>0</v>
-      </c>
-      <c r="C34" s="7">
-        <v>0</v>
-      </c>
-      <c r="D34" s="7">
-        <v>0</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="8">
+      <c r="E29" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30" s="72">
+        <v>0</v>
+      </c>
+      <c r="C30" s="72">
+        <v>0</v>
+      </c>
+      <c r="D30" s="72">
+        <v>0</v>
+      </c>
+      <c r="E30" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="72">
+        <v>0</v>
+      </c>
+      <c r="C31" s="72">
+        <v>0</v>
+      </c>
+      <c r="D31" s="72">
+        <v>0</v>
+      </c>
+      <c r="E31" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="72">
+        <v>0</v>
+      </c>
+      <c r="C32" s="72">
+        <v>0</v>
+      </c>
+      <c r="D32" s="72">
+        <v>0</v>
+      </c>
+      <c r="E32" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" s="72">
+        <v>0</v>
+      </c>
+      <c r="C33" s="72">
+        <v>0</v>
+      </c>
+      <c r="D33" s="72">
+        <v>0</v>
+      </c>
+      <c r="E33" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" s="72">
+        <v>0</v>
+      </c>
+      <c r="C34" s="72">
+        <v>0</v>
+      </c>
+      <c r="D34" s="72">
+        <v>0</v>
+      </c>
+      <c r="E34" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="B35" s="73">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="73">
         <v>0.875</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="73">
         <v>0.73472300000000001</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="73">
         <v>0</v>
       </c>
     </row>
@@ -8624,49 +8645,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B5" s="11"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>128</v>
+    <row r="1" spans="1:2" ht="15.75">
+      <c r="A1" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="74" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" s="75" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="74" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="75"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="74" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="75" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="74" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="75" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="74" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" s="75" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -8676,6 +8697,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3c298670-db79-47a5-968d-a4570c34317f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="17e8e7ea-beb0-4155-adc4-5bfa61f32508" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F57AE488C1C9C348AE667C65EC1B6349" ma:contentTypeVersion="83" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="584bf6b77295f7da4f9cf4ac656056b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3c298670-db79-47a5-968d-a4570c34317f" xmlns:ns3="17e8e7ea-beb0-4155-adc4-5bfa61f32508" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0744868ac059cd1623b27209cff1bde4" ns2:_="" ns3:_="">
     <xsd:import namespace="3c298670-db79-47a5-968d-a4570c34317f"/>
@@ -8820,28 +8861,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3c298670-db79-47a5-968d-a4570c34317f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="17e8e7ea-beb0-4155-adc4-5bfa61f32508" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55258B40-0392-499F-BBA5-A4C6FB1ACB8A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B3E9373-21F1-472D-A1B7-AB92AB4BB0C0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8849,5 +8870,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B3E9373-21F1-472D-A1B7-AB92AB4BB0C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55258B40-0392-499F-BBA5-A4C6FB1ACB8A}"/>
 </file>
--- a/Plannings 2026 S14.xlsx
+++ b/Plannings 2026 S14.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{150E33BF-47F0-4B68-8AA0-FBA696D166AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05A385D4-9949-4BBB-BE7E-6087CBA21D57}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{150E33BF-47F0-4B68-8AA0-FBA696D166AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A1E570E-3024-42B6-B1F7-2E6DA6078454}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -945,7 +945,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1154,10 +1154,7 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4015,67 +4012,2323 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E336BB2D-9E6B-47B9-BE5E-FFE8C1BB1112}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="6105525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6622D570-B9A8-4D55-BB7D-59FF206FA5DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="6486525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A72682A-4003-4AD9-92D2-66FFD05512D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="6867525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E455B04-0B57-4353-9A4A-29E00C6CFD34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="6105525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21309003-2EB5-43C5-AE11-9FE11F8AABEB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="6486525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{601E8654-CA14-40AA-9235-F816679D7AEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="6867525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0043B4C8-3617-48BF-932C-3A7E85E4AA1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="6486525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53641B0D-E6A1-4342-BD6D-1700BCC5A3EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="6105525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45020C9B-22C4-40D0-B2E3-27CBFEFEDA40}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="6486525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0933B496-0D4A-45FE-B385-61B5C9E2751A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="6867525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F3F8387-5776-46BC-A0AE-BEC530736891}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="7248525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D985268F-5094-43E3-BB46-806A6647F231}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3657600" y="6105525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{219D8BC5-7AC6-4839-BF80-8F352C912B3B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7960179" y="4871357"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1145537A-5613-4C97-AEAD-4E8C568A8320}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7960179" y="4871357"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>61</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{938346EC-4D64-469E-8E17-F994EEA43509}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6395357" y="11674929"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F3D6B16-D338-46BD-AF0B-90221FD57753}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6395357" y="2721429"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9797F6C7-5EE5-48DF-B225-068CC6FBAFEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6BC8F89-9F7F-44F5-A10A-8838A3FB2525}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A720C05B-FE82-4CFB-B4CE-1DB48AD6CD1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="4962525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61F8412D-29DD-4A64-9212-9F359FCD979B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01A479F5-06CB-4D1D-983D-7C15D096051B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6C3EBB1-996F-4483-8D04-33980E6B34E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3048000" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="123" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F515ACB-C59F-4BD4-968A-FA5E5D40D45C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9593036" y="4871357"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="124" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E44C59AC-4363-4F01-A01D-A57BCD98DD59}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6395357" y="11484429"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="125" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{054D7FC7-F6A0-4112-ACF7-68D41389B396}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6395357" y="11865429"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Image 7" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E683E050-DA9B-4D59-99DE-0B8870E96189}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{054D7FC7-F6A0-4112-ACF7-68D41389B396}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16002000" y="11401425"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Image 13" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBE173F4-AFE1-4F2C-B530-F2826F8AD0D5}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E683E050-DA9B-4D59-99DE-0B8870E96189}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12801600" y="12544425"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="Image 32" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AE168D3-72BF-4E47-8438-FA289729665B}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EBE173F4-AFE1-4F2C-B530-F2826F8AD0D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12801600" y="12163425"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Image 13" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{965B5492-7230-45E4-ACAF-2849F9724C0E}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8AE168D3-72BF-4E47-8438-FA289729665B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4091,2163 +6344,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E336BB2D-9E6B-47B9-BE5E-FFE8C1BB1112}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="6105525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6622D570-B9A8-4D55-BB7D-59FF206FA5DA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="6486525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A72682A-4003-4AD9-92D2-66FFD05512D0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="6867525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E455B04-0B57-4353-9A4A-29E00C6CFD34}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="6105525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21309003-2EB5-43C5-AE11-9FE11F8AABEB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="6486525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{601E8654-CA14-40AA-9235-F816679D7AEC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="6867525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0043B4C8-3617-48BF-932C-3A7E85E4AA1A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="6486525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53641B0D-E6A1-4342-BD6D-1700BCC5A3EE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="6105525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45020C9B-22C4-40D0-B2E3-27CBFEFEDA40}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="6486525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0933B496-0D4A-45FE-B385-61B5C9E2751A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="6867525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F3F8387-5776-46BC-A0AE-BEC530736891}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="7248525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D985268F-5094-43E3-BB46-806A6647F231}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3657600" y="6105525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{219D8BC5-7AC6-4839-BF80-8F352C912B3B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7960179" y="4871357"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1145537A-5613-4C97-AEAD-4E8C568A8320}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7960179" y="4871357"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{938346EC-4D64-469E-8E17-F994EEA43509}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6395357" y="11674929"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F3D6B16-D338-46BD-AF0B-90221FD57753}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6395357" y="2721429"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9797F6C7-5EE5-48DF-B225-068CC6FBAFEC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6BC8F89-9F7F-44F5-A10A-8838A3FB2525}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A720C05B-FE82-4CFB-B4CE-1DB48AD6CD1C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="4962525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61F8412D-29DD-4A64-9212-9F359FCD979B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01A479F5-06CB-4D1D-983D-7C15D096051B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6C3EBB1-996F-4483-8D04-33980E6B34E0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="123" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F515ACB-C59F-4BD4-968A-FA5E5D40D45C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9593036" y="4871357"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="124" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E44C59AC-4363-4F01-A01D-A57BCD98DD59}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6395357" y="11484429"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="125" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{054D7FC7-F6A0-4112-ACF7-68D41389B396}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6395357" y="11865429"/>
+          <a:off x="12801600" y="12544425"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7587,7 +7684,7 @@
       <c r="D62" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E62" s="70" t="s">
+      <c r="E62" s="64" t="s">
         <v>21</v>
       </c>
       <c r="F62" s="67" t="s">
@@ -7607,7 +7704,7 @@
       <c r="D63" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E63" s="71" t="s">
+      <c r="E63" s="70" t="s">
         <v>104</v>
       </c>
       <c r="F63" s="67" t="s">
@@ -8147,16 +8244,16 @@
       <c r="A7" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="72">
-        <v>0</v>
-      </c>
-      <c r="C7" s="72">
-        <v>0</v>
-      </c>
-      <c r="D7" s="72">
-        <v>0</v>
-      </c>
-      <c r="E7" s="72">
+      <c r="B7" s="71">
+        <v>0</v>
+      </c>
+      <c r="C7" s="71">
+        <v>0</v>
+      </c>
+      <c r="D7" s="71">
+        <v>0</v>
+      </c>
+      <c r="E7" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8164,16 +8261,16 @@
       <c r="A8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="72">
-        <v>0</v>
-      </c>
-      <c r="C8" s="72">
-        <v>0</v>
-      </c>
-      <c r="D8" s="72">
-        <v>0</v>
-      </c>
-      <c r="E8" s="72">
+      <c r="B8" s="71">
+        <v>0</v>
+      </c>
+      <c r="C8" s="71">
+        <v>0</v>
+      </c>
+      <c r="D8" s="71">
+        <v>0</v>
+      </c>
+      <c r="E8" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8181,16 +8278,16 @@
       <c r="A9" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="72">
-        <v>0</v>
-      </c>
-      <c r="C9" s="72">
+      <c r="B9" s="71">
+        <v>0</v>
+      </c>
+      <c r="C9" s="71">
         <v>4.1667000000000003E-2</v>
       </c>
-      <c r="D9" s="72">
-        <v>0</v>
-      </c>
-      <c r="E9" s="72">
+      <c r="D9" s="71">
+        <v>0</v>
+      </c>
+      <c r="E9" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8198,16 +8295,16 @@
       <c r="A10" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="72">
-        <v>0</v>
-      </c>
-      <c r="C10" s="72">
-        <v>0</v>
-      </c>
-      <c r="D10" s="72">
-        <v>0</v>
-      </c>
-      <c r="E10" s="72">
+      <c r="B10" s="71">
+        <v>0</v>
+      </c>
+      <c r="C10" s="71">
+        <v>0</v>
+      </c>
+      <c r="D10" s="71">
+        <v>0</v>
+      </c>
+      <c r="E10" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8215,16 +8312,16 @@
       <c r="A11" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="72">
-        <v>0</v>
-      </c>
-      <c r="C11" s="72">
-        <v>0</v>
-      </c>
-      <c r="D11" s="72">
-        <v>0</v>
-      </c>
-      <c r="E11" s="72">
+      <c r="B11" s="71">
+        <v>0</v>
+      </c>
+      <c r="C11" s="71">
+        <v>0</v>
+      </c>
+      <c r="D11" s="71">
+        <v>0</v>
+      </c>
+      <c r="E11" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8232,16 +8329,16 @@
       <c r="A12" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="72">
-        <v>0</v>
-      </c>
-      <c r="C12" s="72">
-        <v>0</v>
-      </c>
-      <c r="D12" s="72">
-        <v>0</v>
-      </c>
-      <c r="E12" s="72">
+      <c r="B12" s="71">
+        <v>0</v>
+      </c>
+      <c r="C12" s="71">
+        <v>0</v>
+      </c>
+      <c r="D12" s="71">
+        <v>0</v>
+      </c>
+      <c r="E12" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8249,16 +8346,16 @@
       <c r="A13" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="72">
-        <v>0</v>
-      </c>
-      <c r="C13" s="72">
-        <v>0</v>
-      </c>
-      <c r="D13" s="72">
+      <c r="B13" s="71">
+        <v>0</v>
+      </c>
+      <c r="C13" s="71">
+        <v>0</v>
+      </c>
+      <c r="D13" s="71">
         <v>0.24166699999999999</v>
       </c>
-      <c r="E13" s="72">
+      <c r="E13" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8266,16 +8363,16 @@
       <c r="A14" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="72">
-        <v>0</v>
-      </c>
-      <c r="C14" s="72">
-        <v>0</v>
-      </c>
-      <c r="D14" s="72">
-        <v>0</v>
-      </c>
-      <c r="E14" s="72">
+      <c r="B14" s="71">
+        <v>0</v>
+      </c>
+      <c r="C14" s="71">
+        <v>0</v>
+      </c>
+      <c r="D14" s="71">
+        <v>0</v>
+      </c>
+      <c r="E14" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8283,16 +8380,16 @@
       <c r="A15" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="72">
-        <v>0</v>
-      </c>
-      <c r="C15" s="72">
-        <v>0</v>
-      </c>
-      <c r="D15" s="72">
-        <v>0</v>
-      </c>
-      <c r="E15" s="72">
+      <c r="B15" s="71">
+        <v>0</v>
+      </c>
+      <c r="C15" s="71">
+        <v>0</v>
+      </c>
+      <c r="D15" s="71">
+        <v>0</v>
+      </c>
+      <c r="E15" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8300,16 +8397,16 @@
       <c r="A16" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="72">
+      <c r="B16" s="71">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="C16" s="72">
+      <c r="C16" s="71">
         <v>8.3334000000000005E-2</v>
       </c>
-      <c r="D16" s="72">
-        <v>0</v>
-      </c>
-      <c r="E16" s="72">
+      <c r="D16" s="71">
+        <v>0</v>
+      </c>
+      <c r="E16" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8317,16 +8414,16 @@
       <c r="A17" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="72">
-        <v>0</v>
-      </c>
-      <c r="C17" s="72">
-        <v>0</v>
-      </c>
-      <c r="D17" s="72">
-        <v>0</v>
-      </c>
-      <c r="E17" s="72">
+      <c r="B17" s="71">
+        <v>0</v>
+      </c>
+      <c r="C17" s="71">
+        <v>0</v>
+      </c>
+      <c r="D17" s="71">
+        <v>0</v>
+      </c>
+      <c r="E17" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8334,16 +8431,16 @@
       <c r="A18" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="B18" s="72">
-        <v>0</v>
-      </c>
-      <c r="C18" s="72">
-        <v>0</v>
-      </c>
-      <c r="D18" s="72">
-        <v>0</v>
-      </c>
-      <c r="E18" s="72">
+      <c r="B18" s="71">
+        <v>0</v>
+      </c>
+      <c r="C18" s="71">
+        <v>0</v>
+      </c>
+      <c r="D18" s="71">
+        <v>0</v>
+      </c>
+      <c r="E18" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8351,16 +8448,16 @@
       <c r="A19" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="72">
-        <v>0</v>
-      </c>
-      <c r="C19" s="72">
-        <v>0</v>
-      </c>
-      <c r="D19" s="72">
-        <v>0</v>
-      </c>
-      <c r="E19" s="72">
+      <c r="B19" s="71">
+        <v>0</v>
+      </c>
+      <c r="C19" s="71">
+        <v>0</v>
+      </c>
+      <c r="D19" s="71">
+        <v>0</v>
+      </c>
+      <c r="E19" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8368,16 +8465,16 @@
       <c r="A20" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="B20" s="72">
-        <v>0</v>
-      </c>
-      <c r="C20" s="72">
-        <v>0</v>
-      </c>
-      <c r="D20" s="72">
-        <v>0</v>
-      </c>
-      <c r="E20" s="72">
+      <c r="B20" s="71">
+        <v>0</v>
+      </c>
+      <c r="C20" s="71">
+        <v>0</v>
+      </c>
+      <c r="D20" s="71">
+        <v>0</v>
+      </c>
+      <c r="E20" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8385,16 +8482,16 @@
       <c r="A21" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="72">
-        <v>0</v>
-      </c>
-      <c r="C21" s="72">
-        <v>0</v>
-      </c>
-      <c r="D21" s="72">
-        <v>0</v>
-      </c>
-      <c r="E21" s="72">
+      <c r="B21" s="71">
+        <v>0</v>
+      </c>
+      <c r="C21" s="71">
+        <v>0</v>
+      </c>
+      <c r="D21" s="71">
+        <v>0</v>
+      </c>
+      <c r="E21" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8402,16 +8499,16 @@
       <c r="A22" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B22" s="72">
-        <v>0</v>
-      </c>
-      <c r="C22" s="72">
-        <v>0</v>
-      </c>
-      <c r="D22" s="72">
-        <v>0</v>
-      </c>
-      <c r="E22" s="72">
+      <c r="B22" s="71">
+        <v>0</v>
+      </c>
+      <c r="C22" s="71">
+        <v>0</v>
+      </c>
+      <c r="D22" s="71">
+        <v>0</v>
+      </c>
+      <c r="E22" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8419,16 +8516,16 @@
       <c r="A23" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="72">
-        <v>0</v>
-      </c>
-      <c r="C23" s="72">
-        <v>0</v>
-      </c>
-      <c r="D23" s="72">
-        <v>0</v>
-      </c>
-      <c r="E23" s="72">
+      <c r="B23" s="71">
+        <v>0</v>
+      </c>
+      <c r="C23" s="71">
+        <v>0</v>
+      </c>
+      <c r="D23" s="71">
+        <v>0</v>
+      </c>
+      <c r="E23" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8436,16 +8533,16 @@
       <c r="A24" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="72">
-        <v>0</v>
-      </c>
-      <c r="C24" s="72">
-        <v>0</v>
-      </c>
-      <c r="D24" s="72">
+      <c r="B24" s="71">
+        <v>0</v>
+      </c>
+      <c r="C24" s="71">
+        <v>0</v>
+      </c>
+      <c r="D24" s="71">
         <v>0.25</v>
       </c>
-      <c r="E24" s="72">
+      <c r="E24" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8453,16 +8550,16 @@
       <c r="A25" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B25" s="72">
-        <v>0</v>
-      </c>
-      <c r="C25" s="72">
+      <c r="B25" s="71">
+        <v>0</v>
+      </c>
+      <c r="C25" s="71">
         <v>0.45833400000000002</v>
       </c>
-      <c r="D25" s="72">
-        <v>0</v>
-      </c>
-      <c r="E25" s="72">
+      <c r="D25" s="71">
+        <v>0</v>
+      </c>
+      <c r="E25" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8470,16 +8567,16 @@
       <c r="A26" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="72">
-        <v>0</v>
-      </c>
-      <c r="C26" s="72">
+      <c r="B26" s="71">
+        <v>0</v>
+      </c>
+      <c r="C26" s="71">
         <v>0.16666700000000001</v>
       </c>
-      <c r="D26" s="72">
+      <c r="D26" s="71">
         <v>8.3334000000000005E-2</v>
       </c>
-      <c r="E26" s="72">
+      <c r="E26" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8487,16 +8584,16 @@
       <c r="A27" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="B27" s="72">
-        <v>0</v>
-      </c>
-      <c r="C27" s="72">
-        <v>0</v>
-      </c>
-      <c r="D27" s="72">
-        <v>0</v>
-      </c>
-      <c r="E27" s="72">
+      <c r="B27" s="71">
+        <v>0</v>
+      </c>
+      <c r="C27" s="71">
+        <v>0</v>
+      </c>
+      <c r="D27" s="71">
+        <v>0</v>
+      </c>
+      <c r="E27" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8504,16 +8601,16 @@
       <c r="A28" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="B28" s="72">
-        <v>0</v>
-      </c>
-      <c r="C28" s="72">
-        <v>0</v>
-      </c>
-      <c r="D28" s="72">
-        <v>0</v>
-      </c>
-      <c r="E28" s="72">
+      <c r="B28" s="71">
+        <v>0</v>
+      </c>
+      <c r="C28" s="71">
+        <v>0</v>
+      </c>
+      <c r="D28" s="71">
+        <v>0</v>
+      </c>
+      <c r="E28" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8521,16 +8618,16 @@
       <c r="A29" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="B29" s="72">
-        <v>0</v>
-      </c>
-      <c r="C29" s="72">
+      <c r="B29" s="71">
+        <v>0</v>
+      </c>
+      <c r="C29" s="71">
         <v>0.125</v>
       </c>
-      <c r="D29" s="72">
+      <c r="D29" s="71">
         <v>0.159723</v>
       </c>
-      <c r="E29" s="72">
+      <c r="E29" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8538,16 +8635,16 @@
       <c r="A30" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="B30" s="72">
-        <v>0</v>
-      </c>
-      <c r="C30" s="72">
-        <v>0</v>
-      </c>
-      <c r="D30" s="72">
-        <v>0</v>
-      </c>
-      <c r="E30" s="72">
+      <c r="B30" s="71">
+        <v>0</v>
+      </c>
+      <c r="C30" s="71">
+        <v>0</v>
+      </c>
+      <c r="D30" s="71">
+        <v>0</v>
+      </c>
+      <c r="E30" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8555,16 +8652,16 @@
       <c r="A31" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="B31" s="72">
-        <v>0</v>
-      </c>
-      <c r="C31" s="72">
-        <v>0</v>
-      </c>
-      <c r="D31" s="72">
-        <v>0</v>
-      </c>
-      <c r="E31" s="72">
+      <c r="B31" s="71">
+        <v>0</v>
+      </c>
+      <c r="C31" s="71">
+        <v>0</v>
+      </c>
+      <c r="D31" s="71">
+        <v>0</v>
+      </c>
+      <c r="E31" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8572,16 +8669,16 @@
       <c r="A32" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="B32" s="72">
-        <v>0</v>
-      </c>
-      <c r="C32" s="72">
-        <v>0</v>
-      </c>
-      <c r="D32" s="72">
-        <v>0</v>
-      </c>
-      <c r="E32" s="72">
+      <c r="B32" s="71">
+        <v>0</v>
+      </c>
+      <c r="C32" s="71">
+        <v>0</v>
+      </c>
+      <c r="D32" s="71">
+        <v>0</v>
+      </c>
+      <c r="E32" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8589,16 +8686,16 @@
       <c r="A33" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="B33" s="72">
-        <v>0</v>
-      </c>
-      <c r="C33" s="72">
-        <v>0</v>
-      </c>
-      <c r="D33" s="72">
-        <v>0</v>
-      </c>
-      <c r="E33" s="72">
+      <c r="B33" s="71">
+        <v>0</v>
+      </c>
+      <c r="C33" s="71">
+        <v>0</v>
+      </c>
+      <c r="D33" s="71">
+        <v>0</v>
+      </c>
+      <c r="E33" s="71">
         <v>0</v>
       </c>
     </row>
@@ -8606,30 +8703,30 @@
       <c r="A34" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B34" s="72">
-        <v>0</v>
-      </c>
-      <c r="C34" s="72">
-        <v>0</v>
-      </c>
-      <c r="D34" s="72">
-        <v>0</v>
-      </c>
-      <c r="E34" s="72">
+      <c r="B34" s="71">
+        <v>0</v>
+      </c>
+      <c r="C34" s="71">
+        <v>0</v>
+      </c>
+      <c r="D34" s="71">
+        <v>0</v>
+      </c>
+      <c r="E34" s="71">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="B35" s="73">
+      <c r="B35" s="72">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="C35" s="73">
+      <c r="C35" s="72">
         <v>0.875</v>
       </c>
-      <c r="D35" s="73">
+      <c r="D35" s="72">
         <v>0.73472300000000001</v>
       </c>
-      <c r="E35" s="73">
+      <c r="E35" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8653,40 +8750,40 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="73" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="74" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="73" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="75"/>
+      <c r="B5" s="74"/>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="74" t="s">
+      <c r="A6" s="73" t="s">
         <v>144</v>
       </c>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="74" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="73" t="s">
         <v>145</v>
       </c>
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="74" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="74" t="s">
+      <c r="A8" s="73" t="s">
         <v>147</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="74" t="s">
         <v>148</v>
       </c>
     </row>

--- a/Plannings 2026 S14.xlsx
+++ b/Plannings 2026 S14.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{150E33BF-47F0-4B68-8AA0-FBA696D166AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A1E570E-3024-42B6-B1F7-2E6DA6078454}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{150E33BF-47F0-4B68-8AA0-FBA696D166AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43AAB536-26BF-4921-B8A8-A04C20079534}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="152">
   <si>
     <t>Mars-2026</t>
   </si>
@@ -382,9 +382,15 @@
     <t>PUJOL Mathieu</t>
   </si>
   <si>
+    <t>INVEN</t>
+  </si>
+  <si>
     <t>09:45/18:00</t>
   </si>
   <si>
+    <t>07:30/11:30</t>
+  </si>
+  <si>
     <t>17:30/18:45</t>
   </si>
   <si>
@@ -395,6 +401,9 @@
   </si>
   <si>
     <t>EDF-A</t>
+  </si>
+  <si>
+    <t>11:30/17:00</t>
   </si>
   <si>
     <t>18:45/22:45</t>
@@ -620,7 +629,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -941,11 +950,119 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1139,13 +1256,7 @@
     <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1154,7 +1265,52 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1177,8 +1333,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCFFFF"/>
       <color rgb="FFCC99FF"/>
-      <color rgb="FFCCFFFF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -4320,50 +4476,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>71</xdr:row>
@@ -6345,6 +6457,53 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12801600" y="12544425"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="Image 34" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C20438AB-D331-4320-8743-3CB6BED06766}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{965B5492-7230-45E4-ACAF-2849F9724C0E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9601200" y="14068425"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7642,10 +7801,10 @@
       <c r="D60" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="E60" s="68" t="s">
+      <c r="E60" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="F60" s="65" t="s">
+      <c r="F60" s="71" t="s">
         <v>18</v>
       </c>
       <c r="G60" s="27" t="s">
@@ -7664,10 +7823,10 @@
       <c r="D61" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="E61" s="69" t="s">
+      <c r="E61" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="F61" s="67" t="s">
+      <c r="F61" s="72" t="s">
         <v>76</v>
       </c>
       <c r="G61" s="26" t="s">
@@ -7687,7 +7846,7 @@
       <c r="E62" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="F62" s="67" t="s">
+      <c r="F62" s="72" t="s">
         <v>101</v>
       </c>
       <c r="G62" s="25" t="s">
@@ -7707,7 +7866,7 @@
       <c r="E63" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="F63" s="67" t="s">
+      <c r="F63" s="72" t="s">
         <v>101</v>
       </c>
       <c r="G63" s="26" t="s">
@@ -7724,10 +7883,10 @@
       <c r="D64" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E64" s="64" t="s">
+      <c r="E64" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="F64" s="67" t="s">
+      <c r="F64" s="72" t="s">
         <v>101</v>
       </c>
       <c r="G64" s="25" t="s">
@@ -7744,10 +7903,10 @@
       <c r="D65" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="E65" s="66" t="s">
+      <c r="E65" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="F65" s="67" t="s">
+      <c r="F65" s="72" t="s">
         <v>101</v>
       </c>
       <c r="G65" s="26" t="s">
@@ -7765,7 +7924,7 @@
       <c r="E66" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="F66" s="67" t="s">
+      <c r="F66" s="72" t="s">
         <v>101</v>
       </c>
       <c r="G66" s="42" t="s">
@@ -7780,10 +7939,10 @@
         <v>92</v>
       </c>
       <c r="D67" s="31"/>
-      <c r="E67" s="66" t="s">
+      <c r="E67" s="65" t="s">
         <v>109</v>
       </c>
-      <c r="F67" s="67" t="s">
+      <c r="F67" s="72" t="s">
         <v>101</v>
       </c>
       <c r="G67" s="34" t="s">
@@ -7798,10 +7957,10 @@
         <v>21</v>
       </c>
       <c r="D68" s="31"/>
-      <c r="E68" s="66" t="s">
+      <c r="E68" s="65" t="s">
         <v>101</v>
       </c>
-      <c r="F68" s="67" t="s">
+      <c r="F68" s="72" t="s">
         <v>101</v>
       </c>
       <c r="G68" s="34"/>
@@ -7814,10 +7973,10 @@
         <v>111</v>
       </c>
       <c r="D69" s="30"/>
-      <c r="E69" s="66" t="s">
+      <c r="E69" s="65" t="s">
         <v>101</v>
       </c>
-      <c r="F69" s="67" t="s">
+      <c r="F69" s="72" t="s">
         <v>101</v>
       </c>
       <c r="G69" s="41"/>
@@ -7854,114 +8013,122 @@
       <c r="H71" s="13"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="48" t="s">
+      <c r="A72" s="73" t="s">
         <v>113</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8" t="s">
+      <c r="C72" s="74"/>
+      <c r="D72" s="75" t="s">
+        <v>114</v>
+      </c>
+      <c r="E72" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="F72" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="F72" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G72" s="8" t="s">
+      <c r="G72" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="H72" s="9"/>
+      <c r="H72" s="76"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="53"/>
+      <c r="A73" s="77"/>
       <c r="B73" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C73" s="1"/>
-      <c r="D73" s="1" t="s">
-        <v>114</v>
+      <c r="D73" s="67" t="s">
+        <v>116</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H73" s="13"/>
+        <v>119</v>
+      </c>
+      <c r="H73" s="78"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="53"/>
+      <c r="A74" s="77"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
+      <c r="D74" s="64" t="s">
+        <v>21</v>
+      </c>
       <c r="E74" s="20" t="s">
         <v>72</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="H74" s="13"/>
+        <v>120</v>
+      </c>
+      <c r="H74" s="78"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="53"/>
+      <c r="A75" s="77"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
+      <c r="D75" s="65" t="s">
+        <v>121</v>
+      </c>
       <c r="E75" s="21" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="H75" s="13"/>
+        <v>123</v>
+      </c>
+      <c r="H75" s="78"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="53"/>
+      <c r="A76" s="77"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
+      <c r="D76" s="65" t="s">
+        <v>101</v>
+      </c>
       <c r="E76" s="21"/>
       <c r="F76" s="1"/>
       <c r="G76" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H76" s="13"/>
-    </row>
-    <row r="77" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A77" s="49"/>
-      <c r="B77" s="11"/>
-      <c r="C77" s="11"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="23"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="H77" s="12"/>
+      <c r="H76" s="78"/>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="79"/>
+      <c r="B77" s="80"/>
+      <c r="C77" s="80"/>
+      <c r="D77" s="81" t="s">
+        <v>101</v>
+      </c>
+      <c r="E77" s="82"/>
+      <c r="F77" s="80"/>
+      <c r="G77" s="80" t="s">
+        <v>124</v>
+      </c>
+      <c r="H77" s="83"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="B78" s="32" t="s">
+      <c r="A78" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="B78" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-      <c r="G78" s="33" t="s">
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="H78" s="9"/>
+      <c r="H78" s="13"/>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="53"/>
@@ -7997,13 +8164,13 @@
       <c r="E81" s="11"/>
       <c r="F81" s="11"/>
       <c r="G81" s="11" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H81" s="12"/>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="48" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
@@ -8020,7 +8187,7 @@
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
       <c r="D83" s="28" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E83" s="11"/>
       <c r="F83" s="11"/>
@@ -8029,7 +8196,7 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="48" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
@@ -8079,7 +8246,7 @@
     </row>
     <row r="88" spans="1:8" ht="15.75" thickBot="1">
       <c r="A88" s="14" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B88" s="50"/>
       <c r="C88" s="51"/>
@@ -8091,7 +8258,7 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="60" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -8116,16 +8283,16 @@
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="12" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="48" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
@@ -8142,7 +8309,7 @@
       <c r="B92" s="11"/>
       <c r="C92" s="11"/>
       <c r="D92" s="28" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="11"/>
@@ -8204,12 +8371,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="62" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
@@ -8217,7 +8384,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="63" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C5" s="63"/>
       <c r="D5" s="63"/>
@@ -8228,32 +8395,32 @@
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="71">
-        <v>0</v>
-      </c>
-      <c r="C7" s="71">
-        <v>0</v>
-      </c>
-      <c r="D7" s="71">
-        <v>0</v>
-      </c>
-      <c r="E7" s="71">
+      <c r="B7" s="84">
+        <v>0</v>
+      </c>
+      <c r="C7" s="84">
+        <v>0</v>
+      </c>
+      <c r="D7" s="84">
+        <v>0</v>
+      </c>
+      <c r="E7" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8261,16 +8428,16 @@
       <c r="A8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="71">
-        <v>0</v>
-      </c>
-      <c r="C8" s="71">
-        <v>0</v>
-      </c>
-      <c r="D8" s="71">
-        <v>0</v>
-      </c>
-      <c r="E8" s="71">
+      <c r="B8" s="84">
+        <v>0</v>
+      </c>
+      <c r="C8" s="84">
+        <v>0</v>
+      </c>
+      <c r="D8" s="84">
+        <v>0</v>
+      </c>
+      <c r="E8" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8278,16 +8445,16 @@
       <c r="A9" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="71">
-        <v>0</v>
-      </c>
-      <c r="C9" s="71">
+      <c r="B9" s="84">
+        <v>0</v>
+      </c>
+      <c r="C9" s="84">
         <v>4.1667000000000003E-2</v>
       </c>
-      <c r="D9" s="71">
-        <v>0</v>
-      </c>
-      <c r="E9" s="71">
+      <c r="D9" s="84">
+        <v>0</v>
+      </c>
+      <c r="E9" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8295,16 +8462,16 @@
       <c r="A10" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="71">
-        <v>0</v>
-      </c>
-      <c r="C10" s="71">
-        <v>0</v>
-      </c>
-      <c r="D10" s="71">
-        <v>0</v>
-      </c>
-      <c r="E10" s="71">
+      <c r="B10" s="84">
+        <v>0</v>
+      </c>
+      <c r="C10" s="84">
+        <v>0</v>
+      </c>
+      <c r="D10" s="84">
+        <v>0</v>
+      </c>
+      <c r="E10" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8312,16 +8479,16 @@
       <c r="A11" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="71">
-        <v>0</v>
-      </c>
-      <c r="C11" s="71">
-        <v>0</v>
-      </c>
-      <c r="D11" s="71">
-        <v>0</v>
-      </c>
-      <c r="E11" s="71">
+      <c r="B11" s="84">
+        <v>0</v>
+      </c>
+      <c r="C11" s="84">
+        <v>0</v>
+      </c>
+      <c r="D11" s="84">
+        <v>0</v>
+      </c>
+      <c r="E11" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8329,16 +8496,16 @@
       <c r="A12" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="71">
-        <v>0</v>
-      </c>
-      <c r="C12" s="71">
-        <v>0</v>
-      </c>
-      <c r="D12" s="71">
-        <v>0</v>
-      </c>
-      <c r="E12" s="71">
+      <c r="B12" s="84">
+        <v>0</v>
+      </c>
+      <c r="C12" s="84">
+        <v>0</v>
+      </c>
+      <c r="D12" s="84">
+        <v>0</v>
+      </c>
+      <c r="E12" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8346,16 +8513,16 @@
       <c r="A13" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="71">
-        <v>0</v>
-      </c>
-      <c r="C13" s="71">
-        <v>0</v>
-      </c>
-      <c r="D13" s="71">
+      <c r="B13" s="84">
+        <v>0</v>
+      </c>
+      <c r="C13" s="84">
+        <v>0</v>
+      </c>
+      <c r="D13" s="84">
         <v>0.24166699999999999</v>
       </c>
-      <c r="E13" s="71">
+      <c r="E13" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8363,16 +8530,16 @@
       <c r="A14" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="71">
-        <v>0</v>
-      </c>
-      <c r="C14" s="71">
-        <v>0</v>
-      </c>
-      <c r="D14" s="71">
-        <v>0</v>
-      </c>
-      <c r="E14" s="71">
+      <c r="B14" s="84">
+        <v>0</v>
+      </c>
+      <c r="C14" s="84">
+        <v>0</v>
+      </c>
+      <c r="D14" s="84">
+        <v>0</v>
+      </c>
+      <c r="E14" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8380,16 +8547,16 @@
       <c r="A15" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="71">
-        <v>0</v>
-      </c>
-      <c r="C15" s="71">
-        <v>0</v>
-      </c>
-      <c r="D15" s="71">
-        <v>0</v>
-      </c>
-      <c r="E15" s="71">
+      <c r="B15" s="84">
+        <v>0</v>
+      </c>
+      <c r="C15" s="84">
+        <v>0</v>
+      </c>
+      <c r="D15" s="84">
+        <v>0</v>
+      </c>
+      <c r="E15" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8397,16 +8564,16 @@
       <c r="A16" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="71">
+      <c r="B16" s="84">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="C16" s="71">
+      <c r="C16" s="84">
         <v>8.3334000000000005E-2</v>
       </c>
-      <c r="D16" s="71">
-        <v>0</v>
-      </c>
-      <c r="E16" s="71">
+      <c r="D16" s="84">
+        <v>0</v>
+      </c>
+      <c r="E16" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8414,33 +8581,33 @@
       <c r="A17" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="71">
-        <v>0</v>
-      </c>
-      <c r="C17" s="71">
-        <v>0</v>
-      </c>
-      <c r="D17" s="71">
-        <v>0</v>
-      </c>
-      <c r="E17" s="71">
+      <c r="B17" s="84">
+        <v>0</v>
+      </c>
+      <c r="C17" s="84">
+        <v>0</v>
+      </c>
+      <c r="D17" s="84">
+        <v>0</v>
+      </c>
+      <c r="E17" s="84">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="B18" s="71">
-        <v>0</v>
-      </c>
-      <c r="C18" s="71">
-        <v>0</v>
-      </c>
-      <c r="D18" s="71">
-        <v>0</v>
-      </c>
-      <c r="E18" s="71">
+        <v>142</v>
+      </c>
+      <c r="B18" s="84">
+        <v>0</v>
+      </c>
+      <c r="C18" s="84">
+        <v>0</v>
+      </c>
+      <c r="D18" s="84">
+        <v>0</v>
+      </c>
+      <c r="E18" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8448,16 +8615,16 @@
       <c r="A19" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="71">
-        <v>0</v>
-      </c>
-      <c r="C19" s="71">
-        <v>0</v>
-      </c>
-      <c r="D19" s="71">
-        <v>0</v>
-      </c>
-      <c r="E19" s="71">
+      <c r="B19" s="84">
+        <v>0</v>
+      </c>
+      <c r="C19" s="84">
+        <v>0</v>
+      </c>
+      <c r="D19" s="84">
+        <v>0</v>
+      </c>
+      <c r="E19" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8465,16 +8632,16 @@
       <c r="A20" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="B20" s="71">
-        <v>0</v>
-      </c>
-      <c r="C20" s="71">
-        <v>0</v>
-      </c>
-      <c r="D20" s="71">
-        <v>0</v>
-      </c>
-      <c r="E20" s="71">
+      <c r="B20" s="84">
+        <v>0</v>
+      </c>
+      <c r="C20" s="84">
+        <v>0</v>
+      </c>
+      <c r="D20" s="84">
+        <v>0</v>
+      </c>
+      <c r="E20" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8482,16 +8649,16 @@
       <c r="A21" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="71">
-        <v>0</v>
-      </c>
-      <c r="C21" s="71">
-        <v>0</v>
-      </c>
-      <c r="D21" s="71">
-        <v>0</v>
-      </c>
-      <c r="E21" s="71">
+      <c r="B21" s="84">
+        <v>0</v>
+      </c>
+      <c r="C21" s="84">
+        <v>0</v>
+      </c>
+      <c r="D21" s="84">
+        <v>0</v>
+      </c>
+      <c r="E21" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8499,33 +8666,33 @@
       <c r="A22" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B22" s="71">
-        <v>0</v>
-      </c>
-      <c r="C22" s="71">
-        <v>0</v>
-      </c>
-      <c r="D22" s="71">
-        <v>0</v>
-      </c>
-      <c r="E22" s="71">
+      <c r="B22" s="84">
+        <v>0</v>
+      </c>
+      <c r="C22" s="84">
+        <v>0</v>
+      </c>
+      <c r="D22" s="84">
+        <v>0</v>
+      </c>
+      <c r="E22" s="84">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="B23" s="71">
-        <v>0</v>
-      </c>
-      <c r="C23" s="71">
-        <v>0</v>
-      </c>
-      <c r="D23" s="71">
-        <v>0</v>
-      </c>
-      <c r="E23" s="71">
+        <v>143</v>
+      </c>
+      <c r="B23" s="84">
+        <v>0</v>
+      </c>
+      <c r="C23" s="84">
+        <v>0</v>
+      </c>
+      <c r="D23" s="84">
+        <v>0</v>
+      </c>
+      <c r="E23" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8533,16 +8700,16 @@
       <c r="A24" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="71">
-        <v>0</v>
-      </c>
-      <c r="C24" s="71">
-        <v>0</v>
-      </c>
-      <c r="D24" s="71">
+      <c r="B24" s="84">
+        <v>0</v>
+      </c>
+      <c r="C24" s="84">
+        <v>0</v>
+      </c>
+      <c r="D24" s="84">
         <v>0.25</v>
       </c>
-      <c r="E24" s="71">
+      <c r="E24" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8550,16 +8717,16 @@
       <c r="A25" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B25" s="71">
-        <v>0</v>
-      </c>
-      <c r="C25" s="71">
+      <c r="B25" s="84">
+        <v>0</v>
+      </c>
+      <c r="C25" s="84">
         <v>0.45833400000000002</v>
       </c>
-      <c r="D25" s="71">
-        <v>0</v>
-      </c>
-      <c r="E25" s="71">
+      <c r="D25" s="84">
+        <v>0</v>
+      </c>
+      <c r="E25" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8567,16 +8734,16 @@
       <c r="A26" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="71">
-        <v>0</v>
-      </c>
-      <c r="C26" s="71">
+      <c r="B26" s="84">
+        <v>0</v>
+      </c>
+      <c r="C26" s="84">
         <v>0.16666700000000001</v>
       </c>
-      <c r="D26" s="71">
+      <c r="D26" s="84">
         <v>8.3334000000000005E-2</v>
       </c>
-      <c r="E26" s="71">
+      <c r="E26" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8584,16 +8751,16 @@
       <c r="A27" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="B27" s="71">
-        <v>0</v>
-      </c>
-      <c r="C27" s="71">
-        <v>0</v>
-      </c>
-      <c r="D27" s="71">
-        <v>0</v>
-      </c>
-      <c r="E27" s="71">
+      <c r="B27" s="84">
+        <v>0</v>
+      </c>
+      <c r="C27" s="84">
+        <v>0</v>
+      </c>
+      <c r="D27" s="84">
+        <v>0</v>
+      </c>
+      <c r="E27" s="84">
         <v>0</v>
       </c>
     </row>
@@ -8601,132 +8768,132 @@
       <c r="A28" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="B28" s="71">
-        <v>0</v>
-      </c>
-      <c r="C28" s="71">
-        <v>0</v>
-      </c>
-      <c r="D28" s="71">
-        <v>0</v>
-      </c>
-      <c r="E28" s="71">
+      <c r="B28" s="84">
+        <v>0</v>
+      </c>
+      <c r="C28" s="84">
+        <v>0</v>
+      </c>
+      <c r="D28" s="84">
+        <v>0</v>
+      </c>
+      <c r="E28" s="84">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="B29" s="71">
-        <v>0</v>
-      </c>
-      <c r="C29" s="71">
+        <v>125</v>
+      </c>
+      <c r="B29" s="84">
+        <v>0</v>
+      </c>
+      <c r="C29" s="84">
         <v>0.125</v>
       </c>
-      <c r="D29" s="71">
+      <c r="D29" s="84">
         <v>0.159723</v>
       </c>
-      <c r="E29" s="71">
+      <c r="E29" s="84">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="B30" s="71">
-        <v>0</v>
-      </c>
-      <c r="C30" s="71">
-        <v>0</v>
-      </c>
-      <c r="D30" s="71">
-        <v>0</v>
-      </c>
-      <c r="E30" s="71">
+        <v>127</v>
+      </c>
+      <c r="B30" s="84">
+        <v>0</v>
+      </c>
+      <c r="C30" s="84">
+        <v>0</v>
+      </c>
+      <c r="D30" s="84">
+        <v>0</v>
+      </c>
+      <c r="E30" s="84">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="B31" s="71">
-        <v>0</v>
-      </c>
-      <c r="C31" s="71">
-        <v>0</v>
-      </c>
-      <c r="D31" s="71">
-        <v>0</v>
-      </c>
-      <c r="E31" s="71">
+        <v>129</v>
+      </c>
+      <c r="B31" s="84">
+        <v>0</v>
+      </c>
+      <c r="C31" s="84">
+        <v>0</v>
+      </c>
+      <c r="D31" s="84">
+        <v>0</v>
+      </c>
+      <c r="E31" s="84">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="B32" s="71">
-        <v>0</v>
-      </c>
-      <c r="C32" s="71">
-        <v>0</v>
-      </c>
-      <c r="D32" s="71">
-        <v>0</v>
-      </c>
-      <c r="E32" s="71">
+        <v>130</v>
+      </c>
+      <c r="B32" s="84">
+        <v>0</v>
+      </c>
+      <c r="C32" s="84">
+        <v>0</v>
+      </c>
+      <c r="D32" s="84">
+        <v>0</v>
+      </c>
+      <c r="E32" s="84">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="B33" s="71">
-        <v>0</v>
-      </c>
-      <c r="C33" s="71">
-        <v>0</v>
-      </c>
-      <c r="D33" s="71">
-        <v>0</v>
-      </c>
-      <c r="E33" s="71">
+        <v>131</v>
+      </c>
+      <c r="B33" s="84">
+        <v>0</v>
+      </c>
+      <c r="C33" s="84">
+        <v>0</v>
+      </c>
+      <c r="D33" s="84">
+        <v>0</v>
+      </c>
+      <c r="E33" s="84">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="B34" s="71">
-        <v>0</v>
-      </c>
-      <c r="C34" s="71">
-        <v>0</v>
-      </c>
-      <c r="D34" s="71">
-        <v>0</v>
-      </c>
-      <c r="E34" s="71">
+        <v>134</v>
+      </c>
+      <c r="B34" s="84">
+        <v>0</v>
+      </c>
+      <c r="C34" s="84">
+        <v>0</v>
+      </c>
+      <c r="D34" s="84">
+        <v>0</v>
+      </c>
+      <c r="E34" s="84">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="B35" s="72">
+      <c r="B35" s="85">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="C35" s="72">
+      <c r="C35" s="85">
         <v>0.875</v>
       </c>
-      <c r="D35" s="72">
+      <c r="D35" s="85">
         <v>0.73472300000000001</v>
       </c>
-      <c r="E35" s="72">
+      <c r="E35" s="85">
         <v>0</v>
       </c>
     </row>
@@ -8746,45 +8913,45 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="73" t="s">
-        <v>141</v>
-      </c>
-      <c r="B4" s="74" t="s">
-        <v>142</v>
+      <c r="A4" s="86" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="87" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="73" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="74"/>
+      <c r="A5" s="86" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="87"/>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="73" t="s">
-        <v>144</v>
-      </c>
-      <c r="B6" s="74" t="s">
+      <c r="A6" s="86" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="87" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="73" t="s">
-        <v>145</v>
-      </c>
-      <c r="B7" s="74" t="s">
-        <v>146</v>
+      <c r="A7" s="86" t="s">
+        <v>148</v>
+      </c>
+      <c r="B7" s="87" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="73" t="s">
-        <v>147</v>
-      </c>
-      <c r="B8" s="74" t="s">
-        <v>148</v>
+      <c r="A8" s="86" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" s="87" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S14.xlsx
+++ b/Plannings 2026 S14.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{150E33BF-47F0-4B68-8AA0-FBA696D166AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43AAB536-26BF-4921-B8A8-A04C20079534}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{150E33BF-47F0-4B68-8AA0-FBA696D166AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05A385D4-9949-4BBB-BE7E-6087CBA21D57}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="149">
   <si>
     <t>Mars-2026</t>
   </si>
@@ -382,15 +382,9 @@
     <t>PUJOL Mathieu</t>
   </si>
   <si>
-    <t>INVEN</t>
-  </si>
-  <si>
     <t>09:45/18:00</t>
   </si>
   <si>
-    <t>07:30/11:30</t>
-  </si>
-  <si>
     <t>17:30/18:45</t>
   </si>
   <si>
@@ -401,9 +395,6 @@
   </si>
   <si>
     <t>EDF-A</t>
-  </si>
-  <si>
-    <t>11:30/17:00</t>
   </si>
   <si>
     <t>18:45/22:45</t>
@@ -629,7 +620,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -950,119 +941,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1256,7 +1139,13 @@
     <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1269,48 +1158,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1333,8 +1180,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCC99FF"/>
       <color rgb="FFCCFFFF"/>
-      <color rgb="FFCC99FF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -4168,6 +4015,94 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>59</xdr:row>
@@ -4476,6 +4411,50 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>71</xdr:row>
@@ -6269,241 +6248,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6395357" y="11865429"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Image 7" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E683E050-DA9B-4D59-99DE-0B8870E96189}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{054D7FC7-F6A0-4112-ACF7-68D41389B396}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16002000" y="11401425"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Image 13" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBE173F4-AFE1-4F2C-B530-F2826F8AD0D5}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E683E050-DA9B-4D59-99DE-0B8870E96189}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12801600" y="12544425"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="Image 32" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AE168D3-72BF-4E47-8438-FA289729665B}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{EBE173F4-AFE1-4F2C-B530-F2826F8AD0D5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12801600" y="12163425"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Image 13" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{965B5492-7230-45E4-ACAF-2849F9724C0E}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8AE168D3-72BF-4E47-8438-FA289729665B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12801600" y="12544425"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Image 34" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C20438AB-D331-4320-8743-3CB6BED06766}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{965B5492-7230-45E4-ACAF-2849F9724C0E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9601200" y="14068425"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7801,10 +7545,10 @@
       <c r="D60" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="E60" s="66" t="s">
+      <c r="E60" s="68" t="s">
         <v>95</v>
       </c>
-      <c r="F60" s="71" t="s">
+      <c r="F60" s="65" t="s">
         <v>18</v>
       </c>
       <c r="G60" s="27" t="s">
@@ -7823,10 +7567,10 @@
       <c r="D61" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="E61" s="67" t="s">
+      <c r="E61" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="F61" s="72" t="s">
+      <c r="F61" s="67" t="s">
         <v>76</v>
       </c>
       <c r="G61" s="26" t="s">
@@ -7843,10 +7587,10 @@
       <c r="D62" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E62" s="64" t="s">
+      <c r="E62" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="F62" s="72" t="s">
+      <c r="F62" s="67" t="s">
         <v>101</v>
       </c>
       <c r="G62" s="25" t="s">
@@ -7863,10 +7607,10 @@
       <c r="D63" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E63" s="70" t="s">
+      <c r="E63" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="F63" s="72" t="s">
+      <c r="F63" s="67" t="s">
         <v>101</v>
       </c>
       <c r="G63" s="26" t="s">
@@ -7883,10 +7627,10 @@
       <c r="D64" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E64" s="68" t="s">
+      <c r="E64" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="F64" s="72" t="s">
+      <c r="F64" s="67" t="s">
         <v>101</v>
       </c>
       <c r="G64" s="25" t="s">
@@ -7903,10 +7647,10 @@
       <c r="D65" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="E65" s="69" t="s">
+      <c r="E65" s="66" t="s">
         <v>108</v>
       </c>
-      <c r="F65" s="72" t="s">
+      <c r="F65" s="67" t="s">
         <v>101</v>
       </c>
       <c r="G65" s="26" t="s">
@@ -7924,7 +7668,7 @@
       <c r="E66" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="F66" s="72" t="s">
+      <c r="F66" s="67" t="s">
         <v>101</v>
       </c>
       <c r="G66" s="42" t="s">
@@ -7939,10 +7683,10 @@
         <v>92</v>
       </c>
       <c r="D67" s="31"/>
-      <c r="E67" s="65" t="s">
+      <c r="E67" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="F67" s="72" t="s">
+      <c r="F67" s="67" t="s">
         <v>101</v>
       </c>
       <c r="G67" s="34" t="s">
@@ -7957,10 +7701,10 @@
         <v>21</v>
       </c>
       <c r="D68" s="31"/>
-      <c r="E68" s="65" t="s">
+      <c r="E68" s="66" t="s">
         <v>101</v>
       </c>
-      <c r="F68" s="72" t="s">
+      <c r="F68" s="67" t="s">
         <v>101</v>
       </c>
       <c r="G68" s="34"/>
@@ -7973,10 +7717,10 @@
         <v>111</v>
       </c>
       <c r="D69" s="30"/>
-      <c r="E69" s="65" t="s">
+      <c r="E69" s="66" t="s">
         <v>101</v>
       </c>
-      <c r="F69" s="72" t="s">
+      <c r="F69" s="67" t="s">
         <v>101</v>
       </c>
       <c r="G69" s="41"/>
@@ -8013,122 +7757,114 @@
       <c r="H71" s="13"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="73" t="s">
+      <c r="A72" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="B72" s="74" t="s">
+      <c r="B72" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C72" s="74"/>
-      <c r="D72" s="75" t="s">
+      <c r="C72" s="8"/>
+      <c r="D72" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H72" s="9"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="53"/>
+      <c r="B73" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E72" s="74" t="s">
-        <v>21</v>
-      </c>
-      <c r="F72" s="74" t="s">
-        <v>21</v>
-      </c>
-      <c r="G72" s="74" t="s">
-        <v>59</v>
-      </c>
-      <c r="H72" s="76"/>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="77"/>
-      <c r="B73" s="1" t="s">
+      <c r="C73" s="1"/>
+      <c r="D73" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C73" s="1"/>
-      <c r="D73" s="67" t="s">
+      <c r="F73" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="G73" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F73" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H73" s="78"/>
+      <c r="H73" s="13"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="77"/>
+      <c r="A74" s="53"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
-      <c r="D74" s="64" t="s">
-        <v>21</v>
-      </c>
+      <c r="D74" s="1"/>
       <c r="E74" s="20" t="s">
         <v>72</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="H74" s="78"/>
+        <v>118</v>
+      </c>
+      <c r="H74" s="13"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="77"/>
+      <c r="A75" s="53"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
-      <c r="D75" s="65" t="s">
-        <v>121</v>
-      </c>
+      <c r="D75" s="1"/>
       <c r="E75" s="21" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="H75" s="78"/>
+        <v>120</v>
+      </c>
+      <c r="H75" s="13"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="77"/>
+      <c r="A76" s="53"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
-      <c r="D76" s="65" t="s">
-        <v>101</v>
-      </c>
+      <c r="D76" s="1"/>
       <c r="E76" s="21"/>
       <c r="F76" s="1"/>
       <c r="G76" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H76" s="78"/>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="79"/>
-      <c r="B77" s="80"/>
-      <c r="C77" s="80"/>
-      <c r="D77" s="81" t="s">
-        <v>101</v>
-      </c>
-      <c r="E77" s="82"/>
-      <c r="F77" s="80"/>
-      <c r="G77" s="80" t="s">
-        <v>124</v>
-      </c>
-      <c r="H77" s="83"/>
+      <c r="H76" s="13"/>
+    </row>
+    <row r="77" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A77" s="49"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="23"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="H77" s="12"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="B78" s="31" t="s">
+      <c r="A78" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="B78" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="34" t="s">
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="H78" s="13"/>
+      <c r="H78" s="9"/>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="53"/>
@@ -8164,13 +7900,13 @@
       <c r="E81" s="11"/>
       <c r="F81" s="11"/>
       <c r="G81" s="11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H81" s="12"/>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="48" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
@@ -8187,7 +7923,7 @@
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
       <c r="D83" s="28" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E83" s="11"/>
       <c r="F83" s="11"/>
@@ -8196,7 +7932,7 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="48" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
@@ -8246,7 +7982,7 @@
     </row>
     <row r="88" spans="1:8" ht="15.75" thickBot="1">
       <c r="A88" s="14" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B88" s="50"/>
       <c r="C88" s="51"/>
@@ -8258,7 +7994,7 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="60" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -8283,16 +8019,16 @@
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G90" s="11"/>
       <c r="H90" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="48" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
@@ -8309,7 +8045,7 @@
       <c r="B92" s="11"/>
       <c r="C92" s="11"/>
       <c r="D92" s="28" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="11"/>
@@ -8371,12 +8107,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="62" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
@@ -8384,7 +8120,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="63" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C5" s="63"/>
       <c r="D5" s="63"/>
@@ -8395,32 +8131,32 @@
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="84">
-        <v>0</v>
-      </c>
-      <c r="C7" s="84">
-        <v>0</v>
-      </c>
-      <c r="D7" s="84">
-        <v>0</v>
-      </c>
-      <c r="E7" s="84">
+      <c r="B7" s="72">
+        <v>0</v>
+      </c>
+      <c r="C7" s="72">
+        <v>0</v>
+      </c>
+      <c r="D7" s="72">
+        <v>0</v>
+      </c>
+      <c r="E7" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8428,16 +8164,16 @@
       <c r="A8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="84">
-        <v>0</v>
-      </c>
-      <c r="C8" s="84">
-        <v>0</v>
-      </c>
-      <c r="D8" s="84">
-        <v>0</v>
-      </c>
-      <c r="E8" s="84">
+      <c r="B8" s="72">
+        <v>0</v>
+      </c>
+      <c r="C8" s="72">
+        <v>0</v>
+      </c>
+      <c r="D8" s="72">
+        <v>0</v>
+      </c>
+      <c r="E8" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8445,16 +8181,16 @@
       <c r="A9" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="84">
-        <v>0</v>
-      </c>
-      <c r="C9" s="84">
+      <c r="B9" s="72">
+        <v>0</v>
+      </c>
+      <c r="C9" s="72">
         <v>4.1667000000000003E-2</v>
       </c>
-      <c r="D9" s="84">
-        <v>0</v>
-      </c>
-      <c r="E9" s="84">
+      <c r="D9" s="72">
+        <v>0</v>
+      </c>
+      <c r="E9" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8462,16 +8198,16 @@
       <c r="A10" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="84">
-        <v>0</v>
-      </c>
-      <c r="C10" s="84">
-        <v>0</v>
-      </c>
-      <c r="D10" s="84">
-        <v>0</v>
-      </c>
-      <c r="E10" s="84">
+      <c r="B10" s="72">
+        <v>0</v>
+      </c>
+      <c r="C10" s="72">
+        <v>0</v>
+      </c>
+      <c r="D10" s="72">
+        <v>0</v>
+      </c>
+      <c r="E10" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8479,16 +8215,16 @@
       <c r="A11" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="84">
-        <v>0</v>
-      </c>
-      <c r="C11" s="84">
-        <v>0</v>
-      </c>
-      <c r="D11" s="84">
-        <v>0</v>
-      </c>
-      <c r="E11" s="84">
+      <c r="B11" s="72">
+        <v>0</v>
+      </c>
+      <c r="C11" s="72">
+        <v>0</v>
+      </c>
+      <c r="D11" s="72">
+        <v>0</v>
+      </c>
+      <c r="E11" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8496,16 +8232,16 @@
       <c r="A12" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="84">
-        <v>0</v>
-      </c>
-      <c r="C12" s="84">
-        <v>0</v>
-      </c>
-      <c r="D12" s="84">
-        <v>0</v>
-      </c>
-      <c r="E12" s="84">
+      <c r="B12" s="72">
+        <v>0</v>
+      </c>
+      <c r="C12" s="72">
+        <v>0</v>
+      </c>
+      <c r="D12" s="72">
+        <v>0</v>
+      </c>
+      <c r="E12" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8513,16 +8249,16 @@
       <c r="A13" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="84">
-        <v>0</v>
-      </c>
-      <c r="C13" s="84">
-        <v>0</v>
-      </c>
-      <c r="D13" s="84">
+      <c r="B13" s="72">
+        <v>0</v>
+      </c>
+      <c r="C13" s="72">
+        <v>0</v>
+      </c>
+      <c r="D13" s="72">
         <v>0.24166699999999999</v>
       </c>
-      <c r="E13" s="84">
+      <c r="E13" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8530,16 +8266,16 @@
       <c r="A14" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="84">
-        <v>0</v>
-      </c>
-      <c r="C14" s="84">
-        <v>0</v>
-      </c>
-      <c r="D14" s="84">
-        <v>0</v>
-      </c>
-      <c r="E14" s="84">
+      <c r="B14" s="72">
+        <v>0</v>
+      </c>
+      <c r="C14" s="72">
+        <v>0</v>
+      </c>
+      <c r="D14" s="72">
+        <v>0</v>
+      </c>
+      <c r="E14" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8547,16 +8283,16 @@
       <c r="A15" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="84">
-        <v>0</v>
-      </c>
-      <c r="C15" s="84">
-        <v>0</v>
-      </c>
-      <c r="D15" s="84">
-        <v>0</v>
-      </c>
-      <c r="E15" s="84">
+      <c r="B15" s="72">
+        <v>0</v>
+      </c>
+      <c r="C15" s="72">
+        <v>0</v>
+      </c>
+      <c r="D15" s="72">
+        <v>0</v>
+      </c>
+      <c r="E15" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8564,16 +8300,16 @@
       <c r="A16" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="84">
+      <c r="B16" s="72">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="C16" s="84">
+      <c r="C16" s="72">
         <v>8.3334000000000005E-2</v>
       </c>
-      <c r="D16" s="84">
-        <v>0</v>
-      </c>
-      <c r="E16" s="84">
+      <c r="D16" s="72">
+        <v>0</v>
+      </c>
+      <c r="E16" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8581,33 +8317,33 @@
       <c r="A17" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="84">
-        <v>0</v>
-      </c>
-      <c r="C17" s="84">
-        <v>0</v>
-      </c>
-      <c r="D17" s="84">
-        <v>0</v>
-      </c>
-      <c r="E17" s="84">
+      <c r="B17" s="72">
+        <v>0</v>
+      </c>
+      <c r="C17" s="72">
+        <v>0</v>
+      </c>
+      <c r="D17" s="72">
+        <v>0</v>
+      </c>
+      <c r="E17" s="72">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="B18" s="84">
-        <v>0</v>
-      </c>
-      <c r="C18" s="84">
-        <v>0</v>
-      </c>
-      <c r="D18" s="84">
-        <v>0</v>
-      </c>
-      <c r="E18" s="84">
+        <v>139</v>
+      </c>
+      <c r="B18" s="72">
+        <v>0</v>
+      </c>
+      <c r="C18" s="72">
+        <v>0</v>
+      </c>
+      <c r="D18" s="72">
+        <v>0</v>
+      </c>
+      <c r="E18" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8615,16 +8351,16 @@
       <c r="A19" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="84">
-        <v>0</v>
-      </c>
-      <c r="C19" s="84">
-        <v>0</v>
-      </c>
-      <c r="D19" s="84">
-        <v>0</v>
-      </c>
-      <c r="E19" s="84">
+      <c r="B19" s="72">
+        <v>0</v>
+      </c>
+      <c r="C19" s="72">
+        <v>0</v>
+      </c>
+      <c r="D19" s="72">
+        <v>0</v>
+      </c>
+      <c r="E19" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8632,16 +8368,16 @@
       <c r="A20" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="B20" s="84">
-        <v>0</v>
-      </c>
-      <c r="C20" s="84">
-        <v>0</v>
-      </c>
-      <c r="D20" s="84">
-        <v>0</v>
-      </c>
-      <c r="E20" s="84">
+      <c r="B20" s="72">
+        <v>0</v>
+      </c>
+      <c r="C20" s="72">
+        <v>0</v>
+      </c>
+      <c r="D20" s="72">
+        <v>0</v>
+      </c>
+      <c r="E20" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8649,16 +8385,16 @@
       <c r="A21" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="84">
-        <v>0</v>
-      </c>
-      <c r="C21" s="84">
-        <v>0</v>
-      </c>
-      <c r="D21" s="84">
-        <v>0</v>
-      </c>
-      <c r="E21" s="84">
+      <c r="B21" s="72">
+        <v>0</v>
+      </c>
+      <c r="C21" s="72">
+        <v>0</v>
+      </c>
+      <c r="D21" s="72">
+        <v>0</v>
+      </c>
+      <c r="E21" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8666,33 +8402,33 @@
       <c r="A22" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B22" s="84">
-        <v>0</v>
-      </c>
-      <c r="C22" s="84">
-        <v>0</v>
-      </c>
-      <c r="D22" s="84">
-        <v>0</v>
-      </c>
-      <c r="E22" s="84">
+      <c r="B22" s="72">
+        <v>0</v>
+      </c>
+      <c r="C22" s="72">
+        <v>0</v>
+      </c>
+      <c r="D22" s="72">
+        <v>0</v>
+      </c>
+      <c r="E22" s="72">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="B23" s="84">
-        <v>0</v>
-      </c>
-      <c r="C23" s="84">
-        <v>0</v>
-      </c>
-      <c r="D23" s="84">
-        <v>0</v>
-      </c>
-      <c r="E23" s="84">
+        <v>140</v>
+      </c>
+      <c r="B23" s="72">
+        <v>0</v>
+      </c>
+      <c r="C23" s="72">
+        <v>0</v>
+      </c>
+      <c r="D23" s="72">
+        <v>0</v>
+      </c>
+      <c r="E23" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8700,16 +8436,16 @@
       <c r="A24" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="84">
-        <v>0</v>
-      </c>
-      <c r="C24" s="84">
-        <v>0</v>
-      </c>
-      <c r="D24" s="84">
+      <c r="B24" s="72">
+        <v>0</v>
+      </c>
+      <c r="C24" s="72">
+        <v>0</v>
+      </c>
+      <c r="D24" s="72">
         <v>0.25</v>
       </c>
-      <c r="E24" s="84">
+      <c r="E24" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8717,16 +8453,16 @@
       <c r="A25" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B25" s="84">
-        <v>0</v>
-      </c>
-      <c r="C25" s="84">
+      <c r="B25" s="72">
+        <v>0</v>
+      </c>
+      <c r="C25" s="72">
         <v>0.45833400000000002</v>
       </c>
-      <c r="D25" s="84">
-        <v>0</v>
-      </c>
-      <c r="E25" s="84">
+      <c r="D25" s="72">
+        <v>0</v>
+      </c>
+      <c r="E25" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8734,16 +8470,16 @@
       <c r="A26" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="84">
-        <v>0</v>
-      </c>
-      <c r="C26" s="84">
+      <c r="B26" s="72">
+        <v>0</v>
+      </c>
+      <c r="C26" s="72">
         <v>0.16666700000000001</v>
       </c>
-      <c r="D26" s="84">
+      <c r="D26" s="72">
         <v>8.3334000000000005E-2</v>
       </c>
-      <c r="E26" s="84">
+      <c r="E26" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8751,16 +8487,16 @@
       <c r="A27" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="B27" s="84">
-        <v>0</v>
-      </c>
-      <c r="C27" s="84">
-        <v>0</v>
-      </c>
-      <c r="D27" s="84">
-        <v>0</v>
-      </c>
-      <c r="E27" s="84">
+      <c r="B27" s="72">
+        <v>0</v>
+      </c>
+      <c r="C27" s="72">
+        <v>0</v>
+      </c>
+      <c r="D27" s="72">
+        <v>0</v>
+      </c>
+      <c r="E27" s="72">
         <v>0</v>
       </c>
     </row>
@@ -8768,132 +8504,132 @@
       <c r="A28" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="B28" s="84">
-        <v>0</v>
-      </c>
-      <c r="C28" s="84">
-        <v>0</v>
-      </c>
-      <c r="D28" s="84">
-        <v>0</v>
-      </c>
-      <c r="E28" s="84">
+      <c r="B28" s="72">
+        <v>0</v>
+      </c>
+      <c r="C28" s="72">
+        <v>0</v>
+      </c>
+      <c r="D28" s="72">
+        <v>0</v>
+      </c>
+      <c r="E28" s="72">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="84">
-        <v>0</v>
-      </c>
-      <c r="C29" s="84">
+        <v>122</v>
+      </c>
+      <c r="B29" s="72">
+        <v>0</v>
+      </c>
+      <c r="C29" s="72">
         <v>0.125</v>
       </c>
-      <c r="D29" s="84">
+      <c r="D29" s="72">
         <v>0.159723</v>
       </c>
-      <c r="E29" s="84">
+      <c r="E29" s="72">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="B30" s="84">
-        <v>0</v>
-      </c>
-      <c r="C30" s="84">
-        <v>0</v>
-      </c>
-      <c r="D30" s="84">
-        <v>0</v>
-      </c>
-      <c r="E30" s="84">
+        <v>124</v>
+      </c>
+      <c r="B30" s="72">
+        <v>0</v>
+      </c>
+      <c r="C30" s="72">
+        <v>0</v>
+      </c>
+      <c r="D30" s="72">
+        <v>0</v>
+      </c>
+      <c r="E30" s="72">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="B31" s="84">
-        <v>0</v>
-      </c>
-      <c r="C31" s="84">
-        <v>0</v>
-      </c>
-      <c r="D31" s="84">
-        <v>0</v>
-      </c>
-      <c r="E31" s="84">
+        <v>126</v>
+      </c>
+      <c r="B31" s="72">
+        <v>0</v>
+      </c>
+      <c r="C31" s="72">
+        <v>0</v>
+      </c>
+      <c r="D31" s="72">
+        <v>0</v>
+      </c>
+      <c r="E31" s="72">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="B32" s="84">
-        <v>0</v>
-      </c>
-      <c r="C32" s="84">
-        <v>0</v>
-      </c>
-      <c r="D32" s="84">
-        <v>0</v>
-      </c>
-      <c r="E32" s="84">
+        <v>127</v>
+      </c>
+      <c r="B32" s="72">
+        <v>0</v>
+      </c>
+      <c r="C32" s="72">
+        <v>0</v>
+      </c>
+      <c r="D32" s="72">
+        <v>0</v>
+      </c>
+      <c r="E32" s="72">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="B33" s="84">
-        <v>0</v>
-      </c>
-      <c r="C33" s="84">
-        <v>0</v>
-      </c>
-      <c r="D33" s="84">
-        <v>0</v>
-      </c>
-      <c r="E33" s="84">
+        <v>128</v>
+      </c>
+      <c r="B33" s="72">
+        <v>0</v>
+      </c>
+      <c r="C33" s="72">
+        <v>0</v>
+      </c>
+      <c r="D33" s="72">
+        <v>0</v>
+      </c>
+      <c r="E33" s="72">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="B34" s="84">
-        <v>0</v>
-      </c>
-      <c r="C34" s="84">
-        <v>0</v>
-      </c>
-      <c r="D34" s="84">
-        <v>0</v>
-      </c>
-      <c r="E34" s="84">
+        <v>131</v>
+      </c>
+      <c r="B34" s="72">
+        <v>0</v>
+      </c>
+      <c r="C34" s="72">
+        <v>0</v>
+      </c>
+      <c r="D34" s="72">
+        <v>0</v>
+      </c>
+      <c r="E34" s="72">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="B35" s="85">
+      <c r="B35" s="73">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="C35" s="85">
+      <c r="C35" s="73">
         <v>0.875</v>
       </c>
-      <c r="D35" s="85">
+      <c r="D35" s="73">
         <v>0.73472300000000001</v>
       </c>
-      <c r="E35" s="85">
+      <c r="E35" s="73">
         <v>0</v>
       </c>
     </row>
@@ -8913,45 +8649,45 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="86" t="s">
+      <c r="A4" s="74" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" s="75" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="74" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="75"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="74" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="87" t="s">
+      <c r="B6" s="75" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="74" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="86" t="s">
+      <c r="B7" s="75" t="s">
         <v>146</v>
       </c>
-      <c r="B5" s="87"/>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="86" t="s">
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="74" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="87" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="86" t="s">
+      <c r="B8" s="75" t="s">
         <v>148</v>
-      </c>
-      <c r="B7" s="87" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="86" t="s">
-        <v>150</v>
-      </c>
-      <c r="B8" s="87" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S14.xlsx
+++ b/Plannings 2026 S14.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{150E33BF-47F0-4B68-8AA0-FBA696D166AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43AAB536-26BF-4921-B8A8-A04C20079534}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{150E33BF-47F0-4B68-8AA0-FBA696D166AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E34CF0FB-B08D-48F5-A778-D31CC4122B8E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="154">
   <si>
     <t>Mars-2026</t>
   </si>
@@ -169,6 +169,9 @@
     <t>11:30/14:30</t>
   </si>
   <si>
+    <t>09:00/16:15</t>
+  </si>
+  <si>
     <t>16:00/22:00</t>
   </si>
   <si>
@@ -253,33 +256,39 @@
     <t>COMMD</t>
   </si>
   <si>
+    <t>INVEN</t>
+  </si>
+  <si>
+    <t>EV-LO</t>
+  </si>
+  <si>
+    <t>16:15/17:15</t>
+  </si>
+  <si>
+    <t>08:30/11:00</t>
+  </si>
+  <si>
+    <t>18:30/23:30</t>
+  </si>
+  <si>
+    <t>17:15/19:15</t>
+  </si>
+  <si>
     <t>EDF-B</t>
   </si>
   <si>
-    <t>EV-LO</t>
-  </si>
-  <si>
-    <t>16:15/17:15</t>
-  </si>
-  <si>
     <t>14:15/15:45</t>
   </si>
   <si>
-    <t>18:30/23:30</t>
-  </si>
-  <si>
-    <t>17:15/19:15</t>
+    <t>19:15/00:30+</t>
+  </si>
+  <si>
+    <t>19:15/24:00</t>
   </si>
   <si>
     <t>15:45/17:15</t>
   </si>
   <si>
-    <t>19:15/00:30+</t>
-  </si>
-  <si>
-    <t>19:15/24:00</t>
-  </si>
-  <si>
     <t>17:15/18:45</t>
   </si>
   <si>
@@ -380,9 +389,6 @@
   </si>
   <si>
     <t>PUJOL Mathieu</t>
-  </si>
-  <si>
-    <t>INVEN</t>
   </si>
   <si>
     <t>09:45/18:00</t>
@@ -1062,7 +1068,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1202,57 +1208,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1271,13 +1226,76 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1313,18 +1331,8 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3334,13 +3342,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3378,13 +3386,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3422,13 +3430,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3466,13 +3474,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3510,13 +3518,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3554,13 +3562,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3598,13 +3606,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3642,13 +3650,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3686,13 +3694,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3730,13 +3738,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3774,13 +3782,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3818,13 +3826,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3862,2433 +3870,2433 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>61</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E336BB2D-9E6B-47B9-BE5E-FFE8C1BB1112}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="6105525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6622D570-B9A8-4D55-BB7D-59FF206FA5DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="6486525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A72682A-4003-4AD9-92D2-66FFD05512D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="6867525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E455B04-0B57-4353-9A4A-29E00C6CFD34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="6105525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21309003-2EB5-43C5-AE11-9FE11F8AABEB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="6486525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{601E8654-CA14-40AA-9235-F816679D7AEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="6867525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0043B4C8-3617-48BF-932C-3A7E85E4AA1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="6486525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53641B0D-E6A1-4342-BD6D-1700BCC5A3EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="6105525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45020C9B-22C4-40D0-B2E3-27CBFEFEDA40}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="6486525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0933B496-0D4A-45FE-B385-61B5C9E2751A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="6867525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F3F8387-5776-46BC-A0AE-BEC530736891}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="7248525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D985268F-5094-43E3-BB46-806A6647F231}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3657600" y="6105525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{219D8BC5-7AC6-4839-BF80-8F352C912B3B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7960179" y="4871357"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1145537A-5613-4C97-AEAD-4E8C568A8320}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7960179" y="4871357"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{938346EC-4D64-469E-8E17-F994EEA43509}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6395357" y="11674929"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F3D6B16-D338-46BD-AF0B-90221FD57753}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6395357" y="2721429"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9797F6C7-5EE5-48DF-B225-068CC6FBAFEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6BC8F89-9F7F-44F5-A10A-8838A3FB2525}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A720C05B-FE82-4CFB-B4CE-1DB48AD6CD1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="4962525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61F8412D-29DD-4A64-9212-9F359FCD979B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01A479F5-06CB-4D1D-983D-7C15D096051B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2438400" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6C3EBB1-996F-4483-8D04-33980E6B34E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3048000" y="4581525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="123" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F515ACB-C59F-4BD4-968A-FA5E5D40D45C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9593036" y="4871357"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="124" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E44C59AC-4363-4F01-A01D-A57BCD98DD59}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6395357" y="11484429"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="125" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{054D7FC7-F6A0-4112-ACF7-68D41389B396}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6395357" y="11865429"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E336BB2D-9E6B-47B9-BE5E-FFE8C1BB1112}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="6105525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6622D570-B9A8-4D55-BB7D-59FF206FA5DA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="6486525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A72682A-4003-4AD9-92D2-66FFD05512D0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="6867525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E455B04-0B57-4353-9A4A-29E00C6CFD34}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="6105525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21309003-2EB5-43C5-AE11-9FE11F8AABEB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="6486525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{601E8654-CA14-40AA-9235-F816679D7AEC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="6867525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0043B4C8-3617-48BF-932C-3A7E85E4AA1A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="6486525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53641B0D-E6A1-4342-BD6D-1700BCC5A3EE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="6105525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45020C9B-22C4-40D0-B2E3-27CBFEFEDA40}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="6486525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0933B496-0D4A-45FE-B385-61B5C9E2751A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="6867525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F3F8387-5776-46BC-A0AE-BEC530736891}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="7248525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D985268F-5094-43E3-BB46-806A6647F231}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3657600" y="6105525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{219D8BC5-7AC6-4839-BF80-8F352C912B3B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7960179" y="4871357"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1145537A-5613-4C97-AEAD-4E8C568A8320}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7960179" y="4871357"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{938346EC-4D64-469E-8E17-F994EEA43509}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6395357" y="11674929"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F3D6B16-D338-46BD-AF0B-90221FD57753}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6395357" y="2721429"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9797F6C7-5EE5-48DF-B225-068CC6FBAFEC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="609600" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6BC8F89-9F7F-44F5-A10A-8838A3FB2525}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A720C05B-FE82-4CFB-B4CE-1DB48AD6CD1C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1219200" y="4962525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61F8412D-29DD-4A64-9212-9F359FCD979B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01A479F5-06CB-4D1D-983D-7C15D096051B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2438400" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6C3EBB1-996F-4483-8D04-33980E6B34E0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3048000" y="4581525"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="123" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F515ACB-C59F-4BD4-968A-FA5E5D40D45C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9593036" y="4871357"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="124" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E44C59AC-4363-4F01-A01D-A57BCD98DD59}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6395357" y="11484429"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="125" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{054D7FC7-F6A0-4112-ACF7-68D41389B396}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6395357" y="11865429"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>59</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6329,13 +6337,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6376,13 +6384,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6423,13 +6431,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6470,18 +6478,18 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Image 34" descr="Picture">
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Picture 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C20438AB-D331-4320-8743-3CB6BED06766}"/>
@@ -6504,6 +6512,194 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9601200" y="14068425"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DD17F3C-09AA-49E4-B356-745BF34E0C6F}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C20438AB-D331-4320-8743-3CB6BED06766}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9601200" y="6762750"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6D078EF-9CD7-44C9-8CF0-D0FCE9493419}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{7DD17F3C-09AA-49E4-B356-745BF34E0C6F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9601200" y="7143750"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A299507B-D066-4FF1-AFE9-F6A5C9793E13}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{D6D078EF-9CD7-44C9-8CF0-D0FCE9493419}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9601200" y="7524750"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD1A6363-D645-48A4-8E40-55943C34C084}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A299507B-D066-4FF1-AFE9-F6A5C9793E13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9601200" y="7905750"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6885,35 +7081,35 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="48" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="B1" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47" t="s">
+      <c r="B1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
     </row>
     <row r="3" spans="1:8">
       <c r="B3" s="5" t="s">
@@ -6965,7 +7161,7 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="60" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="7"/>
@@ -6979,7 +7175,7 @@
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A6" s="49"/>
+      <c r="A6" s="61"/>
       <c r="B6" s="10"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -6991,7 +7187,7 @@
       <c r="H6" s="12"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="60" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="8"/>
@@ -7005,7 +7201,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A8" s="49"/>
+      <c r="A8" s="61"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
@@ -7017,7 +7213,7 @@
       <c r="H8" s="12"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="60" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -7039,7 +7235,7 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="53"/>
+      <c r="A10" s="69"/>
       <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
@@ -7059,7 +7255,7 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="53"/>
+      <c r="A11" s="69"/>
       <c r="B11" s="29" t="s">
         <v>30</v>
       </c>
@@ -7075,7 +7271,7 @@
       <c r="H11" s="13"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="53"/>
+      <c r="A12" s="69"/>
       <c r="B12" s="31" t="s">
         <v>31</v>
       </c>
@@ -7091,7 +7287,7 @@
       <c r="H12" s="13"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="53"/>
+      <c r="A13" s="69"/>
       <c r="B13" s="29" t="s">
         <v>34</v>
       </c>
@@ -7105,7 +7301,7 @@
       <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A14" s="49"/>
+      <c r="A14" s="61"/>
       <c r="B14" s="30" t="s">
         <v>35</v>
       </c>
@@ -7119,7 +7315,7 @@
       <c r="H14" s="12"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="60" t="s">
         <v>37</v>
       </c>
       <c r="B15" s="8"/>
@@ -7135,7 +7331,7 @@
       <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A16" s="49"/>
+      <c r="A16" s="61"/>
       <c r="B16" s="11"/>
       <c r="C16" s="11" t="s">
         <v>38</v>
@@ -7152,16 +7348,16 @@
       <c r="A17" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="52"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="65"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="48" t="s">
+      <c r="A18" s="60" t="s">
         <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -7183,7 +7379,7 @@
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="54"/>
+      <c r="A19" s="74"/>
       <c r="B19" s="1" t="s">
         <v>41</v>
       </c>
@@ -7191,19 +7387,19 @@
         <v>42</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="54"/>
+      <c r="A20" s="74"/>
       <c r="B20" s="1"/>
       <c r="C20" s="2" t="s">
         <v>21</v>
@@ -7215,10 +7411,10 @@
       <c r="H20" s="1"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A21" s="49"/>
+      <c r="A21" s="61"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -7227,8 +7423,8 @@
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="48" t="s">
-        <v>45</v>
+      <c r="A22" s="60" t="s">
+        <v>46</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8" t="s">
@@ -7247,25 +7443,25 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="53"/>
+      <c r="A23" s="69"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="53"/>
+      <c r="A24" s="69"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -7279,160 +7475,160 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A25" s="49"/>
+      <c r="A25" s="61"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="55" t="s">
-        <v>52</v>
+      <c r="A26" s="72" t="s">
+        <v>53</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="40" t="s">
         <v>54</v>
-      </c>
-      <c r="E26" s="40" t="s">
-        <v>53</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H26" s="1"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="55"/>
+      <c r="A27" s="72"/>
       <c r="B27" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="39" t="s">
         <v>57</v>
-      </c>
-      <c r="E27" s="39" t="s">
-        <v>56</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H27" s="1"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="55"/>
+      <c r="A28" s="72"/>
       <c r="B28" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="40" t="s">
-        <v>53</v>
-      </c>
       <c r="E28" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="21"/>
       <c r="H28" s="1"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="55"/>
+      <c r="A29" s="72"/>
       <c r="B29" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D29" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="21"/>
       <c r="H29" s="1"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="55"/>
+      <c r="A30" s="72"/>
       <c r="B30" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E30" s="40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="21"/>
       <c r="H30" s="1"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="55"/>
+      <c r="A31" s="72"/>
       <c r="B31" s="21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C31" s="39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E31" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="21"/>
       <c r="H31" s="1"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="55"/>
+      <c r="A32" s="72"/>
       <c r="B32" s="21"/>
       <c r="C32" s="39"/>
       <c r="D32" s="26"/>
       <c r="E32" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="21"/>
       <c r="H32" s="1"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A33" s="55"/>
+      <c r="A33" s="72"/>
       <c r="B33" s="21"/>
       <c r="C33" s="39"/>
       <c r="D33" s="26"/>
       <c r="E33" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="21"/>
       <c r="H33" s="1"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="48" t="s">
-        <v>68</v>
+      <c r="A34" s="60" t="s">
+        <v>69</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -7444,8 +7640,8 @@
       </c>
       <c r="H34" s="9"/>
     </row>
-    <row r="35" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A35" s="49"/>
+    <row r="35" spans="1:8">
+      <c r="A35" s="61"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
@@ -7457,18 +7653,18 @@
       <c r="H35" s="12"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="48" t="s">
-        <v>69</v>
+      <c r="A36" s="60" t="s">
+        <v>70</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C36" s="8"/>
-      <c r="D36" s="27" t="s">
-        <v>71</v>
+      <c r="D36" s="88" t="s">
+        <v>72</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F36" s="27" t="s">
         <v>18</v>
@@ -7477,31 +7673,31 @@
       <c r="H36" s="9"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="53"/>
+      <c r="A37" s="69"/>
       <c r="B37" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C37" s="1"/>
-      <c r="D37" s="26" t="s">
-        <v>74</v>
+      <c r="D37" s="89" t="s">
+        <v>75</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="13"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="53"/>
+      <c r="A38" s="69"/>
       <c r="B38" s="25" t="s">
         <v>18</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="2" t="s">
-        <v>21</v>
+      <c r="D38" s="27" t="s">
+        <v>78</v>
       </c>
       <c r="E38" s="21"/>
       <c r="F38" s="2" t="s">
@@ -7511,29 +7707,29 @@
       <c r="H38" s="13"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="53"/>
+      <c r="A39" s="69"/>
       <c r="B39" s="26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C39" s="1"/>
-      <c r="D39" s="1" t="s">
-        <v>77</v>
+      <c r="D39" s="26" t="s">
+        <v>79</v>
       </c>
       <c r="E39" s="21"/>
       <c r="F39" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="13"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="53"/>
+      <c r="A40" s="69"/>
       <c r="B40" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C40" s="1"/>
-      <c r="D40" s="25" t="s">
-        <v>71</v>
+      <c r="D40" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="E40" s="21"/>
       <c r="F40" s="1"/>
@@ -7541,13 +7737,13 @@
       <c r="H40" s="13"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="53"/>
+      <c r="A41" s="69"/>
       <c r="B41" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C41" s="1"/>
-      <c r="D41" s="26" t="s">
-        <v>80</v>
+      <c r="D41" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="E41" s="21"/>
       <c r="F41" s="1"/>
@@ -7555,808 +7751,832 @@
       <c r="H41" s="13"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="53"/>
+      <c r="A42" s="69"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="29" t="s">
-        <v>34</v>
+      <c r="D42" s="25" t="s">
+        <v>78</v>
       </c>
       <c r="E42" s="21"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="13"/>
     </row>
-    <row r="43" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A43" s="49"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="E43" s="23"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="12"/>
-    </row>
-    <row r="44" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A44" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="50"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="51"/>
-      <c r="E44" s="51"/>
-      <c r="F44" s="51"/>
-      <c r="G44" s="51"/>
-      <c r="H44" s="52"/>
-    </row>
-    <row r="45" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A45" s="14" t="s">
+    <row r="43" spans="1:8">
+      <c r="A43" s="71"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="B45" s="50"/>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="51"/>
-      <c r="H45" s="52"/>
-    </row>
-    <row r="46" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A46" s="14" t="s">
+      <c r="E43" s="21"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="13"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="71"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="21"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="13"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="61"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="B46" s="50"/>
-      <c r="C46" s="51"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="51"/>
-      <c r="G46" s="51"/>
-      <c r="H46" s="52"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="12"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="63"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="64"/>
+      <c r="H46" s="65"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A47" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B47" s="57"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="59"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="48" t="s">
+      <c r="A47" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="G48" s="8"/>
-      <c r="H48" s="9"/>
+      <c r="B47" s="63"/>
+      <c r="C47" s="64"/>
+      <c r="D47" s="64"/>
+      <c r="E47" s="64"/>
+      <c r="F47" s="64"/>
+      <c r="G47" s="64"/>
+      <c r="H47" s="65"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A48" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B48" s="63"/>
+      <c r="C48" s="64"/>
+      <c r="D48" s="64"/>
+      <c r="E48" s="64"/>
+      <c r="F48" s="64"/>
+      <c r="G48" s="64"/>
+      <c r="H48" s="65"/>
     </row>
     <row r="49" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A49" s="49"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="G49" s="11"/>
-      <c r="H49" s="12"/>
+      <c r="A49" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B49" s="66"/>
+      <c r="C49" s="67"/>
+      <c r="D49" s="67"/>
+      <c r="E49" s="67"/>
+      <c r="F49" s="67"/>
+      <c r="G49" s="67"/>
+      <c r="H49" s="68"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="48" t="s">
-        <v>87</v>
+      <c r="A50" s="60" t="s">
+        <v>89</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
+      <c r="F50" s="27" t="s">
+        <v>18</v>
+      </c>
       <c r="G50" s="8"/>
-      <c r="H50" s="9" t="s">
+      <c r="H50" s="9"/>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A51" s="61"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="G51" s="11"/>
+      <c r="H51" s="12"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="53"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="53"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="35" t="s">
-        <v>8</v>
-      </c>
-    </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="53"/>
+      <c r="A53" s="69"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
-      <c r="H53" s="37" t="s">
-        <v>89</v>
+      <c r="H53" s="13" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="53"/>
+      <c r="A54" s="69"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-      <c r="H54" s="15" t="s">
-        <v>21</v>
+      <c r="H54" s="35" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="53"/>
+      <c r="A55" s="69"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
-      <c r="H55" s="13" t="s">
-        <v>90</v>
+      <c r="H55" s="37" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="53"/>
+      <c r="A56" s="69"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
-      <c r="H56" s="35" t="s">
+      <c r="H56" s="15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="69"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="69"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="35" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A57" s="49"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="36" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="B58" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C58" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="D58" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="E58" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="9"/>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="49"/>
-      <c r="B59" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C59" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D59" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="E59" s="30" t="s">
-        <v>93</v>
-      </c>
+    <row r="59" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A59" s="61"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
       <c r="F59" s="11"/>
       <c r="G59" s="11"/>
-      <c r="H59" s="12"/>
+      <c r="H59" s="36" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="48" t="s">
+      <c r="A60" s="60" t="s">
         <v>94</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C60" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="E60" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="9"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="61"/>
+      <c r="B61" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="C61" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="D61" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="E61" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="12"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="B62" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C60" s="43" t="s">
+      <c r="C62" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="D60" s="27" t="s">
+      <c r="D62" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="E60" s="66" t="s">
+      <c r="E62" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="F62" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H62" s="9"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="69"/>
+      <c r="B63" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C63" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="D63" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E63" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="F63" s="55" t="s">
+        <v>77</v>
+      </c>
+      <c r="G63" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="H63" s="13"/>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="69"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F64" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="G64" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="H64" s="13"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="69"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E65" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="F65" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="G65" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="H65" s="13"/>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="69"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D66" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="F66" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="G66" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66" s="13"/>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="69"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D67" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="E67" s="52" t="s">
+        <v>111</v>
+      </c>
+      <c r="F67" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="G67" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="H67" s="13"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="69"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D68" s="31"/>
+      <c r="E68" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F68" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="G68" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="H68" s="13"/>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="69"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="F60" s="71" t="s">
-        <v>18</v>
-      </c>
-      <c r="G60" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="H60" s="9"/>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="53"/>
-      <c r="B61" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C61" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="D61" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="E61" s="67" t="s">
-        <v>99</v>
-      </c>
-      <c r="F61" s="72" t="s">
-        <v>76</v>
-      </c>
-      <c r="G61" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="H61" s="13"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="53"/>
-      <c r="B62" s="1"/>
-      <c r="C62" s="2" t="s">
+      <c r="D69" s="31"/>
+      <c r="E69" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="F69" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="G69" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="H69" s="13"/>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="69"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E62" s="64" t="s">
-        <v>21</v>
-      </c>
-      <c r="F62" s="72" t="s">
-        <v>101</v>
-      </c>
-      <c r="G62" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="H62" s="13"/>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="53"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E63" s="70" t="s">
+      <c r="D70" s="31"/>
+      <c r="E70" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="F63" s="72" t="s">
-        <v>101</v>
-      </c>
-      <c r="G63" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="H63" s="13"/>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="53"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D64" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="E64" s="68" t="s">
-        <v>106</v>
-      </c>
-      <c r="F64" s="72" t="s">
-        <v>101</v>
-      </c>
-      <c r="G64" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H64" s="13"/>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="53"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="D65" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="E65" s="69" t="s">
-        <v>108</v>
-      </c>
-      <c r="F65" s="72" t="s">
-        <v>101</v>
-      </c>
-      <c r="G65" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="H65" s="13"/>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="53"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D66" s="31"/>
-      <c r="E66" s="64" t="s">
-        <v>21</v>
-      </c>
-      <c r="F66" s="72" t="s">
-        <v>101</v>
-      </c>
-      <c r="G66" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="H66" s="13"/>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="53"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="D67" s="31"/>
-      <c r="E67" s="65" t="s">
-        <v>109</v>
-      </c>
-      <c r="F67" s="72" t="s">
-        <v>101</v>
-      </c>
-      <c r="G67" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="H67" s="13"/>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="53"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D68" s="31"/>
-      <c r="E68" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="F68" s="72" t="s">
-        <v>101</v>
-      </c>
-      <c r="G68" s="34"/>
-      <c r="H68" s="13"/>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="49"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D69" s="30"/>
-      <c r="E69" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="F69" s="72" t="s">
-        <v>101</v>
-      </c>
-      <c r="G69" s="41"/>
-      <c r="H69" s="12"/>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="48" t="s">
-        <v>112</v>
-      </c>
-      <c r="B70" s="8"/>
-      <c r="C70" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="G70" s="8"/>
-      <c r="H70" s="9"/>
+      <c r="F70" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="G70" s="34"/>
+      <c r="H70" s="13"/>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="61"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="G71" s="1"/>
-      <c r="H71" s="13"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D71" s="30"/>
+      <c r="E71" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="F71" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="G71" s="41"/>
+      <c r="H71" s="12"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="73" t="s">
-        <v>113</v>
-      </c>
-      <c r="B72" s="74" t="s">
+      <c r="A72" s="60" t="s">
+        <v>115</v>
+      </c>
+      <c r="B72" s="8"/>
+      <c r="C72" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" s="8"/>
+      <c r="H72" s="9"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="71"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="G73" s="1"/>
+      <c r="H73" s="13"/>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="77" t="s">
+        <v>116</v>
+      </c>
+      <c r="B74" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="C72" s="74"/>
-      <c r="D72" s="75" t="s">
-        <v>114</v>
-      </c>
-      <c r="E72" s="74" t="s">
+      <c r="C74" s="78"/>
+      <c r="D74" s="79" t="s">
+        <v>72</v>
+      </c>
+      <c r="E74" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="F72" s="74" t="s">
+      <c r="F74" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="G72" s="74" t="s">
-        <v>59</v>
-      </c>
-      <c r="H72" s="76"/>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="77"/>
-      <c r="B73" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C73" s="1"/>
-      <c r="D73" s="67" t="s">
-        <v>116</v>
-      </c>
-      <c r="E73" s="1" t="s">
+      <c r="G74" s="78" t="s">
+        <v>60</v>
+      </c>
+      <c r="H74" s="80"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="81"/>
+      <c r="B75" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="C75" s="1"/>
+      <c r="D75" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="G73" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H73" s="78"/>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="77"/>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="64" t="s">
-        <v>21</v>
-      </c>
-      <c r="E74" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="F74" s="1"/>
-      <c r="G74" s="25" t="s">
+      <c r="F75" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H74" s="78"/>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="77"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="65" t="s">
+      <c r="G75" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E75" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="F75" s="1"/>
-      <c r="G75" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="H75" s="78"/>
+      <c r="H75" s="82"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="77"/>
+      <c r="A76" s="81"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
-      <c r="D76" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="E76" s="21"/>
+      <c r="D76" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>73</v>
+      </c>
       <c r="F76" s="1"/>
-      <c r="G76" s="2" t="s">
+      <c r="G76" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="H76" s="82"/>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="81"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="E77" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="F77" s="1"/>
+      <c r="G77" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="H77" s="82"/>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="81"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="E78" s="21"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H76" s="78"/>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="79"/>
-      <c r="B77" s="80"/>
-      <c r="C77" s="80"/>
-      <c r="D77" s="81" t="s">
-        <v>101</v>
-      </c>
-      <c r="E77" s="82"/>
-      <c r="F77" s="80"/>
-      <c r="G77" s="80" t="s">
-        <v>124</v>
-      </c>
-      <c r="H77" s="83"/>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="B78" s="31" t="s">
+      <c r="H78" s="82"/>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="83"/>
+      <c r="B79" s="84"/>
+      <c r="C79" s="84"/>
+      <c r="D79" s="85" t="s">
+        <v>104</v>
+      </c>
+      <c r="E79" s="86"/>
+      <c r="F79" s="84"/>
+      <c r="G79" s="84" t="s">
+        <v>126</v>
+      </c>
+      <c r="H79" s="87"/>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="B80" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" s="13"/>
-    </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="53"/>
-      <c r="B79" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="H79" s="13"/>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="A80" s="53"/>
-      <c r="B80" s="31"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="2" t="s">
+      <c r="G80" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="H80" s="13"/>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="69"/>
+      <c r="B81" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="H81" s="13"/>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="69"/>
+      <c r="B82" s="31"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H80" s="13"/>
-    </row>
-    <row r="81" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A81" s="49"/>
-      <c r="B81" s="30"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="H81" s="12"/>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="9"/>
+      <c r="H82" s="13"/>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A83" s="49"/>
-      <c r="B83" s="11"/>
+      <c r="A83" s="61"/>
+      <c r="B83" s="30"/>
       <c r="C83" s="11"/>
-      <c r="D83" s="28" t="s">
-        <v>128</v>
-      </c>
+      <c r="D83" s="11"/>
       <c r="E83" s="11"/>
       <c r="F83" s="11"/>
-      <c r="G83" s="11"/>
+      <c r="G83" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="H83" s="12"/>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="48" t="s">
+      <c r="A84" s="60" t="s">
         <v>129</v>
       </c>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
+      <c r="D84" s="27" t="s">
+        <v>18</v>
+      </c>
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
-      <c r="G84" s="27" t="s">
+      <c r="G84" s="8"/>
+      <c r="H84" s="9"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A85" s="61"/>
+      <c r="B85" s="11"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E85" s="11"/>
+      <c r="F85" s="11"/>
+      <c r="G85" s="11"/>
+      <c r="H85" s="12"/>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H84" s="9"/>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="53"/>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="26" t="s">
+      <c r="H86" s="9"/>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="69"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H85" s="13"/>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="53"/>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="25" t="s">
+      <c r="H87" s="13"/>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="69"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="H86" s="13"/>
-    </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A87" s="49"/>
-      <c r="B87" s="11"/>
-      <c r="C87" s="11"/>
-      <c r="D87" s="11"/>
-      <c r="E87" s="11"/>
-      <c r="F87" s="11"/>
-      <c r="G87" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="H87" s="12"/>
-    </row>
-    <row r="88" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A88" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="B88" s="50"/>
-      <c r="C88" s="51"/>
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="51"/>
-      <c r="G88" s="51"/>
-      <c r="H88" s="52"/>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89" s="60" t="s">
-        <v>131</v>
-      </c>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1" t="s">
+      <c r="H88" s="13"/>
+    </row>
+    <row r="89" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A89" s="61"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
+      <c r="F89" s="11"/>
+      <c r="G89" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="H89" s="12"/>
+    </row>
+    <row r="90" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A90" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B90" s="63"/>
+      <c r="C90" s="64"/>
+      <c r="D90" s="64"/>
+      <c r="E90" s="64"/>
+      <c r="F90" s="64"/>
+      <c r="G90" s="64"/>
+      <c r="H90" s="65"/>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="70" t="s">
+        <v>133</v>
+      </c>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1" t="s">
+      <c r="E91" s="1"/>
+      <c r="F91" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G89" s="1"/>
-      <c r="H89" s="13" t="s">
+      <c r="G91" s="1"/>
+      <c r="H91" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A90" s="49"/>
-      <c r="B90" s="11"/>
-      <c r="C90" s="11"/>
-      <c r="D90" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E90" s="11"/>
-      <c r="F90" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="G90" s="11"/>
-      <c r="H90" s="12" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
-      <c r="D91" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
-      <c r="G91" s="8"/>
-      <c r="H91" s="9"/>
-    </row>
     <row r="92" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A92" s="49"/>
+      <c r="A92" s="61"/>
       <c r="B92" s="11"/>
       <c r="C92" s="11"/>
-      <c r="D92" s="28" t="s">
-        <v>128</v>
+      <c r="D92" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="E92" s="11"/>
-      <c r="F92" s="11"/>
+      <c r="F92" s="11" t="s">
+        <v>134</v>
+      </c>
       <c r="G92" s="11"/>
-      <c r="H92" s="12"/>
-    </row>
-    <row r="93" spans="1:8" ht="6.75" customHeight="1">
-      <c r="B93" s="56"/>
-      <c r="C93" s="56"/>
-      <c r="D93" s="56"/>
-      <c r="E93" s="56"/>
-      <c r="F93" s="56"/>
-      <c r="G93" s="56"/>
-      <c r="H93" s="56"/>
+      <c r="H92" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="B93" s="8"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E93" s="8"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="9"/>
+    </row>
+    <row r="94" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A94" s="61"/>
+      <c r="B94" s="11"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E94" s="11"/>
+      <c r="F94" s="11"/>
+      <c r="G94" s="11"/>
+      <c r="H94" s="12"/>
+    </row>
+    <row r="95" spans="1:8" ht="6.75" customHeight="1">
+      <c r="B95" s="62"/>
+      <c r="C95" s="62"/>
+      <c r="D95" s="62"/>
+      <c r="E95" s="62"/>
+      <c r="F95" s="62"/>
+      <c r="G95" s="62"/>
+      <c r="H95" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="B93:H93"/>
-    <mergeCell ref="B88:H88"/>
-    <mergeCell ref="B47:H47"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A87"/>
-    <mergeCell ref="A89:A90"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A69"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A77"/>
-    <mergeCell ref="A48:A49"/>
     <mergeCell ref="A26:A33"/>
     <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A43"/>
-    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="A36:A45"/>
+    <mergeCell ref="B47:H47"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B46:H46"/>
     <mergeCell ref="A9:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B17:H17"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="B95:H95"/>
+    <mergeCell ref="B90:H90"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A52:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A79"/>
+    <mergeCell ref="A50:A51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="34" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -8371,56 +8591,56 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="B4" s="62" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
+      <c r="B4" s="75" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="B5" s="63" t="s">
-        <v>137</v>
-      </c>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
+      <c r="B5" s="76" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="84">
-        <v>0</v>
-      </c>
-      <c r="C7" s="84">
-        <v>0</v>
-      </c>
-      <c r="D7" s="84">
-        <v>0</v>
-      </c>
-      <c r="E7" s="84">
+      <c r="B7" s="56">
+        <v>0</v>
+      </c>
+      <c r="C7" s="56">
+        <v>0</v>
+      </c>
+      <c r="D7" s="56">
+        <v>0</v>
+      </c>
+      <c r="E7" s="56">
         <v>0</v>
       </c>
     </row>
@@ -8428,16 +8648,16 @@
       <c r="A8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="84">
-        <v>0</v>
-      </c>
-      <c r="C8" s="84">
-        <v>0</v>
-      </c>
-      <c r="D8" s="84">
-        <v>0</v>
-      </c>
-      <c r="E8" s="84">
+      <c r="B8" s="56">
+        <v>0</v>
+      </c>
+      <c r="C8" s="56">
+        <v>0</v>
+      </c>
+      <c r="D8" s="56">
+        <v>0</v>
+      </c>
+      <c r="E8" s="56">
         <v>0</v>
       </c>
     </row>
@@ -8445,16 +8665,16 @@
       <c r="A9" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="84">
-        <v>0</v>
-      </c>
-      <c r="C9" s="84">
+      <c r="B9" s="56">
+        <v>0</v>
+      </c>
+      <c r="C9" s="56">
         <v>4.1667000000000003E-2</v>
       </c>
-      <c r="D9" s="84">
-        <v>0</v>
-      </c>
-      <c r="E9" s="84">
+      <c r="D9" s="56">
+        <v>0</v>
+      </c>
+      <c r="E9" s="56">
         <v>0</v>
       </c>
     </row>
@@ -8462,16 +8682,16 @@
       <c r="A10" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="84">
-        <v>0</v>
-      </c>
-      <c r="C10" s="84">
-        <v>0</v>
-      </c>
-      <c r="D10" s="84">
-        <v>0</v>
-      </c>
-      <c r="E10" s="84">
+      <c r="B10" s="56">
+        <v>0</v>
+      </c>
+      <c r="C10" s="56">
+        <v>0</v>
+      </c>
+      <c r="D10" s="56">
+        <v>0</v>
+      </c>
+      <c r="E10" s="56">
         <v>0</v>
       </c>
     </row>
@@ -8479,16 +8699,16 @@
       <c r="A11" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="84">
-        <v>0</v>
-      </c>
-      <c r="C11" s="84">
-        <v>0</v>
-      </c>
-      <c r="D11" s="84">
-        <v>0</v>
-      </c>
-      <c r="E11" s="84">
+      <c r="B11" s="56">
+        <v>0</v>
+      </c>
+      <c r="C11" s="56">
+        <v>0</v>
+      </c>
+      <c r="D11" s="56">
+        <v>0</v>
+      </c>
+      <c r="E11" s="56">
         <v>0</v>
       </c>
     </row>
@@ -8496,404 +8716,404 @@
       <c r="A12" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="84">
-        <v>0</v>
-      </c>
-      <c r="C12" s="84">
-        <v>0</v>
-      </c>
-      <c r="D12" s="84">
-        <v>0</v>
-      </c>
-      <c r="E12" s="84">
+      <c r="B12" s="56">
+        <v>0</v>
+      </c>
+      <c r="C12" s="56">
+        <v>0</v>
+      </c>
+      <c r="D12" s="56">
+        <v>0</v>
+      </c>
+      <c r="E12" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="84">
-        <v>0</v>
-      </c>
-      <c r="C13" s="84">
-        <v>0</v>
-      </c>
-      <c r="D13" s="84">
+        <v>46</v>
+      </c>
+      <c r="B13" s="56">
+        <v>0</v>
+      </c>
+      <c r="C13" s="56">
+        <v>0</v>
+      </c>
+      <c r="D13" s="56">
         <v>0.24166699999999999</v>
       </c>
-      <c r="E13" s="84">
+      <c r="E13" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="84">
-        <v>0</v>
-      </c>
-      <c r="C14" s="84">
-        <v>0</v>
-      </c>
-      <c r="D14" s="84">
-        <v>0</v>
-      </c>
-      <c r="E14" s="84">
+        <v>53</v>
+      </c>
+      <c r="B14" s="56">
+        <v>0</v>
+      </c>
+      <c r="C14" s="56">
+        <v>0</v>
+      </c>
+      <c r="D14" s="56">
+        <v>0</v>
+      </c>
+      <c r="E14" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="84">
-        <v>0</v>
-      </c>
-      <c r="C15" s="84">
-        <v>0</v>
-      </c>
-      <c r="D15" s="84">
-        <v>0</v>
-      </c>
-      <c r="E15" s="84">
+        <v>69</v>
+      </c>
+      <c r="B15" s="56">
+        <v>0</v>
+      </c>
+      <c r="C15" s="56">
+        <v>0</v>
+      </c>
+      <c r="D15" s="56">
+        <v>0</v>
+      </c>
+      <c r="E15" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="84">
+        <v>70</v>
+      </c>
+      <c r="B16" s="56">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="C16" s="84">
+      <c r="C16" s="56">
         <v>8.3334000000000005E-2</v>
       </c>
-      <c r="D16" s="84">
-        <v>0</v>
-      </c>
-      <c r="E16" s="84">
+      <c r="D16" s="56">
+        <v>0</v>
+      </c>
+      <c r="E16" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="B17" s="84">
-        <v>0</v>
-      </c>
-      <c r="C17" s="84">
-        <v>0</v>
-      </c>
-      <c r="D17" s="84">
-        <v>0</v>
-      </c>
-      <c r="E17" s="84">
+        <v>85</v>
+      </c>
+      <c r="B17" s="56">
+        <v>0</v>
+      </c>
+      <c r="C17" s="56">
+        <v>0</v>
+      </c>
+      <c r="D17" s="56">
+        <v>0</v>
+      </c>
+      <c r="E17" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="B18" s="84">
-        <v>0</v>
-      </c>
-      <c r="C18" s="84">
-        <v>0</v>
-      </c>
-      <c r="D18" s="84">
-        <v>0</v>
-      </c>
-      <c r="E18" s="84">
+        <v>144</v>
+      </c>
+      <c r="B18" s="56">
+        <v>0</v>
+      </c>
+      <c r="C18" s="56">
+        <v>0</v>
+      </c>
+      <c r="D18" s="56">
+        <v>0</v>
+      </c>
+      <c r="E18" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="B19" s="84">
-        <v>0</v>
-      </c>
-      <c r="C19" s="84">
-        <v>0</v>
-      </c>
-      <c r="D19" s="84">
-        <v>0</v>
-      </c>
-      <c r="E19" s="84">
+        <v>86</v>
+      </c>
+      <c r="B19" s="56">
+        <v>0</v>
+      </c>
+      <c r="C19" s="56">
+        <v>0</v>
+      </c>
+      <c r="D19" s="56">
+        <v>0</v>
+      </c>
+      <c r="E19" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" s="84">
-        <v>0</v>
-      </c>
-      <c r="C20" s="84">
-        <v>0</v>
-      </c>
-      <c r="D20" s="84">
-        <v>0</v>
-      </c>
-      <c r="E20" s="84">
+        <v>87</v>
+      </c>
+      <c r="B20" s="56">
+        <v>0</v>
+      </c>
+      <c r="C20" s="56">
+        <v>0</v>
+      </c>
+      <c r="D20" s="56">
+        <v>0</v>
+      </c>
+      <c r="E20" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="B21" s="84">
-        <v>0</v>
-      </c>
-      <c r="C21" s="84">
-        <v>0</v>
-      </c>
-      <c r="D21" s="84">
-        <v>0</v>
-      </c>
-      <c r="E21" s="84">
+        <v>88</v>
+      </c>
+      <c r="B21" s="56">
+        <v>0</v>
+      </c>
+      <c r="C21" s="56">
+        <v>0</v>
+      </c>
+      <c r="D21" s="56">
+        <v>0</v>
+      </c>
+      <c r="E21" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="84">
-        <v>0</v>
-      </c>
-      <c r="C22" s="84">
-        <v>0</v>
-      </c>
-      <c r="D22" s="84">
-        <v>0</v>
-      </c>
-      <c r="E22" s="84">
+        <v>89</v>
+      </c>
+      <c r="B22" s="56">
+        <v>0</v>
+      </c>
+      <c r="C22" s="56">
+        <v>0</v>
+      </c>
+      <c r="D22" s="56">
+        <v>0</v>
+      </c>
+      <c r="E22" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="B23" s="84">
-        <v>0</v>
-      </c>
-      <c r="C23" s="84">
-        <v>0</v>
-      </c>
-      <c r="D23" s="84">
-        <v>0</v>
-      </c>
-      <c r="E23" s="84">
+        <v>145</v>
+      </c>
+      <c r="B23" s="56">
+        <v>0</v>
+      </c>
+      <c r="C23" s="56">
+        <v>0</v>
+      </c>
+      <c r="D23" s="56">
+        <v>0</v>
+      </c>
+      <c r="E23" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="B24" s="84">
-        <v>0</v>
-      </c>
-      <c r="C24" s="84">
-        <v>0</v>
-      </c>
-      <c r="D24" s="84">
+        <v>90</v>
+      </c>
+      <c r="B24" s="56">
+        <v>0</v>
+      </c>
+      <c r="C24" s="56">
+        <v>0</v>
+      </c>
+      <c r="D24" s="56">
         <v>0.25</v>
       </c>
-      <c r="E24" s="84">
+      <c r="E24" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" s="84">
-        <v>0</v>
-      </c>
-      <c r="C25" s="84">
+        <v>94</v>
+      </c>
+      <c r="B25" s="56">
+        <v>0</v>
+      </c>
+      <c r="C25" s="56">
         <v>0.45833400000000002</v>
       </c>
-      <c r="D25" s="84">
-        <v>0</v>
-      </c>
-      <c r="E25" s="84">
+      <c r="D25" s="56">
+        <v>0</v>
+      </c>
+      <c r="E25" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="B26" s="84">
-        <v>0</v>
-      </c>
-      <c r="C26" s="84">
+        <v>97</v>
+      </c>
+      <c r="B26" s="56">
+        <v>0</v>
+      </c>
+      <c r="C26" s="56">
         <v>0.16666700000000001</v>
       </c>
-      <c r="D26" s="84">
+      <c r="D26" s="56">
         <v>8.3334000000000005E-2</v>
       </c>
-      <c r="E26" s="84">
+      <c r="E26" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="B27" s="84">
-        <v>0</v>
-      </c>
-      <c r="C27" s="84">
-        <v>0</v>
-      </c>
-      <c r="D27" s="84">
-        <v>0</v>
-      </c>
-      <c r="E27" s="84">
+        <v>115</v>
+      </c>
+      <c r="B27" s="56">
+        <v>0</v>
+      </c>
+      <c r="C27" s="56">
+        <v>0</v>
+      </c>
+      <c r="D27" s="56">
+        <v>0</v>
+      </c>
+      <c r="E27" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B28" s="84">
-        <v>0</v>
-      </c>
-      <c r="C28" s="84">
-        <v>0</v>
-      </c>
-      <c r="D28" s="84">
-        <v>0</v>
-      </c>
-      <c r="E28" s="84">
+        <v>116</v>
+      </c>
+      <c r="B28" s="56">
+        <v>0</v>
+      </c>
+      <c r="C28" s="56">
+        <v>0</v>
+      </c>
+      <c r="D28" s="56">
+        <v>0</v>
+      </c>
+      <c r="E28" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="84">
-        <v>0</v>
-      </c>
-      <c r="C29" s="84">
+        <v>127</v>
+      </c>
+      <c r="B29" s="56">
+        <v>0</v>
+      </c>
+      <c r="C29" s="56">
         <v>0.125</v>
       </c>
-      <c r="D29" s="84">
+      <c r="D29" s="56">
         <v>0.159723</v>
       </c>
-      <c r="E29" s="84">
+      <c r="E29" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="B30" s="84">
-        <v>0</v>
-      </c>
-      <c r="C30" s="84">
-        <v>0</v>
-      </c>
-      <c r="D30" s="84">
-        <v>0</v>
-      </c>
-      <c r="E30" s="84">
+        <v>129</v>
+      </c>
+      <c r="B30" s="56">
+        <v>0</v>
+      </c>
+      <c r="C30" s="56">
+        <v>0</v>
+      </c>
+      <c r="D30" s="56">
+        <v>0</v>
+      </c>
+      <c r="E30" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="B31" s="84">
-        <v>0</v>
-      </c>
-      <c r="C31" s="84">
-        <v>0</v>
-      </c>
-      <c r="D31" s="84">
-        <v>0</v>
-      </c>
-      <c r="E31" s="84">
+        <v>131</v>
+      </c>
+      <c r="B31" s="56">
+        <v>0</v>
+      </c>
+      <c r="C31" s="56">
+        <v>0</v>
+      </c>
+      <c r="D31" s="56">
+        <v>0</v>
+      </c>
+      <c r="E31" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="B32" s="84">
-        <v>0</v>
-      </c>
-      <c r="C32" s="84">
-        <v>0</v>
-      </c>
-      <c r="D32" s="84">
-        <v>0</v>
-      </c>
-      <c r="E32" s="84">
+        <v>132</v>
+      </c>
+      <c r="B32" s="56">
+        <v>0</v>
+      </c>
+      <c r="C32" s="56">
+        <v>0</v>
+      </c>
+      <c r="D32" s="56">
+        <v>0</v>
+      </c>
+      <c r="E32" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="B33" s="84">
-        <v>0</v>
-      </c>
-      <c r="C33" s="84">
-        <v>0</v>
-      </c>
-      <c r="D33" s="84">
-        <v>0</v>
-      </c>
-      <c r="E33" s="84">
+        <v>133</v>
+      </c>
+      <c r="B33" s="56">
+        <v>0</v>
+      </c>
+      <c r="C33" s="56">
+        <v>0</v>
+      </c>
+      <c r="D33" s="56">
+        <v>0</v>
+      </c>
+      <c r="E33" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="B34" s="84">
-        <v>0</v>
-      </c>
-      <c r="C34" s="84">
-        <v>0</v>
-      </c>
-      <c r="D34" s="84">
-        <v>0</v>
-      </c>
-      <c r="E34" s="84">
+        <v>136</v>
+      </c>
+      <c r="B34" s="56">
+        <v>0</v>
+      </c>
+      <c r="C34" s="56">
+        <v>0</v>
+      </c>
+      <c r="D34" s="56">
+        <v>0</v>
+      </c>
+      <c r="E34" s="56">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="B35" s="85">
+      <c r="B35" s="57">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="C35" s="85">
+      <c r="C35" s="57">
         <v>0.875</v>
       </c>
-      <c r="D35" s="85">
+      <c r="D35" s="57">
         <v>0.73472300000000001</v>
       </c>
-      <c r="E35" s="85">
+      <c r="E35" s="57">
         <v>0</v>
       </c>
     </row>
@@ -8913,45 +9133,45 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="86" t="s">
-        <v>144</v>
-      </c>
-      <c r="B4" s="87" t="s">
-        <v>145</v>
+      <c r="A4" s="58" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="86" t="s">
-        <v>146</v>
-      </c>
-      <c r="B5" s="87"/>
+      <c r="A5" s="58" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="59"/>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="86" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="87" t="s">
-        <v>113</v>
+      <c r="A6" s="58" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="86" t="s">
-        <v>148</v>
-      </c>
-      <c r="B7" s="87" t="s">
-        <v>149</v>
+      <c r="A7" s="58" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="86" t="s">
-        <v>150</v>
-      </c>
-      <c r="B8" s="87" t="s">
-        <v>151</v>
+      <c r="A8" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -8972,15 +9192,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F57AE488C1C9C348AE667C65EC1B6349" ma:contentTypeVersion="83" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="584bf6b77295f7da4f9cf4ac656056b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3c298670-db79-47a5-968d-a4570c34317f" xmlns:ns3="17e8e7ea-beb0-4155-adc4-5bfa61f32508" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0744868ac059cd1623b27209cff1bde4" ns2:_="" ns3:_="">
     <xsd:import namespace="3c298670-db79-47a5-968d-a4570c34317f"/>
@@ -9125,14 +9336,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B3E9373-21F1-472D-A1B7-AB92AB4BB0C0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE50E459-6C86-4FD6-AF9A-BF99153D4F10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55258B40-0392-499F-BBA5-A4C6FB1ACB8A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55258B40-0392-499F-BBA5-A4C6FB1ACB8A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE50E459-6C86-4FD6-AF9A-BF99153D4F10}"/>
 </file>
--- a/Plannings 2026 S14.xlsx
+++ b/Plannings 2026 S14.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{150E33BF-47F0-4B68-8AA0-FBA696D166AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E34CF0FB-B08D-48F5-A778-D31CC4122B8E}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{150E33BF-47F0-4B68-8AA0-FBA696D166AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7334A45-FEEF-469E-9123-A3EA64B69B1C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -635,7 +635,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1064,11 +1064,68 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1083,9 +1140,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1121,9 +1175,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1131,12 +1182,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1206,6 +1251,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1331,8 +1379,33 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3313,50 +3386,6 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7084,32 +7113,32 @@
   <dimension ref="A1:H95"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="8" width="48" customWidth="1"/>
+    <col min="1" max="8" width="49.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="B1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
     </row>
     <row r="3" spans="1:8">
       <c r="B3" s="5" t="s">
@@ -7161,81 +7190,81 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="27" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="9"/>
+      <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A6" s="61"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="28" t="s">
+      <c r="A6" s="58"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="12"/>
+      <c r="H6" s="11"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="60" t="s">
+      <c r="A7" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="9"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A8" s="61"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11" t="s">
+      <c r="A8" s="58"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="12"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="11"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="7"/>
+      <c r="E9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="43" t="s">
+      <c r="F9" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="9" t="s">
+      <c r="G9" s="7"/>
+      <c r="H9" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="69"/>
+      <c r="A10" s="66"/>
       <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
@@ -7246,17 +7275,17 @@
       <c r="E10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F10" s="42" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="12" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="69"/>
-      <c r="B11" s="29" t="s">
+      <c r="A11" s="66"/>
+      <c r="B11" s="25" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="1"/>
@@ -7268,11 +7297,11 @@
         <v>21</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11" s="13"/>
+      <c r="H11" s="12"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="69"/>
-      <c r="B12" s="31" t="s">
+      <c r="A12" s="66"/>
+      <c r="B12" s="27" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="1"/>
@@ -7280,84 +7309,84 @@
       <c r="E12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="45" t="s">
+      <c r="F12" s="41" t="s">
         <v>33</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="H12" s="13"/>
+      <c r="H12" s="12"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="69"/>
-      <c r="B13" s="29" t="s">
+      <c r="A13" s="66"/>
+      <c r="B13" s="25" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="25" t="s">
         <v>30</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="13"/>
+      <c r="H13" s="12"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A14" s="61"/>
-      <c r="B14" s="30" t="s">
+      <c r="A14" s="58"/>
+      <c r="B14" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="30" t="s">
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="12"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="11"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="9"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A16" s="61"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11" t="s">
+      <c r="A16" s="58"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="12"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="11"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="63"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="65"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="62"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="60" t="s">
+      <c r="A18" s="57" t="s">
         <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -7379,7 +7408,7 @@
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="74"/>
+      <c r="A19" s="71"/>
       <c r="B19" s="1" t="s">
         <v>41</v>
       </c>
@@ -7399,7 +7428,7 @@
       <c r="H19" s="1"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="74"/>
+      <c r="A20" s="71"/>
       <c r="B20" s="1"/>
       <c r="C20" s="2" t="s">
         <v>21</v>
@@ -7411,7 +7440,7 @@
       <c r="H20" s="1"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A21" s="61"/>
+      <c r="A21" s="58"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
         <v>44</v>
@@ -7423,27 +7452,27 @@
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8" t="s">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8" t="s">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="33" t="s">
+      <c r="F22" s="7"/>
+      <c r="G22" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="38" t="s">
+      <c r="H22" s="34" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="69"/>
+      <c r="A23" s="66"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
         <v>47</v>
@@ -7453,15 +7482,15 @@
         <v>48</v>
       </c>
       <c r="F23" s="1"/>
-      <c r="G23" s="34" t="s">
+      <c r="G23" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="H23" s="37" t="s">
+      <c r="H23" s="33" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="69"/>
+      <c r="A24" s="66"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -7470,260 +7499,260 @@
       <c r="G24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="15" t="s">
+      <c r="H24" s="14" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A25" s="61"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11" t="s">
+      <c r="A25" s="58"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="H25" s="11" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="72" t="s">
+      <c r="A26" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="36" t="s">
         <v>54</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E26" s="40" t="s">
+      <c r="E26" s="36" t="s">
         <v>54</v>
       </c>
       <c r="F26" s="1"/>
-      <c r="G26" s="20" t="s">
+      <c r="G26" s="18" t="s">
         <v>56</v>
       </c>
       <c r="H26" s="1"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="72"/>
-      <c r="B27" s="39" t="s">
+      <c r="A27" s="69"/>
+      <c r="B27" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="35" t="s">
         <v>57</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="39" t="s">
+      <c r="E27" s="35" t="s">
         <v>57</v>
       </c>
       <c r="F27" s="1"/>
-      <c r="G27" s="21" t="s">
+      <c r="G27" s="19" t="s">
         <v>59</v>
       </c>
       <c r="H27" s="1"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="72"/>
+      <c r="A28" s="69"/>
       <c r="B28" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="40" t="s">
+      <c r="D28" s="36" t="s">
         <v>54</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>60</v>
       </c>
       <c r="F28" s="1"/>
-      <c r="G28" s="21"/>
+      <c r="G28" s="19"/>
       <c r="H28" s="1"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="72"/>
+      <c r="A29" s="69"/>
       <c r="B29" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="39" t="s">
+      <c r="D29" s="35" t="s">
         <v>63</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F29" s="1"/>
-      <c r="G29" s="21"/>
+      <c r="G29" s="19"/>
       <c r="H29" s="1"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="72"/>
-      <c r="B30" s="20" t="s">
+      <c r="A30" s="69"/>
+      <c r="B30" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C30" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="25" t="s">
+      <c r="D30" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E30" s="40" t="s">
+      <c r="E30" s="36" t="s">
         <v>54</v>
       </c>
       <c r="F30" s="1"/>
-      <c r="G30" s="21"/>
+      <c r="G30" s="19"/>
       <c r="H30" s="1"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="72"/>
-      <c r="B31" s="21" t="s">
+      <c r="A31" s="69"/>
+      <c r="B31" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="D31" s="26" t="s">
+      <c r="D31" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="E31" s="39" t="s">
+      <c r="E31" s="35" t="s">
         <v>67</v>
       </c>
       <c r="F31" s="1"/>
-      <c r="G31" s="21"/>
+      <c r="G31" s="19"/>
       <c r="H31" s="1"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="72"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="26"/>
+      <c r="A32" s="69"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="22"/>
       <c r="E32" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F32" s="1"/>
-      <c r="G32" s="21"/>
+      <c r="G32" s="19"/>
       <c r="H32" s="1"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A33" s="72"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="26"/>
+      <c r="A33" s="69"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="22"/>
       <c r="E33" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F33" s="1"/>
-      <c r="G33" s="21"/>
+      <c r="G33" s="19"/>
       <c r="H33" s="1"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="60" t="s">
+      <c r="A34" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="27" t="s">
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H34" s="9"/>
+      <c r="H34" s="8"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="61"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="28" t="s">
+      <c r="A35" s="68"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="22" t="s">
         <v>19</v>
       </c>
       <c r="H35" s="12"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="60" t="s">
+      <c r="A36" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="85" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="88" t="s">
+      <c r="C36" s="75"/>
+      <c r="D36" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="F36" s="27" t="s">
+      <c r="F36" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="G36" s="8"/>
-      <c r="H36" s="9"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="77"/>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="69"/>
-      <c r="B37" s="19" t="s">
+      <c r="A37" s="78"/>
+      <c r="B37" s="17" t="s">
         <v>74</v>
       </c>
       <c r="C37" s="1"/>
-      <c r="D37" s="89" t="s">
+      <c r="D37" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="E37" s="21" t="s">
+      <c r="E37" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="26" t="s">
+      <c r="F37" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G37" s="1"/>
-      <c r="H37" s="13"/>
+      <c r="H37" s="79"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="69"/>
-      <c r="B38" s="25" t="s">
+      <c r="A38" s="78"/>
+      <c r="B38" s="21" t="s">
         <v>18</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="27" t="s">
+      <c r="D38" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="E38" s="21"/>
+      <c r="E38" s="19"/>
       <c r="F38" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G38" s="1"/>
-      <c r="H38" s="13"/>
+      <c r="H38" s="79"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="69"/>
-      <c r="B39" s="26" t="s">
+      <c r="A39" s="78"/>
+      <c r="B39" s="22" t="s">
         <v>77</v>
       </c>
       <c r="C39" s="1"/>
-      <c r="D39" s="26" t="s">
+      <c r="D39" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="E39" s="21"/>
+      <c r="E39" s="19"/>
       <c r="F39" s="1" t="s">
         <v>80</v>
       </c>
       <c r="G39" s="1"/>
-      <c r="H39" s="13"/>
+      <c r="H39" s="79"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="69"/>
+      <c r="A40" s="78"/>
       <c r="B40" s="2" t="s">
         <v>21</v>
       </c>
@@ -7731,13 +7760,13 @@
       <c r="D40" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E40" s="21"/>
+      <c r="E40" s="19"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="H40" s="13"/>
+      <c r="H40" s="79"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="69"/>
+      <c r="A41" s="78"/>
       <c r="B41" s="1" t="s">
         <v>81</v>
       </c>
@@ -7745,317 +7774,317 @@
       <c r="D41" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E41" s="21"/>
+      <c r="E41" s="19"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-      <c r="H41" s="13"/>
+      <c r="H41" s="79"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="69"/>
+      <c r="A42" s="78"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="25" t="s">
+      <c r="D42" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="E42" s="21"/>
+      <c r="E42" s="19"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="13"/>
+      <c r="H42" s="79"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="71"/>
+      <c r="A43" s="88"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
-      <c r="D43" s="26" t="s">
+      <c r="D43" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="E43" s="21"/>
+      <c r="E43" s="19"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
-      <c r="H43" s="13"/>
+      <c r="H43" s="79"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="71"/>
+      <c r="A44" s="88"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
-      <c r="D44" s="29" t="s">
+      <c r="D44" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="E44" s="21"/>
+      <c r="E44" s="19"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
-      <c r="H44" s="13"/>
+      <c r="H44" s="79"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="61"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="31" t="s">
+      <c r="A45" s="80"/>
+      <c r="B45" s="81"/>
+      <c r="C45" s="81"/>
+      <c r="D45" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="E45" s="23"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="12"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
+      <c r="H45" s="84"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="B46" s="63"/>
-      <c r="C46" s="64"/>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="64"/>
-      <c r="G46" s="64"/>
-      <c r="H46" s="65"/>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A47" s="14" t="s">
+      <c r="B46" s="90"/>
+      <c r="C46" s="91"/>
+      <c r="D46" s="91"/>
+      <c r="E46" s="91"/>
+      <c r="F46" s="91"/>
+      <c r="G46" s="91"/>
+      <c r="H46" s="92"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B47" s="63"/>
-      <c r="C47" s="64"/>
-      <c r="D47" s="64"/>
-      <c r="E47" s="64"/>
-      <c r="F47" s="64"/>
-      <c r="G47" s="64"/>
-      <c r="H47" s="65"/>
+      <c r="B47" s="60"/>
+      <c r="C47" s="61"/>
+      <c r="D47" s="61"/>
+      <c r="E47" s="61"/>
+      <c r="F47" s="61"/>
+      <c r="G47" s="61"/>
+      <c r="H47" s="62"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B48" s="63"/>
-      <c r="C48" s="64"/>
-      <c r="D48" s="64"/>
-      <c r="E48" s="64"/>
-      <c r="F48" s="64"/>
-      <c r="G48" s="64"/>
-      <c r="H48" s="65"/>
+      <c r="B48" s="60"/>
+      <c r="C48" s="61"/>
+      <c r="D48" s="61"/>
+      <c r="E48" s="61"/>
+      <c r="F48" s="61"/>
+      <c r="G48" s="61"/>
+      <c r="H48" s="62"/>
     </row>
     <row r="49" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A49" s="16" t="s">
+      <c r="A49" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="B49" s="66"/>
-      <c r="C49" s="67"/>
-      <c r="D49" s="67"/>
-      <c r="E49" s="67"/>
-      <c r="F49" s="67"/>
-      <c r="G49" s="67"/>
-      <c r="H49" s="68"/>
+      <c r="B49" s="63"/>
+      <c r="C49" s="64"/>
+      <c r="D49" s="64"/>
+      <c r="E49" s="64"/>
+      <c r="F49" s="64"/>
+      <c r="G49" s="64"/>
+      <c r="H49" s="65"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="60" t="s">
+      <c r="A50" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="27" t="s">
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="G50" s="8"/>
-      <c r="H50" s="9"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="8"/>
     </row>
     <row r="51" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A51" s="61"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="28" t="s">
+      <c r="A51" s="58"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="G51" s="11"/>
-      <c r="H51" s="12"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="11"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="60" t="s">
+      <c r="A52" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="9" t="s">
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="69"/>
+      <c r="A53" s="66"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
-      <c r="H53" s="13" t="s">
+      <c r="H53" s="12" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="69"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-      <c r="H54" s="35" t="s">
+      <c r="H54" s="31" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="69"/>
+      <c r="A55" s="66"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
-      <c r="H55" s="37" t="s">
+      <c r="H55" s="33" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="69"/>
+      <c r="A56" s="66"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
-      <c r="H56" s="15" t="s">
+      <c r="H56" s="14" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="69"/>
+      <c r="A57" s="66"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
-      <c r="H57" s="13" t="s">
+      <c r="H57" s="12" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="69"/>
+      <c r="A58" s="66"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
-      <c r="H58" s="35" t="s">
+      <c r="H58" s="31" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A59" s="61"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="36" t="s">
+      <c r="A59" s="58"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="32" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="60" t="s">
+      <c r="A60" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="B60" s="32" t="s">
+      <c r="B60" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="C60" s="32" t="s">
+      <c r="C60" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D60" s="32" t="s">
+      <c r="D60" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="E60" s="32" t="s">
+      <c r="E60" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="9"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="8"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="61"/>
-      <c r="B61" s="30" t="s">
+      <c r="A61" s="58"/>
+      <c r="B61" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="C61" s="30" t="s">
+      <c r="C61" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="D61" s="30" t="s">
+      <c r="D61" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="E61" s="30" t="s">
+      <c r="E61" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="12"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="11"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="60" t="s">
+      <c r="A62" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="43" t="s">
+      <c r="C62" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="D62" s="27" t="s">
+      <c r="D62" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="E62" s="49" t="s">
+      <c r="E62" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="F62" s="54" t="s">
+      <c r="F62" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="G62" s="27" t="s">
+      <c r="G62" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H62" s="9"/>
+      <c r="H62" s="8"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="69"/>
+      <c r="A63" s="66"/>
       <c r="B63" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C63" s="44" t="s">
+      <c r="C63" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="D63" s="26" t="s">
+      <c r="D63" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="E63" s="50" t="s">
+      <c r="E63" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="F63" s="55" t="s">
+      <c r="F63" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="G63" s="26" t="s">
+      <c r="G63" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="H63" s="13"/>
+      <c r="H63" s="12"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="69"/>
+      <c r="A64" s="66"/>
       <c r="B64" s="1"/>
       <c r="C64" s="2" t="s">
         <v>21</v>
@@ -8063,19 +8092,19 @@
       <c r="D64" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E64" s="47" t="s">
+      <c r="E64" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="F64" s="55" t="s">
+      <c r="F64" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G64" s="25" t="s">
+      <c r="G64" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="H64" s="13"/>
+      <c r="H64" s="12"/>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="69"/>
+      <c r="A65" s="66"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
         <v>105</v>
@@ -8083,184 +8112,184 @@
       <c r="D65" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E65" s="53" t="s">
+      <c r="E65" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="F65" s="55" t="s">
+      <c r="F65" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G65" s="26" t="s">
+      <c r="G65" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="H65" s="13"/>
+      <c r="H65" s="12"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="69"/>
+      <c r="A66" s="66"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="25" t="s">
+      <c r="C66" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="D66" s="29" t="s">
+      <c r="D66" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="E66" s="51" t="s">
+      <c r="E66" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="F66" s="55" t="s">
+      <c r="F66" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G66" s="25" t="s">
+      <c r="G66" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="H66" s="13"/>
+      <c r="H66" s="12"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="69"/>
+      <c r="A67" s="66"/>
       <c r="B67" s="1"/>
-      <c r="C67" s="26" t="s">
+      <c r="C67" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="D67" s="31" t="s">
+      <c r="D67" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="E67" s="52" t="s">
+      <c r="E67" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="F67" s="55" t="s">
+      <c r="F67" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G67" s="26" t="s">
+      <c r="G67" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="H67" s="13"/>
+      <c r="H67" s="12"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="69"/>
+      <c r="A68" s="66"/>
       <c r="B68" s="1"/>
-      <c r="C68" s="29" t="s">
+      <c r="C68" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D68" s="31"/>
-      <c r="E68" s="47" t="s">
+      <c r="D68" s="27"/>
+      <c r="E68" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="F68" s="55" t="s">
+      <c r="F68" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G68" s="42" t="s">
+      <c r="G68" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="H68" s="13"/>
+      <c r="H68" s="12"/>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="69"/>
+      <c r="A69" s="66"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="31" t="s">
+      <c r="C69" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="D69" s="31"/>
-      <c r="E69" s="48" t="s">
+      <c r="D69" s="27"/>
+      <c r="E69" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="F69" s="55" t="s">
+      <c r="F69" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G69" s="34" t="s">
+      <c r="G69" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="H69" s="13"/>
+      <c r="H69" s="12"/>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="69"/>
+      <c r="A70" s="66"/>
       <c r="B70" s="1"/>
       <c r="C70" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D70" s="31"/>
-      <c r="E70" s="48" t="s">
+      <c r="D70" s="27"/>
+      <c r="E70" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="F70" s="55" t="s">
+      <c r="F70" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G70" s="34"/>
-      <c r="H70" s="13"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="12"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="61"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11" t="s">
+      <c r="A71" s="58"/>
+      <c r="B71" s="10"/>
+      <c r="C71" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="D71" s="30"/>
-      <c r="E71" s="48" t="s">
+      <c r="D71" s="26"/>
+      <c r="E71" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="F71" s="55" t="s">
+      <c r="F71" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G71" s="41"/>
-      <c r="H71" s="12"/>
+      <c r="G71" s="37"/>
+      <c r="H71" s="11"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="60" t="s">
+      <c r="A72" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="B72" s="8"/>
-      <c r="C72" s="27" t="s">
+      <c r="B72" s="7"/>
+      <c r="C72" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="27" t="s">
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="G72" s="8"/>
-      <c r="H72" s="9"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="8"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="71"/>
+      <c r="A73" s="68"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="26" t="s">
+      <c r="C73" s="22" t="s">
         <v>77</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
-      <c r="F73" s="26" t="s">
+      <c r="F73" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G73" s="1"/>
-      <c r="H73" s="13"/>
+      <c r="H73" s="12"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="77" t="s">
+      <c r="A74" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="B74" s="78" t="s">
+      <c r="B74" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="78"/>
-      <c r="D74" s="79" t="s">
+      <c r="C74" s="75"/>
+      <c r="D74" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="E74" s="78" t="s">
+      <c r="E74" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="F74" s="78" t="s">
+      <c r="F74" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="G74" s="78" t="s">
+      <c r="G74" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="H74" s="80"/>
+      <c r="H74" s="77"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="81"/>
+      <c r="A75" s="78"/>
       <c r="B75" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C75" s="1"/>
-      <c r="D75" s="50" t="s">
+      <c r="D75" s="47" t="s">
         <v>118</v>
       </c>
       <c r="E75" s="1" t="s">
@@ -8272,101 +8301,101 @@
       <c r="G75" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H75" s="82"/>
+      <c r="H75" s="79"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="81"/>
+      <c r="A76" s="78"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
-      <c r="D76" s="47" t="s">
+      <c r="D76" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="E76" s="20" t="s">
+      <c r="E76" s="18" t="s">
         <v>73</v>
       </c>
       <c r="F76" s="1"/>
-      <c r="G76" s="25" t="s">
+      <c r="G76" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="H76" s="82"/>
+      <c r="H76" s="79"/>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="81"/>
+      <c r="A77" s="78"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
-      <c r="D77" s="48" t="s">
+      <c r="D77" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E77" s="21" t="s">
+      <c r="E77" s="19" t="s">
         <v>124</v>
       </c>
       <c r="F77" s="1"/>
-      <c r="G77" s="26" t="s">
+      <c r="G77" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H77" s="82"/>
+      <c r="H77" s="79"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="81"/>
+      <c r="A78" s="78"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
-      <c r="D78" s="48" t="s">
+      <c r="D78" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="E78" s="21"/>
+      <c r="E78" s="19"/>
       <c r="F78" s="1"/>
       <c r="G78" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H78" s="82"/>
+      <c r="H78" s="79"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="83"/>
-      <c r="B79" s="84"/>
-      <c r="C79" s="84"/>
-      <c r="D79" s="85" t="s">
+      <c r="A79" s="80"/>
+      <c r="B79" s="81"/>
+      <c r="C79" s="81"/>
+      <c r="D79" s="82" t="s">
         <v>104</v>
       </c>
-      <c r="E79" s="86"/>
-      <c r="F79" s="84"/>
-      <c r="G79" s="84" t="s">
+      <c r="E79" s="83"/>
+      <c r="F79" s="81"/>
+      <c r="G79" s="81" t="s">
         <v>126</v>
       </c>
-      <c r="H79" s="87"/>
+      <c r="H79" s="84"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="70" t="s">
+      <c r="A80" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="B80" s="31" t="s">
+      <c r="B80" s="27" t="s">
         <v>34</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="34" t="s">
+      <c r="G80" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H80" s="13"/>
+      <c r="H80" s="12"/>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="69"/>
-      <c r="B81" s="31" t="s">
+      <c r="A81" s="66"/>
+      <c r="B81" s="27" t="s">
         <v>95</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="34" t="s">
+      <c r="G81" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="H81" s="13"/>
+      <c r="H81" s="12"/>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="69"/>
-      <c r="B82" s="31"/>
+      <c r="A82" s="66"/>
+      <c r="B82" s="27"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -8374,110 +8403,110 @@
       <c r="G82" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H82" s="13"/>
+      <c r="H82" s="12"/>
     </row>
     <row r="83" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A83" s="61"/>
-      <c r="B83" s="30"/>
-      <c r="C83" s="11"/>
-      <c r="D83" s="11"/>
-      <c r="E83" s="11"/>
-      <c r="F83" s="11"/>
-      <c r="G83" s="11" t="s">
+      <c r="A83" s="58"/>
+      <c r="B83" s="26"/>
+      <c r="C83" s="10"/>
+      <c r="D83" s="10"/>
+      <c r="E83" s="10"/>
+      <c r="F83" s="10"/>
+      <c r="G83" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="H83" s="12"/>
+      <c r="H83" s="11"/>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="60" t="s">
+      <c r="A84" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="27" t="s">
+      <c r="B84" s="7"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="9"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="8"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A85" s="61"/>
-      <c r="B85" s="11"/>
-      <c r="C85" s="11"/>
-      <c r="D85" s="28" t="s">
+      <c r="A85" s="58"/>
+      <c r="B85" s="10"/>
+      <c r="C85" s="10"/>
+      <c r="D85" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="E85" s="11"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="11"/>
-      <c r="H85" s="12"/>
+      <c r="E85" s="10"/>
+      <c r="F85" s="10"/>
+      <c r="G85" s="10"/>
+      <c r="H85" s="11"/>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="60" t="s">
+      <c r="A86" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
-      <c r="G86" s="27" t="s">
+      <c r="B86" s="7"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="7"/>
+      <c r="G86" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H86" s="9"/>
+      <c r="H86" s="8"/>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="69"/>
+      <c r="A87" s="66"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="26" t="s">
+      <c r="G87" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="H87" s="13"/>
+      <c r="H87" s="12"/>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="69"/>
+      <c r="A88" s="66"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
-      <c r="G88" s="25" t="s">
+      <c r="G88" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="H88" s="13"/>
+      <c r="H88" s="12"/>
     </row>
     <row r="89" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A89" s="61"/>
-      <c r="B89" s="11"/>
-      <c r="C89" s="11"/>
-      <c r="D89" s="11"/>
-      <c r="E89" s="11"/>
-      <c r="F89" s="11"/>
-      <c r="G89" s="28" t="s">
+      <c r="A89" s="58"/>
+      <c r="B89" s="10"/>
+      <c r="C89" s="10"/>
+      <c r="D89" s="10"/>
+      <c r="E89" s="10"/>
+      <c r="F89" s="10"/>
+      <c r="G89" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="H89" s="12"/>
+      <c r="H89" s="11"/>
     </row>
     <row r="90" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A90" s="14" t="s">
+      <c r="A90" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="B90" s="63"/>
-      <c r="C90" s="64"/>
-      <c r="D90" s="64"/>
-      <c r="E90" s="64"/>
-      <c r="F90" s="64"/>
-      <c r="G90" s="64"/>
-      <c r="H90" s="65"/>
+      <c r="B90" s="60"/>
+      <c r="C90" s="61"/>
+      <c r="D90" s="61"/>
+      <c r="E90" s="61"/>
+      <c r="F90" s="61"/>
+      <c r="G90" s="61"/>
+      <c r="H90" s="62"/>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="70" t="s">
+      <c r="A91" s="67" t="s">
         <v>133</v>
       </c>
       <c r="B91" s="1"/>
@@ -8490,60 +8519,60 @@
         <v>21</v>
       </c>
       <c r="G91" s="1"/>
-      <c r="H91" s="13" t="s">
+      <c r="H91" s="12" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A92" s="61"/>
-      <c r="B92" s="11"/>
-      <c r="C92" s="11"/>
-      <c r="D92" s="11" t="s">
+      <c r="A92" s="58"/>
+      <c r="B92" s="10"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E92" s="11"/>
-      <c r="F92" s="11" t="s">
+      <c r="E92" s="10"/>
+      <c r="F92" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="G92" s="11"/>
-      <c r="H92" s="12" t="s">
+      <c r="G92" s="10"/>
+      <c r="H92" s="11" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="60" t="s">
+      <c r="A93" s="57" t="s">
         <v>136</v>
       </c>
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="27" t="s">
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="9"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="8"/>
     </row>
     <row r="94" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A94" s="61"/>
-      <c r="B94" s="11"/>
-      <c r="C94" s="11"/>
-      <c r="D94" s="28" t="s">
+      <c r="A94" s="58"/>
+      <c r="B94" s="10"/>
+      <c r="C94" s="10"/>
+      <c r="D94" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="E94" s="11"/>
-      <c r="F94" s="11"/>
-      <c r="G94" s="11"/>
-      <c r="H94" s="12"/>
+      <c r="E94" s="10"/>
+      <c r="F94" s="10"/>
+      <c r="G94" s="10"/>
+      <c r="H94" s="11"/>
     </row>
     <row r="95" spans="1:8" ht="6.75" customHeight="1">
-      <c r="B95" s="62"/>
-      <c r="C95" s="62"/>
-      <c r="D95" s="62"/>
-      <c r="E95" s="62"/>
-      <c r="F95" s="62"/>
-      <c r="G95" s="62"/>
-      <c r="H95" s="62"/>
+      <c r="B95" s="59"/>
+      <c r="C95" s="59"/>
+      <c r="D95" s="59"/>
+      <c r="E95" s="59"/>
+      <c r="F95" s="59"/>
+      <c r="G95" s="59"/>
+      <c r="H95" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -8595,23 +8624,23 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="72" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="B5" s="76" t="s">
+      <c r="B5" s="73" t="s">
         <v>139</v>
       </c>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -8628,492 +8657,492 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="56">
-        <v>0</v>
-      </c>
-      <c r="C7" s="56">
-        <v>0</v>
-      </c>
-      <c r="D7" s="56">
-        <v>0</v>
-      </c>
-      <c r="E7" s="56">
+      <c r="B7" s="53">
+        <v>0</v>
+      </c>
+      <c r="C7" s="53">
+        <v>0</v>
+      </c>
+      <c r="D7" s="53">
+        <v>0</v>
+      </c>
+      <c r="E7" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="56">
-        <v>0</v>
-      </c>
-      <c r="C8" s="56">
-        <v>0</v>
-      </c>
-      <c r="D8" s="56">
-        <v>0</v>
-      </c>
-      <c r="E8" s="56">
+      <c r="B8" s="53">
+        <v>0</v>
+      </c>
+      <c r="C8" s="53">
+        <v>0</v>
+      </c>
+      <c r="D8" s="53">
+        <v>0</v>
+      </c>
+      <c r="E8" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="56">
-        <v>0</v>
-      </c>
-      <c r="C9" s="56">
+      <c r="B9" s="53">
+        <v>0</v>
+      </c>
+      <c r="C9" s="53">
         <v>4.1667000000000003E-2</v>
       </c>
-      <c r="D9" s="56">
-        <v>0</v>
-      </c>
-      <c r="E9" s="56">
+      <c r="D9" s="53">
+        <v>0</v>
+      </c>
+      <c r="E9" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="56">
-        <v>0</v>
-      </c>
-      <c r="C10" s="56">
-        <v>0</v>
-      </c>
-      <c r="D10" s="56">
-        <v>0</v>
-      </c>
-      <c r="E10" s="56">
+      <c r="B10" s="53">
+        <v>0</v>
+      </c>
+      <c r="C10" s="53">
+        <v>0</v>
+      </c>
+      <c r="D10" s="53">
+        <v>0</v>
+      </c>
+      <c r="E10" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="56">
-        <v>0</v>
-      </c>
-      <c r="C11" s="56">
-        <v>0</v>
-      </c>
-      <c r="D11" s="56">
-        <v>0</v>
-      </c>
-      <c r="E11" s="56">
+      <c r="B11" s="53">
+        <v>0</v>
+      </c>
+      <c r="C11" s="53">
+        <v>0</v>
+      </c>
+      <c r="D11" s="53">
+        <v>0</v>
+      </c>
+      <c r="E11" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="56">
-        <v>0</v>
-      </c>
-      <c r="C12" s="56">
-        <v>0</v>
-      </c>
-      <c r="D12" s="56">
-        <v>0</v>
-      </c>
-      <c r="E12" s="56">
+      <c r="B12" s="53">
+        <v>0</v>
+      </c>
+      <c r="C12" s="53">
+        <v>0</v>
+      </c>
+      <c r="D12" s="53">
+        <v>0</v>
+      </c>
+      <c r="E12" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="56">
-        <v>0</v>
-      </c>
-      <c r="C13" s="56">
-        <v>0</v>
-      </c>
-      <c r="D13" s="56">
+      <c r="B13" s="53">
+        <v>0</v>
+      </c>
+      <c r="C13" s="53">
+        <v>0</v>
+      </c>
+      <c r="D13" s="53">
         <v>0.24166699999999999</v>
       </c>
-      <c r="E13" s="56">
+      <c r="E13" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="56">
-        <v>0</v>
-      </c>
-      <c r="C14" s="56">
-        <v>0</v>
-      </c>
-      <c r="D14" s="56">
-        <v>0</v>
-      </c>
-      <c r="E14" s="56">
+      <c r="B14" s="53">
+        <v>0</v>
+      </c>
+      <c r="C14" s="53">
+        <v>0</v>
+      </c>
+      <c r="D14" s="53">
+        <v>0</v>
+      </c>
+      <c r="E14" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="56">
-        <v>0</v>
-      </c>
-      <c r="C15" s="56">
-        <v>0</v>
-      </c>
-      <c r="D15" s="56">
-        <v>0</v>
-      </c>
-      <c r="E15" s="56">
+      <c r="B15" s="53">
+        <v>0</v>
+      </c>
+      <c r="C15" s="53">
+        <v>0</v>
+      </c>
+      <c r="D15" s="53">
+        <v>0</v>
+      </c>
+      <c r="E15" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="56">
+      <c r="B16" s="53">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="C16" s="56">
+      <c r="C16" s="53">
         <v>8.3334000000000005E-2</v>
       </c>
-      <c r="D16" s="56">
-        <v>0</v>
-      </c>
-      <c r="E16" s="56">
+      <c r="D16" s="53">
+        <v>0</v>
+      </c>
+      <c r="E16" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="B17" s="56">
-        <v>0</v>
-      </c>
-      <c r="C17" s="56">
-        <v>0</v>
-      </c>
-      <c r="D17" s="56">
-        <v>0</v>
-      </c>
-      <c r="E17" s="56">
+      <c r="B17" s="53">
+        <v>0</v>
+      </c>
+      <c r="C17" s="53">
+        <v>0</v>
+      </c>
+      <c r="D17" s="53">
+        <v>0</v>
+      </c>
+      <c r="E17" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="B18" s="56">
-        <v>0</v>
-      </c>
-      <c r="C18" s="56">
-        <v>0</v>
-      </c>
-      <c r="D18" s="56">
-        <v>0</v>
-      </c>
-      <c r="E18" s="56">
+      <c r="B18" s="53">
+        <v>0</v>
+      </c>
+      <c r="C18" s="53">
+        <v>0</v>
+      </c>
+      <c r="D18" s="53">
+        <v>0</v>
+      </c>
+      <c r="E18" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="56">
-        <v>0</v>
-      </c>
-      <c r="C19" s="56">
-        <v>0</v>
-      </c>
-      <c r="D19" s="56">
-        <v>0</v>
-      </c>
-      <c r="E19" s="56">
+      <c r="B19" s="53">
+        <v>0</v>
+      </c>
+      <c r="C19" s="53">
+        <v>0</v>
+      </c>
+      <c r="D19" s="53">
+        <v>0</v>
+      </c>
+      <c r="E19" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="B20" s="56">
-        <v>0</v>
-      </c>
-      <c r="C20" s="56">
-        <v>0</v>
-      </c>
-      <c r="D20" s="56">
-        <v>0</v>
-      </c>
-      <c r="E20" s="56">
+      <c r="B20" s="53">
+        <v>0</v>
+      </c>
+      <c r="C20" s="53">
+        <v>0</v>
+      </c>
+      <c r="D20" s="53">
+        <v>0</v>
+      </c>
+      <c r="E20" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="56">
-        <v>0</v>
-      </c>
-      <c r="C21" s="56">
-        <v>0</v>
-      </c>
-      <c r="D21" s="56">
-        <v>0</v>
-      </c>
-      <c r="E21" s="56">
+      <c r="B21" s="53">
+        <v>0</v>
+      </c>
+      <c r="C21" s="53">
+        <v>0</v>
+      </c>
+      <c r="D21" s="53">
+        <v>0</v>
+      </c>
+      <c r="E21" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="56">
-        <v>0</v>
-      </c>
-      <c r="C22" s="56">
-        <v>0</v>
-      </c>
-      <c r="D22" s="56">
-        <v>0</v>
-      </c>
-      <c r="E22" s="56">
+      <c r="B22" s="53">
+        <v>0</v>
+      </c>
+      <c r="C22" s="53">
+        <v>0</v>
+      </c>
+      <c r="D22" s="53">
+        <v>0</v>
+      </c>
+      <c r="E22" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="B23" s="56">
-        <v>0</v>
-      </c>
-      <c r="C23" s="56">
-        <v>0</v>
-      </c>
-      <c r="D23" s="56">
-        <v>0</v>
-      </c>
-      <c r="E23" s="56">
+      <c r="B23" s="53">
+        <v>0</v>
+      </c>
+      <c r="C23" s="53">
+        <v>0</v>
+      </c>
+      <c r="D23" s="53">
+        <v>0</v>
+      </c>
+      <c r="E23" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="56">
-        <v>0</v>
-      </c>
-      <c r="C24" s="56">
-        <v>0</v>
-      </c>
-      <c r="D24" s="56">
+      <c r="B24" s="53">
+        <v>0</v>
+      </c>
+      <c r="C24" s="53">
+        <v>0</v>
+      </c>
+      <c r="D24" s="53">
         <v>0.25</v>
       </c>
-      <c r="E24" s="56">
+      <c r="E24" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="56">
-        <v>0</v>
-      </c>
-      <c r="C25" s="56">
+      <c r="B25" s="53">
+        <v>0</v>
+      </c>
+      <c r="C25" s="53">
         <v>0.45833400000000002</v>
       </c>
-      <c r="D25" s="56">
-        <v>0</v>
-      </c>
-      <c r="E25" s="56">
+      <c r="D25" s="53">
+        <v>0</v>
+      </c>
+      <c r="E25" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="B26" s="56">
-        <v>0</v>
-      </c>
-      <c r="C26" s="56">
+      <c r="B26" s="53">
+        <v>0</v>
+      </c>
+      <c r="C26" s="53">
         <v>0.16666700000000001</v>
       </c>
-      <c r="D26" s="56">
+      <c r="D26" s="53">
         <v>8.3334000000000005E-2</v>
       </c>
-      <c r="E26" s="56">
+      <c r="E26" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="56">
-        <v>0</v>
-      </c>
-      <c r="C27" s="56">
-        <v>0</v>
-      </c>
-      <c r="D27" s="56">
-        <v>0</v>
-      </c>
-      <c r="E27" s="56">
+      <c r="B27" s="53">
+        <v>0</v>
+      </c>
+      <c r="C27" s="53">
+        <v>0</v>
+      </c>
+      <c r="D27" s="53">
+        <v>0</v>
+      </c>
+      <c r="E27" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="56">
-        <v>0</v>
-      </c>
-      <c r="C28" s="56">
-        <v>0</v>
-      </c>
-      <c r="D28" s="56">
-        <v>0</v>
-      </c>
-      <c r="E28" s="56">
+      <c r="B28" s="53">
+        <v>0</v>
+      </c>
+      <c r="C28" s="53">
+        <v>0</v>
+      </c>
+      <c r="D28" s="53">
+        <v>0</v>
+      </c>
+      <c r="E28" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="B29" s="56">
-        <v>0</v>
-      </c>
-      <c r="C29" s="56">
+      <c r="B29" s="53">
+        <v>0</v>
+      </c>
+      <c r="C29" s="53">
         <v>0.125</v>
       </c>
-      <c r="D29" s="56">
+      <c r="D29" s="53">
         <v>0.159723</v>
       </c>
-      <c r="E29" s="56">
+      <c r="E29" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="24" t="s">
+      <c r="A30" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="B30" s="56">
-        <v>0</v>
-      </c>
-      <c r="C30" s="56">
-        <v>0</v>
-      </c>
-      <c r="D30" s="56">
-        <v>0</v>
-      </c>
-      <c r="E30" s="56">
+      <c r="B30" s="53">
+        <v>0</v>
+      </c>
+      <c r="C30" s="53">
+        <v>0</v>
+      </c>
+      <c r="D30" s="53">
+        <v>0</v>
+      </c>
+      <c r="E30" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="B31" s="56">
-        <v>0</v>
-      </c>
-      <c r="C31" s="56">
-        <v>0</v>
-      </c>
-      <c r="D31" s="56">
-        <v>0</v>
-      </c>
-      <c r="E31" s="56">
+      <c r="B31" s="53">
+        <v>0</v>
+      </c>
+      <c r="C31" s="53">
+        <v>0</v>
+      </c>
+      <c r="D31" s="53">
+        <v>0</v>
+      </c>
+      <c r="E31" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="24" t="s">
+      <c r="A32" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="B32" s="56">
-        <v>0</v>
-      </c>
-      <c r="C32" s="56">
-        <v>0</v>
-      </c>
-      <c r="D32" s="56">
-        <v>0</v>
-      </c>
-      <c r="E32" s="56">
+      <c r="B32" s="53">
+        <v>0</v>
+      </c>
+      <c r="C32" s="53">
+        <v>0</v>
+      </c>
+      <c r="D32" s="53">
+        <v>0</v>
+      </c>
+      <c r="E32" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="24" t="s">
+      <c r="A33" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="56">
-        <v>0</v>
-      </c>
-      <c r="C33" s="56">
-        <v>0</v>
-      </c>
-      <c r="D33" s="56">
-        <v>0</v>
-      </c>
-      <c r="E33" s="56">
+      <c r="B33" s="53">
+        <v>0</v>
+      </c>
+      <c r="C33" s="53">
+        <v>0</v>
+      </c>
+      <c r="D33" s="53">
+        <v>0</v>
+      </c>
+      <c r="E33" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="B34" s="56">
-        <v>0</v>
-      </c>
-      <c r="C34" s="56">
-        <v>0</v>
-      </c>
-      <c r="D34" s="56">
-        <v>0</v>
-      </c>
-      <c r="E34" s="56">
+      <c r="B34" s="53">
+        <v>0</v>
+      </c>
+      <c r="C34" s="53">
+        <v>0</v>
+      </c>
+      <c r="D34" s="53">
+        <v>0</v>
+      </c>
+      <c r="E34" s="53">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="B35" s="57">
+      <c r="B35" s="54">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="C35" s="57">
+      <c r="C35" s="54">
         <v>0.875</v>
       </c>
-      <c r="D35" s="57">
+      <c r="D35" s="54">
         <v>0.73472300000000001</v>
       </c>
-      <c r="E35" s="57">
+      <c r="E35" s="54">
         <v>0</v>
       </c>
     </row>
@@ -9137,40 +9166,40 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="56" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="55" t="s">
         <v>148</v>
       </c>
-      <c r="B5" s="59"/>
+      <c r="B5" s="56"/>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="56" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="56" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="56" t="s">
         <v>153</v>
       </c>
     </row>

--- a/Plannings 2026 S14.xlsx
+++ b/Plannings 2026 S14.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{150E33BF-47F0-4B68-8AA0-FBA696D166AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E34CF0FB-B08D-48F5-A778-D31CC4122B8E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29799D5C-DD60-45E8-8D29-B1A26F276513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="155">
   <si>
     <t>Mars-2026</t>
   </si>
@@ -500,6 +500,9 @@
   </si>
   <si>
     <t>19/03/2026 12:22</t>
+  </si>
+  <si>
+    <t>INVETAIRE // EDF // LEAGUES</t>
   </si>
 </sst>
 </file>
@@ -509,7 +512,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -635,7 +638,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1064,11 +1067,68 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1083,9 +1143,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1121,9 +1178,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1131,12 +1185,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1208,6 +1256,9 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1247,6 +1298,45 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1274,19 +1364,40 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1298,41 +1409,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3313,50 +3389,6 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7082,36 +7114,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H95"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="48" customWidth="1"/>
+    <col min="1" max="8" width="49.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="B1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="87" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="B2" s="73" t="s">
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
@@ -7119,7 +7151,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>4</v>
+        <v>154</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>5</v>
@@ -7134,7 +7166,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" thickBot="1">
+    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -7160,82 +7192,82 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="60" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="27" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="9"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A6" s="61"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="28" t="s">
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="71"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="12"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="60" t="s">
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="9"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A8" s="61"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="71"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="12"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="60" t="s">
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="7"/>
+      <c r="E9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="43" t="s">
+      <c r="F9" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="9" t="s">
+      <c r="G9" s="7"/>
+      <c r="H9" s="8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="69"/>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="80"/>
       <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
@@ -7246,17 +7278,17 @@
       <c r="E10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F10" s="42" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="12" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="69"/>
-      <c r="B11" s="29" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="80"/>
+      <c r="B11" s="25" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="1"/>
@@ -7268,11 +7300,11 @@
         <v>21</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="69"/>
-      <c r="B12" s="31" t="s">
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="80"/>
+      <c r="B12" s="27" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="1"/>
@@ -7280,84 +7312,84 @@
       <c r="E12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="45" t="s">
+      <c r="F12" s="41" t="s">
         <v>33</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="H12" s="13"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="69"/>
-      <c r="B13" s="29" t="s">
+      <c r="H12" s="12"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="80"/>
+      <c r="B13" s="25" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="25" t="s">
         <v>30</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A14" s="61"/>
-      <c r="B14" s="30" t="s">
+      <c r="H13" s="12"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="71"/>
+      <c r="B14" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="30" t="s">
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="12"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="60" t="s">
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="9"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A16" s="61"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11" t="s">
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="71"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="12"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A17" s="14" t="s">
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="11"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="63"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="65"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="60" t="s">
+      <c r="B17" s="73"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="75"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="70" t="s">
         <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -7378,8 +7410,8 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="74"/>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="91"/>
       <c r="B19" s="1" t="s">
         <v>41</v>
       </c>
@@ -7398,8 +7430,8 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="74"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="91"/>
       <c r="B20" s="1"/>
       <c r="C20" s="2" t="s">
         <v>21</v>
@@ -7410,8 +7442,8 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A21" s="61"/>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="71"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
         <v>44</v>
@@ -7422,28 +7454,28 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="60" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8" t="s">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8" t="s">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="33" t="s">
+      <c r="F22" s="7"/>
+      <c r="G22" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="38" t="s">
+      <c r="H22" s="34" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="69"/>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="80"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
         <v>47</v>
@@ -7453,15 +7485,15 @@
         <v>48</v>
       </c>
       <c r="F23" s="1"/>
-      <c r="G23" s="34" t="s">
+      <c r="G23" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="H23" s="37" t="s">
+      <c r="H23" s="33" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="69"/>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="80"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -7470,260 +7502,260 @@
       <c r="G24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="15" t="s">
+      <c r="H24" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A25" s="61"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11" t="s">
+    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="71"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="H25" s="11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="72" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="85" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="36" t="s">
         <v>54</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E26" s="40" t="s">
+      <c r="E26" s="36" t="s">
         <v>54</v>
       </c>
       <c r="F26" s="1"/>
-      <c r="G26" s="20" t="s">
+      <c r="G26" s="18" t="s">
         <v>56</v>
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="72"/>
-      <c r="B27" s="39" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="85"/>
+      <c r="B27" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="35" t="s">
         <v>57</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="39" t="s">
+      <c r="E27" s="35" t="s">
         <v>57</v>
       </c>
       <c r="F27" s="1"/>
-      <c r="G27" s="21" t="s">
+      <c r="G27" s="19" t="s">
         <v>59</v>
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="72"/>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="85"/>
       <c r="B28" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="40" t="s">
+      <c r="D28" s="36" t="s">
         <v>54</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>60</v>
       </c>
       <c r="F28" s="1"/>
-      <c r="G28" s="21"/>
+      <c r="G28" s="19"/>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="72"/>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="85"/>
       <c r="B29" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="39" t="s">
+      <c r="D29" s="35" t="s">
         <v>63</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F29" s="1"/>
-      <c r="G29" s="21"/>
+      <c r="G29" s="19"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="72"/>
-      <c r="B30" s="20" t="s">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="85"/>
+      <c r="B30" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C30" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="25" t="s">
+      <c r="D30" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E30" s="40" t="s">
+      <c r="E30" s="36" t="s">
         <v>54</v>
       </c>
       <c r="F30" s="1"/>
-      <c r="G30" s="21"/>
+      <c r="G30" s="19"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="72"/>
-      <c r="B31" s="21" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="85"/>
+      <c r="B31" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="D31" s="26" t="s">
+      <c r="D31" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="E31" s="39" t="s">
+      <c r="E31" s="35" t="s">
         <v>67</v>
       </c>
       <c r="F31" s="1"/>
-      <c r="G31" s="21"/>
+      <c r="G31" s="19"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="72"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="26"/>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="85"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="22"/>
       <c r="E32" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F32" s="1"/>
-      <c r="G32" s="21"/>
+      <c r="G32" s="19"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A33" s="72"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="26"/>
+    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="85"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="22"/>
       <c r="E33" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F33" s="1"/>
-      <c r="G33" s="21"/>
+      <c r="G33" s="19"/>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="60" t="s">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="27" t="s">
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="61"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="28" t="s">
+      <c r="H34" s="8"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="81"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="22" t="s">
         <v>19</v>
       </c>
       <c r="H35" s="12"/>
     </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="60" t="s">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="88" t="s">
+      <c r="C36" s="57"/>
+      <c r="D36" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="F36" s="27" t="s">
+      <c r="F36" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="G36" s="8"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="69"/>
-      <c r="B37" s="19" t="s">
+      <c r="G36" s="57"/>
+      <c r="H36" s="59"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="83"/>
+      <c r="B37" s="17" t="s">
         <v>74</v>
       </c>
       <c r="C37" s="1"/>
-      <c r="D37" s="89" t="s">
+      <c r="D37" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="E37" s="21" t="s">
+      <c r="E37" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="26" t="s">
+      <c r="F37" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G37" s="1"/>
-      <c r="H37" s="13"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="69"/>
-      <c r="B38" s="25" t="s">
+      <c r="H37" s="60"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="83"/>
+      <c r="B38" s="21" t="s">
         <v>18</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="27" t="s">
+      <c r="D38" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="E38" s="21"/>
+      <c r="E38" s="19"/>
       <c r="F38" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G38" s="1"/>
-      <c r="H38" s="13"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="69"/>
-      <c r="B39" s="26" t="s">
+      <c r="H38" s="60"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="83"/>
+      <c r="B39" s="22" t="s">
         <v>77</v>
       </c>
       <c r="C39" s="1"/>
-      <c r="D39" s="26" t="s">
+      <c r="D39" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="E39" s="21"/>
+      <c r="E39" s="19"/>
       <c r="F39" s="1" t="s">
         <v>80</v>
       </c>
       <c r="G39" s="1"/>
-      <c r="H39" s="13"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="69"/>
+      <c r="H39" s="60"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="83"/>
       <c r="B40" s="2" t="s">
         <v>21</v>
       </c>
@@ -7731,13 +7763,13 @@
       <c r="D40" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E40" s="21"/>
+      <c r="E40" s="19"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="H40" s="13"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="69"/>
+      <c r="H40" s="60"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="83"/>
       <c r="B41" s="1" t="s">
         <v>81</v>
       </c>
@@ -7745,317 +7777,317 @@
       <c r="D41" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E41" s="21"/>
+      <c r="E41" s="19"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-      <c r="H41" s="13"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="69"/>
+      <c r="H41" s="60"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="83"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="25" t="s">
+      <c r="D42" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="E42" s="21"/>
+      <c r="E42" s="19"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="13"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="71"/>
+      <c r="H42" s="60"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="86"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
-      <c r="D43" s="26" t="s">
+      <c r="D43" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="E43" s="21"/>
+      <c r="E43" s="19"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
-      <c r="H43" s="13"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="71"/>
+      <c r="H43" s="60"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="86"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
-      <c r="D44" s="29" t="s">
+      <c r="D44" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="E44" s="21"/>
+      <c r="E44" s="19"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
-      <c r="H44" s="13"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="61"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="31" t="s">
+      <c r="H44" s="60"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="84"/>
+      <c r="B45" s="61"/>
+      <c r="C45" s="61"/>
+      <c r="D45" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="E45" s="23"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="12"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="6" t="s">
+      <c r="E45" s="63"/>
+      <c r="F45" s="61"/>
+      <c r="G45" s="61"/>
+      <c r="H45" s="64"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="B46" s="63"/>
-      <c r="C46" s="64"/>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="64"/>
-      <c r="G46" s="64"/>
-      <c r="H46" s="65"/>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A47" s="14" t="s">
+      <c r="B46" s="88"/>
+      <c r="C46" s="89"/>
+      <c r="D46" s="89"/>
+      <c r="E46" s="89"/>
+      <c r="F46" s="89"/>
+      <c r="G46" s="89"/>
+      <c r="H46" s="90"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B47" s="63"/>
-      <c r="C47" s="64"/>
-      <c r="D47" s="64"/>
-      <c r="E47" s="64"/>
-      <c r="F47" s="64"/>
-      <c r="G47" s="64"/>
-      <c r="H47" s="65"/>
-    </row>
-    <row r="48" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A48" s="14" t="s">
+      <c r="B47" s="73"/>
+      <c r="C47" s="74"/>
+      <c r="D47" s="74"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="74"/>
+      <c r="H47" s="75"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B48" s="63"/>
-      <c r="C48" s="64"/>
-      <c r="D48" s="64"/>
-      <c r="E48" s="64"/>
-      <c r="F48" s="64"/>
-      <c r="G48" s="64"/>
-      <c r="H48" s="65"/>
-    </row>
-    <row r="49" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A49" s="16" t="s">
+      <c r="B48" s="73"/>
+      <c r="C48" s="74"/>
+      <c r="D48" s="74"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="74"/>
+      <c r="H48" s="75"/>
+    </row>
+    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="B49" s="66"/>
-      <c r="C49" s="67"/>
-      <c r="D49" s="67"/>
-      <c r="E49" s="67"/>
-      <c r="F49" s="67"/>
-      <c r="G49" s="67"/>
-      <c r="H49" s="68"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="60" t="s">
+      <c r="B49" s="76"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="77"/>
+      <c r="E49" s="77"/>
+      <c r="F49" s="77"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="78"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="27" t="s">
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="G50" s="8"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A51" s="61"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="28" t="s">
+      <c r="G50" s="7"/>
+      <c r="H50" s="8"/>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="71"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="G51" s="11"/>
-      <c r="H51" s="12"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="60" t="s">
+      <c r="G51" s="10"/>
+      <c r="H51" s="11"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="70" t="s">
         <v>90</v>
       </c>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="9" t="s">
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="69"/>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="80"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
-      <c r="H53" s="13" t="s">
+      <c r="H53" s="12" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="69"/>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="80"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-      <c r="H54" s="35" t="s">
+      <c r="H54" s="31" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="69"/>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="80"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
-      <c r="H55" s="37" t="s">
+      <c r="H55" s="33" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="69"/>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="80"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
-      <c r="H56" s="15" t="s">
+      <c r="H56" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="69"/>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="80"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
-      <c r="H57" s="13" t="s">
+      <c r="H57" s="12" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="69"/>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="80"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
-      <c r="H58" s="35" t="s">
+      <c r="H58" s="31" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A59" s="61"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="36" t="s">
+    <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="71"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="32" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="60" t="s">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="B60" s="32" t="s">
+      <c r="B60" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="C60" s="32" t="s">
+      <c r="C60" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D60" s="32" t="s">
+      <c r="D60" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="E60" s="32" t="s">
+      <c r="E60" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="9"/>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="61"/>
-      <c r="B61" s="30" t="s">
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="8"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="71"/>
+      <c r="B61" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="C61" s="30" t="s">
+      <c r="C61" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="D61" s="30" t="s">
+      <c r="D61" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="E61" s="30" t="s">
+      <c r="E61" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="12"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="60" t="s">
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="11"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C62" s="43" t="s">
+      <c r="C62" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="D62" s="27" t="s">
+      <c r="D62" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="E62" s="49" t="s">
+      <c r="E62" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="F62" s="54" t="s">
+      <c r="F62" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="G62" s="27" t="s">
+      <c r="G62" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H62" s="9"/>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="69"/>
+      <c r="H62" s="8"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="80"/>
       <c r="B63" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C63" s="44" t="s">
+      <c r="C63" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="D63" s="26" t="s">
+      <c r="D63" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="E63" s="50" t="s">
+      <c r="E63" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="F63" s="55" t="s">
+      <c r="F63" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="G63" s="26" t="s">
+      <c r="G63" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="H63" s="13"/>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="69"/>
+      <c r="H63" s="12"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="80"/>
       <c r="B64" s="1"/>
       <c r="C64" s="2" t="s">
         <v>21</v>
@@ -8063,19 +8095,19 @@
       <c r="D64" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E64" s="47" t="s">
+      <c r="E64" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="F64" s="55" t="s">
+      <c r="F64" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G64" s="25" t="s">
+      <c r="G64" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="H64" s="13"/>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="69"/>
+      <c r="H64" s="12"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="80"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
         <v>105</v>
@@ -8083,184 +8115,184 @@
       <c r="D65" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E65" s="53" t="s">
+      <c r="E65" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="F65" s="55" t="s">
+      <c r="F65" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G65" s="26" t="s">
+      <c r="G65" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="H65" s="13"/>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="69"/>
+      <c r="H65" s="12"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="80"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="25" t="s">
+      <c r="C66" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="D66" s="29" t="s">
+      <c r="D66" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="E66" s="51" t="s">
+      <c r="E66" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="F66" s="55" t="s">
+      <c r="F66" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G66" s="25" t="s">
+      <c r="G66" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="H66" s="13"/>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="69"/>
+      <c r="H66" s="12"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="80"/>
       <c r="B67" s="1"/>
-      <c r="C67" s="26" t="s">
+      <c r="C67" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="D67" s="31" t="s">
+      <c r="D67" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="E67" s="52" t="s">
+      <c r="E67" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="F67" s="55" t="s">
+      <c r="F67" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G67" s="26" t="s">
+      <c r="G67" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="H67" s="13"/>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="69"/>
+      <c r="H67" s="12"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="80"/>
       <c r="B68" s="1"/>
-      <c r="C68" s="29" t="s">
+      <c r="C68" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D68" s="31"/>
-      <c r="E68" s="47" t="s">
+      <c r="D68" s="27"/>
+      <c r="E68" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="F68" s="55" t="s">
+      <c r="F68" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G68" s="42" t="s">
+      <c r="G68" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="H68" s="13"/>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="69"/>
+      <c r="H68" s="12"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="80"/>
       <c r="B69" s="1"/>
-      <c r="C69" s="31" t="s">
+      <c r="C69" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="D69" s="31"/>
-      <c r="E69" s="48" t="s">
+      <c r="D69" s="27"/>
+      <c r="E69" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="F69" s="55" t="s">
+      <c r="F69" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G69" s="34" t="s">
+      <c r="G69" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="H69" s="13"/>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="69"/>
+      <c r="H69" s="12"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="80"/>
       <c r="B70" s="1"/>
       <c r="C70" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D70" s="31"/>
-      <c r="E70" s="48" t="s">
+      <c r="D70" s="27"/>
+      <c r="E70" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="F70" s="55" t="s">
+      <c r="F70" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G70" s="34"/>
-      <c r="H70" s="13"/>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="61"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11" t="s">
+      <c r="G70" s="30"/>
+      <c r="H70" s="12"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="71"/>
+      <c r="B71" s="10"/>
+      <c r="C71" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="D71" s="30"/>
-      <c r="E71" s="48" t="s">
+      <c r="D71" s="26"/>
+      <c r="E71" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="F71" s="55" t="s">
+      <c r="F71" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="G71" s="41"/>
-      <c r="H71" s="12"/>
-    </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="60" t="s">
+      <c r="G71" s="37"/>
+      <c r="H71" s="11"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="B72" s="8"/>
-      <c r="C72" s="27" t="s">
+      <c r="B72" s="7"/>
+      <c r="C72" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="27" t="s">
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="G72" s="8"/>
-      <c r="H72" s="9"/>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="71"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="8"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="81"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="26" t="s">
+      <c r="C73" s="22" t="s">
         <v>77</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
-      <c r="F73" s="26" t="s">
+      <c r="F73" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G73" s="1"/>
-      <c r="H73" s="13"/>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="77" t="s">
+      <c r="H73" s="12"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="B74" s="78" t="s">
+      <c r="B74" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="78"/>
-      <c r="D74" s="79" t="s">
+      <c r="C74" s="57"/>
+      <c r="D74" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="E74" s="78" t="s">
+      <c r="E74" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="F74" s="78" t="s">
+      <c r="F74" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="G74" s="78" t="s">
+      <c r="G74" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="H74" s="80"/>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="81"/>
+      <c r="H74" s="59"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="83"/>
       <c r="B75" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C75" s="1"/>
-      <c r="D75" s="50" t="s">
+      <c r="D75" s="47" t="s">
         <v>118</v>
       </c>
       <c r="E75" s="1" t="s">
@@ -8272,101 +8304,101 @@
       <c r="G75" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H75" s="82"/>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="81"/>
+      <c r="H75" s="60"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="83"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
-      <c r="D76" s="47" t="s">
+      <c r="D76" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="E76" s="20" t="s">
+      <c r="E76" s="18" t="s">
         <v>73</v>
       </c>
       <c r="F76" s="1"/>
-      <c r="G76" s="25" t="s">
+      <c r="G76" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="H76" s="82"/>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="81"/>
+      <c r="H76" s="60"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="83"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
-      <c r="D77" s="48" t="s">
+      <c r="D77" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E77" s="21" t="s">
+      <c r="E77" s="19" t="s">
         <v>124</v>
       </c>
       <c r="F77" s="1"/>
-      <c r="G77" s="26" t="s">
+      <c r="G77" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="H77" s="82"/>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" s="81"/>
+      <c r="H77" s="60"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="83"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
-      <c r="D78" s="48" t="s">
+      <c r="D78" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="E78" s="21"/>
+      <c r="E78" s="19"/>
       <c r="F78" s="1"/>
       <c r="G78" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H78" s="82"/>
-    </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="83"/>
-      <c r="B79" s="84"/>
-      <c r="C79" s="84"/>
-      <c r="D79" s="85" t="s">
+      <c r="H78" s="60"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="84"/>
+      <c r="B79" s="61"/>
+      <c r="C79" s="61"/>
+      <c r="D79" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="E79" s="86"/>
-      <c r="F79" s="84"/>
-      <c r="G79" s="84" t="s">
+      <c r="E79" s="63"/>
+      <c r="F79" s="61"/>
+      <c r="G79" s="61" t="s">
         <v>126</v>
       </c>
-      <c r="H79" s="87"/>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="A80" s="70" t="s">
+      <c r="H79" s="64"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="79" t="s">
         <v>127</v>
       </c>
-      <c r="B80" s="31" t="s">
+      <c r="B80" s="27" t="s">
         <v>34</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="34" t="s">
+      <c r="G80" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H80" s="13"/>
-    </row>
-    <row r="81" spans="1:8">
-      <c r="A81" s="69"/>
-      <c r="B81" s="31" t="s">
+      <c r="H80" s="12"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="80"/>
+      <c r="B81" s="27" t="s">
         <v>95</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="34" t="s">
+      <c r="G81" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="H81" s="13"/>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82" s="69"/>
-      <c r="B82" s="31"/>
+      <c r="H81" s="12"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="80"/>
+      <c r="B82" s="27"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -8374,110 +8406,110 @@
       <c r="G82" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H82" s="13"/>
-    </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A83" s="61"/>
-      <c r="B83" s="30"/>
-      <c r="C83" s="11"/>
-      <c r="D83" s="11"/>
-      <c r="E83" s="11"/>
-      <c r="F83" s="11"/>
-      <c r="G83" s="11" t="s">
+      <c r="H82" s="12"/>
+    </row>
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="71"/>
+      <c r="B83" s="26"/>
+      <c r="C83" s="10"/>
+      <c r="D83" s="10"/>
+      <c r="E83" s="10"/>
+      <c r="F83" s="10"/>
+      <c r="G83" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="H83" s="12"/>
-    </row>
-    <row r="84" spans="1:8">
-      <c r="A84" s="60" t="s">
+      <c r="H83" s="11"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="70" t="s">
         <v>129</v>
       </c>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="27" t="s">
+      <c r="B84" s="7"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="9"/>
-    </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A85" s="61"/>
-      <c r="B85" s="11"/>
-      <c r="C85" s="11"/>
-      <c r="D85" s="28" t="s">
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="8"/>
+    </row>
+    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="71"/>
+      <c r="B85" s="10"/>
+      <c r="C85" s="10"/>
+      <c r="D85" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="E85" s="11"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="11"/>
-      <c r="H85" s="12"/>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="60" t="s">
+      <c r="E85" s="10"/>
+      <c r="F85" s="10"/>
+      <c r="G85" s="10"/>
+      <c r="H85" s="11"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="70" t="s">
         <v>131</v>
       </c>
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
-      <c r="G86" s="27" t="s">
+      <c r="B86" s="7"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="7"/>
+      <c r="G86" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="H86" s="9"/>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87" s="69"/>
+      <c r="H86" s="8"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="80"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="26" t="s">
+      <c r="G87" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="H87" s="13"/>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" s="69"/>
+      <c r="H87" s="12"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="80"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
-      <c r="G88" s="25" t="s">
+      <c r="G88" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="H88" s="13"/>
-    </row>
-    <row r="89" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A89" s="61"/>
-      <c r="B89" s="11"/>
-      <c r="C89" s="11"/>
-      <c r="D89" s="11"/>
-      <c r="E89" s="11"/>
-      <c r="F89" s="11"/>
-      <c r="G89" s="28" t="s">
+      <c r="H88" s="12"/>
+    </row>
+    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="71"/>
+      <c r="B89" s="10"/>
+      <c r="C89" s="10"/>
+      <c r="D89" s="10"/>
+      <c r="E89" s="10"/>
+      <c r="F89" s="10"/>
+      <c r="G89" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="H89" s="12"/>
-    </row>
-    <row r="90" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A90" s="14" t="s">
+      <c r="H89" s="11"/>
+    </row>
+    <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="B90" s="63"/>
-      <c r="C90" s="64"/>
-      <c r="D90" s="64"/>
-      <c r="E90" s="64"/>
-      <c r="F90" s="64"/>
-      <c r="G90" s="64"/>
-      <c r="H90" s="65"/>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" s="70" t="s">
+      <c r="B90" s="73"/>
+      <c r="C90" s="74"/>
+      <c r="D90" s="74"/>
+      <c r="E90" s="74"/>
+      <c r="F90" s="74"/>
+      <c r="G90" s="74"/>
+      <c r="H90" s="75"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="79" t="s">
         <v>133</v>
       </c>
       <c r="B91" s="1"/>
@@ -8490,60 +8522,60 @@
         <v>21</v>
       </c>
       <c r="G91" s="1"/>
-      <c r="H91" s="13" t="s">
+      <c r="H91" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A92" s="61"/>
-      <c r="B92" s="11"/>
-      <c r="C92" s="11"/>
-      <c r="D92" s="11" t="s">
+    <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="71"/>
+      <c r="B92" s="10"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E92" s="11"/>
-      <c r="F92" s="11" t="s">
+      <c r="E92" s="10"/>
+      <c r="F92" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="G92" s="11"/>
-      <c r="H92" s="12" t="s">
+      <c r="G92" s="10"/>
+      <c r="H92" s="11" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="60" t="s">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="70" t="s">
         <v>136</v>
       </c>
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="27" t="s">
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="9"/>
-    </row>
-    <row r="94" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A94" s="61"/>
-      <c r="B94" s="11"/>
-      <c r="C94" s="11"/>
-      <c r="D94" s="28" t="s">
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="8"/>
+    </row>
+    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="71"/>
+      <c r="B94" s="10"/>
+      <c r="C94" s="10"/>
+      <c r="D94" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="E94" s="11"/>
-      <c r="F94" s="11"/>
-      <c r="G94" s="11"/>
-      <c r="H94" s="12"/>
-    </row>
-    <row r="95" spans="1:8" ht="6.75" customHeight="1">
-      <c r="B95" s="62"/>
-      <c r="C95" s="62"/>
-      <c r="D95" s="62"/>
-      <c r="E95" s="62"/>
-      <c r="F95" s="62"/>
-      <c r="G95" s="62"/>
-      <c r="H95" s="62"/>
+      <c r="E94" s="10"/>
+      <c r="F94" s="10"/>
+      <c r="G94" s="10"/>
+      <c r="H94" s="11"/>
+    </row>
+    <row r="95" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="72"/>
+      <c r="C95" s="72"/>
+      <c r="D95" s="72"/>
+      <c r="E95" s="72"/>
+      <c r="F95" s="72"/>
+      <c r="G95" s="72"/>
+      <c r="H95" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -8579,7 +8611,7 @@
     <mergeCell ref="A50:A51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="34" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="33" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -8587,31 +8619,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="B4" s="75" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="B5" s="76" t="s">
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="93" t="s">
         <v>139</v>
       </c>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="17" t="s">
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -8627,493 +8659,493 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="24" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="56">
-        <v>0</v>
-      </c>
-      <c r="C7" s="56">
-        <v>0</v>
-      </c>
-      <c r="D7" s="56">
-        <v>0</v>
-      </c>
-      <c r="E7" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="24" t="s">
+      <c r="B7" s="53">
+        <v>0</v>
+      </c>
+      <c r="C7" s="53">
+        <v>0</v>
+      </c>
+      <c r="D7" s="53">
+        <v>0</v>
+      </c>
+      <c r="E7" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="56">
-        <v>0</v>
-      </c>
-      <c r="C8" s="56">
-        <v>0</v>
-      </c>
-      <c r="D8" s="56">
-        <v>0</v>
-      </c>
-      <c r="E8" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="24" t="s">
+      <c r="B8" s="53">
+        <v>0</v>
+      </c>
+      <c r="C8" s="53">
+        <v>0</v>
+      </c>
+      <c r="D8" s="53">
+        <v>0</v>
+      </c>
+      <c r="E8" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="56">
-        <v>0</v>
-      </c>
-      <c r="C9" s="56">
+      <c r="B9" s="53">
+        <v>0</v>
+      </c>
+      <c r="C9" s="53">
         <v>4.1667000000000003E-2</v>
       </c>
-      <c r="D9" s="56">
-        <v>0</v>
-      </c>
-      <c r="E9" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="24" t="s">
+      <c r="D9" s="53">
+        <v>0</v>
+      </c>
+      <c r="E9" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="56">
-        <v>0</v>
-      </c>
-      <c r="C10" s="56">
-        <v>0</v>
-      </c>
-      <c r="D10" s="56">
-        <v>0</v>
-      </c>
-      <c r="E10" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="24" t="s">
+      <c r="B10" s="53">
+        <v>0</v>
+      </c>
+      <c r="C10" s="53">
+        <v>0</v>
+      </c>
+      <c r="D10" s="53">
+        <v>0</v>
+      </c>
+      <c r="E10" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="56">
-        <v>0</v>
-      </c>
-      <c r="C11" s="56">
-        <v>0</v>
-      </c>
-      <c r="D11" s="56">
-        <v>0</v>
-      </c>
-      <c r="E11" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="24" t="s">
+      <c r="B11" s="53">
+        <v>0</v>
+      </c>
+      <c r="C11" s="53">
+        <v>0</v>
+      </c>
+      <c r="D11" s="53">
+        <v>0</v>
+      </c>
+      <c r="E11" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="56">
-        <v>0</v>
-      </c>
-      <c r="C12" s="56">
-        <v>0</v>
-      </c>
-      <c r="D12" s="56">
-        <v>0</v>
-      </c>
-      <c r="E12" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24" t="s">
+      <c r="B12" s="53">
+        <v>0</v>
+      </c>
+      <c r="C12" s="53">
+        <v>0</v>
+      </c>
+      <c r="D12" s="53">
+        <v>0</v>
+      </c>
+      <c r="E12" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="56">
-        <v>0</v>
-      </c>
-      <c r="C13" s="56">
-        <v>0</v>
-      </c>
-      <c r="D13" s="56">
+      <c r="B13" s="53">
+        <v>0</v>
+      </c>
+      <c r="C13" s="53">
+        <v>0</v>
+      </c>
+      <c r="D13" s="53">
         <v>0.24166699999999999</v>
       </c>
-      <c r="E13" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24" t="s">
+      <c r="E13" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="56">
-        <v>0</v>
-      </c>
-      <c r="C14" s="56">
-        <v>0</v>
-      </c>
-      <c r="D14" s="56">
-        <v>0</v>
-      </c>
-      <c r="E14" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24" t="s">
+      <c r="B14" s="53">
+        <v>0</v>
+      </c>
+      <c r="C14" s="53">
+        <v>0</v>
+      </c>
+      <c r="D14" s="53">
+        <v>0</v>
+      </c>
+      <c r="E14" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="56">
-        <v>0</v>
-      </c>
-      <c r="C15" s="56">
-        <v>0</v>
-      </c>
-      <c r="D15" s="56">
-        <v>0</v>
-      </c>
-      <c r="E15" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24" t="s">
+      <c r="B15" s="53">
+        <v>0</v>
+      </c>
+      <c r="C15" s="53">
+        <v>0</v>
+      </c>
+      <c r="D15" s="53">
+        <v>0</v>
+      </c>
+      <c r="E15" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="56">
+      <c r="B16" s="53">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="C16" s="56">
+      <c r="C16" s="53">
         <v>8.3334000000000005E-2</v>
       </c>
-      <c r="D16" s="56">
-        <v>0</v>
-      </c>
-      <c r="E16" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24" t="s">
+      <c r="D16" s="53">
+        <v>0</v>
+      </c>
+      <c r="E16" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="B17" s="56">
-        <v>0</v>
-      </c>
-      <c r="C17" s="56">
-        <v>0</v>
-      </c>
-      <c r="D17" s="56">
-        <v>0</v>
-      </c>
-      <c r="E17" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24" t="s">
+      <c r="B17" s="53">
+        <v>0</v>
+      </c>
+      <c r="C17" s="53">
+        <v>0</v>
+      </c>
+      <c r="D17" s="53">
+        <v>0</v>
+      </c>
+      <c r="E17" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="B18" s="56">
-        <v>0</v>
-      </c>
-      <c r="C18" s="56">
-        <v>0</v>
-      </c>
-      <c r="D18" s="56">
-        <v>0</v>
-      </c>
-      <c r="E18" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24" t="s">
+      <c r="B18" s="53">
+        <v>0</v>
+      </c>
+      <c r="C18" s="53">
+        <v>0</v>
+      </c>
+      <c r="D18" s="53">
+        <v>0</v>
+      </c>
+      <c r="E18" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="56">
-        <v>0</v>
-      </c>
-      <c r="C19" s="56">
-        <v>0</v>
-      </c>
-      <c r="D19" s="56">
-        <v>0</v>
-      </c>
-      <c r="E19" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24" t="s">
+      <c r="B19" s="53">
+        <v>0</v>
+      </c>
+      <c r="C19" s="53">
+        <v>0</v>
+      </c>
+      <c r="D19" s="53">
+        <v>0</v>
+      </c>
+      <c r="E19" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="B20" s="56">
-        <v>0</v>
-      </c>
-      <c r="C20" s="56">
-        <v>0</v>
-      </c>
-      <c r="D20" s="56">
-        <v>0</v>
-      </c>
-      <c r="E20" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24" t="s">
+      <c r="B20" s="53">
+        <v>0</v>
+      </c>
+      <c r="C20" s="53">
+        <v>0</v>
+      </c>
+      <c r="D20" s="53">
+        <v>0</v>
+      </c>
+      <c r="E20" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="56">
-        <v>0</v>
-      </c>
-      <c r="C21" s="56">
-        <v>0</v>
-      </c>
-      <c r="D21" s="56">
-        <v>0</v>
-      </c>
-      <c r="E21" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24" t="s">
+      <c r="B21" s="53">
+        <v>0</v>
+      </c>
+      <c r="C21" s="53">
+        <v>0</v>
+      </c>
+      <c r="D21" s="53">
+        <v>0</v>
+      </c>
+      <c r="E21" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="56">
-        <v>0</v>
-      </c>
-      <c r="C22" s="56">
-        <v>0</v>
-      </c>
-      <c r="D22" s="56">
-        <v>0</v>
-      </c>
-      <c r="E22" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24" t="s">
+      <c r="B22" s="53">
+        <v>0</v>
+      </c>
+      <c r="C22" s="53">
+        <v>0</v>
+      </c>
+      <c r="D22" s="53">
+        <v>0</v>
+      </c>
+      <c r="E22" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="B23" s="56">
-        <v>0</v>
-      </c>
-      <c r="C23" s="56">
-        <v>0</v>
-      </c>
-      <c r="D23" s="56">
-        <v>0</v>
-      </c>
-      <c r="E23" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24" t="s">
+      <c r="B23" s="53">
+        <v>0</v>
+      </c>
+      <c r="C23" s="53">
+        <v>0</v>
+      </c>
+      <c r="D23" s="53">
+        <v>0</v>
+      </c>
+      <c r="E23" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="56">
-        <v>0</v>
-      </c>
-      <c r="C24" s="56">
-        <v>0</v>
-      </c>
-      <c r="D24" s="56">
+      <c r="B24" s="53">
+        <v>0</v>
+      </c>
+      <c r="C24" s="53">
+        <v>0</v>
+      </c>
+      <c r="D24" s="53">
         <v>0.25</v>
       </c>
-      <c r="E24" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24" t="s">
+      <c r="E24" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="56">
-        <v>0</v>
-      </c>
-      <c r="C25" s="56">
+      <c r="B25" s="53">
+        <v>0</v>
+      </c>
+      <c r="C25" s="53">
         <v>0.45833400000000002</v>
       </c>
-      <c r="D25" s="56">
-        <v>0</v>
-      </c>
-      <c r="E25" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24" t="s">
+      <c r="D25" s="53">
+        <v>0</v>
+      </c>
+      <c r="E25" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="B26" s="56">
-        <v>0</v>
-      </c>
-      <c r="C26" s="56">
+      <c r="B26" s="53">
+        <v>0</v>
+      </c>
+      <c r="C26" s="53">
         <v>0.16666700000000001</v>
       </c>
-      <c r="D26" s="56">
+      <c r="D26" s="53">
         <v>8.3334000000000005E-2</v>
       </c>
-      <c r="E26" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24" t="s">
+      <c r="E26" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="56">
-        <v>0</v>
-      </c>
-      <c r="C27" s="56">
-        <v>0</v>
-      </c>
-      <c r="D27" s="56">
-        <v>0</v>
-      </c>
-      <c r="E27" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24" t="s">
+      <c r="B27" s="53">
+        <v>0</v>
+      </c>
+      <c r="C27" s="53">
+        <v>0</v>
+      </c>
+      <c r="D27" s="53">
+        <v>0</v>
+      </c>
+      <c r="E27" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="56">
-        <v>0</v>
-      </c>
-      <c r="C28" s="56">
-        <v>0</v>
-      </c>
-      <c r="D28" s="56">
-        <v>0</v>
-      </c>
-      <c r="E28" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24" t="s">
+      <c r="B28" s="53">
+        <v>0</v>
+      </c>
+      <c r="C28" s="53">
+        <v>0</v>
+      </c>
+      <c r="D28" s="53">
+        <v>0</v>
+      </c>
+      <c r="E28" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="B29" s="56">
-        <v>0</v>
-      </c>
-      <c r="C29" s="56">
+      <c r="B29" s="53">
+        <v>0</v>
+      </c>
+      <c r="C29" s="53">
         <v>0.125</v>
       </c>
-      <c r="D29" s="56">
+      <c r="D29" s="53">
         <v>0.159723</v>
       </c>
-      <c r="E29" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24" t="s">
+      <c r="E29" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="B30" s="56">
-        <v>0</v>
-      </c>
-      <c r="C30" s="56">
-        <v>0</v>
-      </c>
-      <c r="D30" s="56">
-        <v>0</v>
-      </c>
-      <c r="E30" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24" t="s">
+      <c r="B30" s="53">
+        <v>0</v>
+      </c>
+      <c r="C30" s="53">
+        <v>0</v>
+      </c>
+      <c r="D30" s="53">
+        <v>0</v>
+      </c>
+      <c r="E30" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="B31" s="56">
-        <v>0</v>
-      </c>
-      <c r="C31" s="56">
-        <v>0</v>
-      </c>
-      <c r="D31" s="56">
-        <v>0</v>
-      </c>
-      <c r="E31" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24" t="s">
+      <c r="B31" s="53">
+        <v>0</v>
+      </c>
+      <c r="C31" s="53">
+        <v>0</v>
+      </c>
+      <c r="D31" s="53">
+        <v>0</v>
+      </c>
+      <c r="E31" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="B32" s="56">
-        <v>0</v>
-      </c>
-      <c r="C32" s="56">
-        <v>0</v>
-      </c>
-      <c r="D32" s="56">
-        <v>0</v>
-      </c>
-      <c r="E32" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="24" t="s">
+      <c r="B32" s="53">
+        <v>0</v>
+      </c>
+      <c r="C32" s="53">
+        <v>0</v>
+      </c>
+      <c r="D32" s="53">
+        <v>0</v>
+      </c>
+      <c r="E32" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="56">
-        <v>0</v>
-      </c>
-      <c r="C33" s="56">
-        <v>0</v>
-      </c>
-      <c r="D33" s="56">
-        <v>0</v>
-      </c>
-      <c r="E33" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="24" t="s">
+      <c r="B33" s="53">
+        <v>0</v>
+      </c>
+      <c r="C33" s="53">
+        <v>0</v>
+      </c>
+      <c r="D33" s="53">
+        <v>0</v>
+      </c>
+      <c r="E33" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="B34" s="56">
-        <v>0</v>
-      </c>
-      <c r="C34" s="56">
-        <v>0</v>
-      </c>
-      <c r="D34" s="56">
-        <v>0</v>
-      </c>
-      <c r="E34" s="56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="B35" s="57">
+      <c r="B34" s="53">
+        <v>0</v>
+      </c>
+      <c r="C34" s="53">
+        <v>0</v>
+      </c>
+      <c r="D34" s="53">
+        <v>0</v>
+      </c>
+      <c r="E34" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B35" s="54">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="C35" s="57">
+      <c r="C35" s="54">
         <v>0.875</v>
       </c>
-      <c r="D35" s="57">
+      <c r="D35" s="54">
         <v>0.73472300000000001</v>
       </c>
-      <c r="E35" s="57">
+      <c r="E35" s="54">
         <v>0</v>
       </c>
     </row>
@@ -9129,48 +9161,48 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="58" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="56" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="58" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="55" t="s">
         <v>148</v>
       </c>
-      <c r="B5" s="59"/>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="58" t="s">
+      <c r="B5" s="56"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="56" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="58" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="56" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="58" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="56" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9346,13 +9378,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B3E9373-21F1-472D-A1B7-AB92AB4BB0C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B3E9373-21F1-472D-A1B7-AB92AB4BB0C0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55258B40-0392-499F-BBA5-A4C6FB1ACB8A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55258B40-0392-499F-BBA5-A4C6FB1ACB8A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
+    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE50E459-6C86-4FD6-AF9A-BF99153D4F10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE50E459-6C86-4FD6-AF9A-BF99153D4F10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Plannings 2026 S14.xlsx
+++ b/Plannings 2026 S14.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29799D5C-DD60-45E8-8D29-B1A26F276513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7EC2850-C9FC-4923-8844-D0B532F44049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,6 +55,9 @@
     <t>EDF // LEAGUES</t>
   </si>
   <si>
+    <t>INVETAIRE // EDF // LEAGUES</t>
+  </si>
+  <si>
     <t>C. PADEL // EVENT EQUANS // LEAGUES</t>
   </si>
   <si>
@@ -500,9 +503,6 @@
   </si>
   <si>
     <t>19/03/2026 12:22</t>
-  </si>
-  <si>
-    <t>INVETAIRE // EDF // LEAGUES</t>
   </si>
 </sst>
 </file>
@@ -512,7 +512,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1337,13 +1337,25 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1353,6 +1365,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1365,42 +1401,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7114,36 +7114,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H95"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="49.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="87" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87" t="s">
+    <row r="1" spans="1:8">
+      <c r="B1" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="87" t="s">
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="B2" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+    </row>
+    <row r="3" spans="1:8">
       <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
@@ -7151,50 +7151,50 @@
         <v>4</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>154</v>
+        <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" thickBot="1">
       <c r="A4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="70" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="71" t="s">
+        <v>18</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="7"/>
@@ -7202,239 +7202,239 @@
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="71"/>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A6" s="81"/>
       <c r="B6" s="9"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H6" s="11"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="70" t="s">
-        <v>20</v>
+    <row r="7" spans="1:8">
+      <c r="A7" s="71" t="s">
+        <v>21</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="71"/>
+    <row r="8" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A8" s="81"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="11"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="70" t="s">
-        <v>23</v>
+    <row r="9" spans="1:8">
+      <c r="A9" s="71" t="s">
+        <v>24</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="80"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="85"/>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10" s="42" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="80"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="85"/>
       <c r="B11" s="25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="12"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="80"/>
+    <row r="12" spans="1:8">
+      <c r="A12" s="85"/>
       <c r="B12" s="27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="12"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="80"/>
+    <row r="13" spans="1:8">
+      <c r="A13" s="85"/>
       <c r="B13" s="25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="12"/>
     </row>
-    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="71"/>
+    <row r="14" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A14" s="81"/>
       <c r="B14" s="26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
       <c r="H14" s="11"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="70" t="s">
-        <v>37</v>
+    <row r="15" spans="1:8">
+      <c r="A15" s="71" t="s">
+        <v>38</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="71"/>
+    <row r="16" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A16" s="81"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
       <c r="H16" s="11"/>
     </row>
-    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="15.75" thickBot="1">
       <c r="A17" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="73"/>
-      <c r="C17" s="74"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="75"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="70" t="s">
         <v>40</v>
       </c>
+      <c r="B17" s="77"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="79"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="71" t="s">
+        <v>41</v>
+      </c>
       <c r="B18" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="91"/>
+    <row r="19" spans="1:8">
+      <c r="A19" s="86"/>
       <c r="B19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="91"/>
+    <row r="20" spans="1:8">
+      <c r="A20" s="86"/>
       <c r="B20" s="1"/>
       <c r="C20" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -7442,11 +7442,11 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="71"/>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A21" s="81"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -7454,213 +7454,213 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="70" t="s">
-        <v>46</v>
+    <row r="22" spans="1:8">
+      <c r="A22" s="71" t="s">
+        <v>47</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H22" s="34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="80"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="85"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H23" s="33" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="80"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="85"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="71"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A25" s="81"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="85" t="s">
         <v>53</v>
       </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="70" t="s">
+        <v>54</v>
+      </c>
       <c r="B26" s="36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="36" t="s">
         <v>55</v>
-      </c>
-      <c r="E26" s="36" t="s">
-        <v>54</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="85"/>
+    <row r="27" spans="1:8">
+      <c r="A27" s="70"/>
       <c r="B27" s="35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" s="35" t="s">
         <v>58</v>
-      </c>
-      <c r="E27" s="35" t="s">
-        <v>57</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="85"/>
+    <row r="28" spans="1:8">
+      <c r="A28" s="70"/>
       <c r="B28" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="36" t="s">
-        <v>54</v>
-      </c>
       <c r="E28" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="19"/>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
+    <row r="29" spans="1:8">
+      <c r="A29" s="70"/>
       <c r="B29" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D29" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="19"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="85"/>
+    <row r="30" spans="1:8">
+      <c r="A30" s="70"/>
       <c r="B30" s="18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C30" s="36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="19"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="85"/>
+    <row r="31" spans="1:8">
+      <c r="A31" s="70"/>
       <c r="B31" s="19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E31" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="19"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
+    <row r="32" spans="1:8">
+      <c r="A32" s="70"/>
       <c r="B32" s="19"/>
       <c r="C32" s="35"/>
       <c r="D32" s="22"/>
       <c r="E32" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="19"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="85"/>
+    <row r="33" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A33" s="70"/>
       <c r="B33" s="19"/>
       <c r="C33" s="35"/>
       <c r="D33" s="22"/>
       <c r="E33" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="19"/>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="70" t="s">
-        <v>69</v>
+    <row r="34" spans="1:8">
+      <c r="A34" s="71" t="s">
+        <v>70</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -7668,245 +7668,245 @@
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="81"/>
+    <row r="35" spans="1:8">
+      <c r="A35" s="72"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H35" s="12"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="82" t="s">
-        <v>70</v>
+    <row r="36" spans="1:8">
+      <c r="A36" s="73" t="s">
+        <v>71</v>
       </c>
       <c r="B36" s="65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C36" s="57"/>
       <c r="D36" s="58" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E36" s="66" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F36" s="67" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G36" s="57"/>
       <c r="H36" s="59"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="83"/>
+    <row r="37" spans="1:8">
+      <c r="A37" s="74"/>
       <c r="B37" s="17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="69" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="60"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="83"/>
+    <row r="38" spans="1:8">
+      <c r="A38" s="74"/>
       <c r="B38" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E38" s="19"/>
       <c r="F38" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="60"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="83"/>
+    <row r="39" spans="1:8">
+      <c r="A39" s="74"/>
       <c r="B39" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E39" s="19"/>
       <c r="F39" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="60"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="83"/>
+    <row r="40" spans="1:8">
+      <c r="A40" s="74"/>
       <c r="B40" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E40" s="19"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="60"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="83"/>
+    <row r="41" spans="1:8">
+      <c r="A41" s="74"/>
       <c r="B41" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E41" s="19"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="60"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="83"/>
+    <row r="42" spans="1:8">
+      <c r="A42" s="74"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E42" s="19"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="60"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="86"/>
+    <row r="43" spans="1:8">
+      <c r="A43" s="75"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E43" s="19"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="60"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="86"/>
+    <row r="44" spans="1:8">
+      <c r="A44" s="75"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E44" s="19"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="60"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="84"/>
+    <row r="45" spans="1:8">
+      <c r="A45" s="76"/>
       <c r="B45" s="61"/>
       <c r="C45" s="61"/>
       <c r="D45" s="68" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E45" s="63"/>
       <c r="F45" s="61"/>
       <c r="G45" s="61"/>
       <c r="H45" s="64"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="B46" s="88"/>
-      <c r="C46" s="89"/>
-      <c r="D46" s="89"/>
-      <c r="E46" s="89"/>
-      <c r="F46" s="89"/>
-      <c r="G46" s="89"/>
-      <c r="H46" s="90"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="B46" s="82"/>
+      <c r="C46" s="83"/>
+      <c r="D46" s="83"/>
+      <c r="E46" s="83"/>
+      <c r="F46" s="83"/>
+      <c r="G46" s="83"/>
+      <c r="H46" s="84"/>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B47" s="73"/>
-      <c r="C47" s="74"/>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="74"/>
-      <c r="H47" s="75"/>
-    </row>
-    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="B47" s="77"/>
+      <c r="C47" s="78"/>
+      <c r="D47" s="78"/>
+      <c r="E47" s="78"/>
+      <c r="F47" s="78"/>
+      <c r="G47" s="78"/>
+      <c r="H47" s="79"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" thickBot="1">
       <c r="A48" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="B48" s="73"/>
-      <c r="C48" s="74"/>
-      <c r="D48" s="74"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="74"/>
-      <c r="H48" s="75"/>
-    </row>
-    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+      <c r="B48" s="77"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="78"/>
+      <c r="G48" s="78"/>
+      <c r="H48" s="79"/>
+    </row>
+    <row r="49" spans="1:8" ht="15.75" thickBot="1">
       <c r="A49" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B49" s="76"/>
-      <c r="C49" s="77"/>
-      <c r="D49" s="77"/>
-      <c r="E49" s="77"/>
-      <c r="F49" s="77"/>
-      <c r="G49" s="77"/>
-      <c r="H49" s="78"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="70" t="s">
         <v>89</v>
+      </c>
+      <c r="B49" s="88"/>
+      <c r="C49" s="89"/>
+      <c r="D49" s="89"/>
+      <c r="E49" s="89"/>
+      <c r="F49" s="89"/>
+      <c r="G49" s="89"/>
+      <c r="H49" s="90"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="71" t="s">
+        <v>90</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
       <c r="F50" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="8"/>
     </row>
-    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="71"/>
+    <row r="51" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A51" s="81"/>
       <c r="B51" s="10"/>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
       <c r="E51" s="10"/>
       <c r="F51" s="24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G51" s="10"/>
       <c r="H51" s="11"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="70" t="s">
-        <v>90</v>
+    <row r="52" spans="1:8">
+      <c r="A52" s="71" t="s">
+        <v>91</v>
       </c>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -7915,11 +7915,11 @@
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
       <c r="H52" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="80"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="85"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -7927,11 +7927,11 @@
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="80"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="85"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -7939,11 +7939,11 @@
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="80"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="85"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -7951,11 +7951,11 @@
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="33" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="80"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="85"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -7963,11 +7963,11 @@
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="80"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="85"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -7975,11 +7975,11 @@
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="80"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="85"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -7987,11 +7987,11 @@
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="71"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A59" s="81"/>
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
@@ -7999,456 +7999,456 @@
       <c r="F59" s="10"/>
       <c r="G59" s="10"/>
       <c r="H59" s="32" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="70" t="s">
-        <v>94</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="71" t="s">
+        <v>95</v>
       </c>
       <c r="B60" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C60" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
       <c r="H60" s="8"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="71"/>
+    <row r="61" spans="1:8">
+      <c r="A61" s="81"/>
       <c r="B61" s="26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D61" s="26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F61" s="10"/>
       <c r="G61" s="10"/>
       <c r="H61" s="11"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="70" t="s">
-        <v>97</v>
+    <row r="62" spans="1:8">
+      <c r="A62" s="71" t="s">
+        <v>98</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C62" s="39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E62" s="46" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F62" s="51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G62" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H62" s="8"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="80"/>
+    <row r="63" spans="1:8">
+      <c r="A63" s="85"/>
       <c r="B63" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C63" s="40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D63" s="22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E63" s="47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F63" s="52" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G63" s="22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H63" s="12"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="80"/>
+    <row r="64" spans="1:8">
+      <c r="A64" s="85"/>
       <c r="B64" s="1"/>
       <c r="C64" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E64" s="44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F64" s="52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G64" s="21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H64" s="12"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="80"/>
+    <row r="65" spans="1:8">
+      <c r="A65" s="85"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E65" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="F65" s="52" t="s">
         <v>105</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E65" s="50" t="s">
-        <v>107</v>
-      </c>
-      <c r="F65" s="52" t="s">
-        <v>104</v>
-      </c>
       <c r="G65" s="22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H65" s="12"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="80"/>
+    <row r="66" spans="1:8">
+      <c r="A66" s="85"/>
       <c r="B66" s="1"/>
       <c r="C66" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D66" s="25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E66" s="48" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F66" s="52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G66" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H66" s="12"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="80"/>
+    <row r="67" spans="1:8">
+      <c r="A67" s="85"/>
       <c r="B67" s="1"/>
       <c r="C67" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E67" s="49" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F67" s="52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G67" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H67" s="12"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="80"/>
+    <row r="68" spans="1:8">
+      <c r="A68" s="85"/>
       <c r="B68" s="1"/>
       <c r="C68" s="25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D68" s="27"/>
       <c r="E68" s="44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F68" s="52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G68" s="38" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H68" s="12"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="80"/>
+    <row r="69" spans="1:8">
+      <c r="A69" s="85"/>
       <c r="B69" s="1"/>
       <c r="C69" s="27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D69" s="27"/>
       <c r="E69" s="45" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F69" s="52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G69" s="30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H69" s="12"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="80"/>
+    <row r="70" spans="1:8">
+      <c r="A70" s="85"/>
       <c r="B70" s="1"/>
       <c r="C70" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D70" s="27"/>
       <c r="E70" s="45" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F70" s="52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G70" s="30"/>
       <c r="H70" s="12"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="71"/>
+    <row r="71" spans="1:8">
+      <c r="A71" s="81"/>
       <c r="B71" s="10"/>
       <c r="C71" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D71" s="26"/>
       <c r="E71" s="45" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F71" s="52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G71" s="37"/>
       <c r="H71" s="11"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="70" t="s">
-        <v>115</v>
+    <row r="72" spans="1:8">
+      <c r="A72" s="71" t="s">
+        <v>116</v>
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D72" s="7"/>
       <c r="E72" s="7"/>
       <c r="F72" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="8"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="81"/>
+    <row r="73" spans="1:8">
+      <c r="A73" s="72"/>
       <c r="B73" s="1"/>
       <c r="C73" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="12"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="82" t="s">
-        <v>116</v>
+    <row r="74" spans="1:8">
+      <c r="A74" s="73" t="s">
+        <v>117</v>
       </c>
       <c r="B74" s="57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C74" s="57"/>
       <c r="D74" s="58" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E74" s="57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F74" s="57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G74" s="57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H74" s="59"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="83"/>
+    <row r="75" spans="1:8">
+      <c r="A75" s="74"/>
       <c r="B75" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H75" s="60"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="83"/>
+    <row r="76" spans="1:8">
+      <c r="A76" s="74"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H76" s="60"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="83"/>
+    <row r="77" spans="1:8">
+      <c r="A77" s="74"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="45" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H77" s="60"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="83"/>
+    <row r="78" spans="1:8">
+      <c r="A78" s="74"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="45" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E78" s="19"/>
       <c r="F78" s="1"/>
       <c r="G78" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H78" s="60"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="84"/>
+    <row r="79" spans="1:8">
+      <c r="A79" s="76"/>
       <c r="B79" s="61"/>
       <c r="C79" s="61"/>
       <c r="D79" s="62" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E79" s="63"/>
       <c r="F79" s="61"/>
       <c r="G79" s="61" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H79" s="64"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="79" t="s">
-        <v>127</v>
+    <row r="80" spans="1:8">
+      <c r="A80" s="91" t="s">
+        <v>128</v>
       </c>
       <c r="B80" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H80" s="12"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="80"/>
+    <row r="81" spans="1:8">
+      <c r="A81" s="85"/>
       <c r="B81" s="27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H81" s="12"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="80"/>
+    <row r="82" spans="1:8">
+      <c r="A82" s="85"/>
       <c r="B82" s="27"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H82" s="12"/>
     </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="71"/>
+    <row r="83" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A83" s="81"/>
       <c r="B83" s="26"/>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
       <c r="E83" s="10"/>
       <c r="F83" s="10"/>
       <c r="G83" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H83" s="11"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="70" t="s">
-        <v>129</v>
+    <row r="84" spans="1:8">
+      <c r="A84" s="71" t="s">
+        <v>130</v>
       </c>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
       <c r="D84" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E84" s="7"/>
       <c r="F84" s="7"/>
       <c r="G84" s="7"/>
       <c r="H84" s="8"/>
     </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="71"/>
+    <row r="85" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A85" s="81"/>
       <c r="B85" s="10"/>
       <c r="C85" s="10"/>
       <c r="D85" s="24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E85" s="10"/>
       <c r="F85" s="10"/>
       <c r="G85" s="10"/>
       <c r="H85" s="11"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="70" t="s">
-        <v>131</v>
+    <row r="86" spans="1:8">
+      <c r="A86" s="71" t="s">
+        <v>132</v>
       </c>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -8456,129 +8456,144 @@
       <c r="E86" s="7"/>
       <c r="F86" s="7"/>
       <c r="G86" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H86" s="8"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="80"/>
+    <row r="87" spans="1:8">
+      <c r="A87" s="85"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H87" s="12"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="80"/>
+    <row r="88" spans="1:8">
+      <c r="A88" s="85"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H88" s="12"/>
     </row>
-    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="71"/>
+    <row r="89" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A89" s="81"/>
       <c r="B89" s="10"/>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
       <c r="E89" s="10"/>
       <c r="F89" s="10"/>
       <c r="G89" s="24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H89" s="11"/>
     </row>
-    <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" ht="15.75" thickBot="1">
       <c r="A90" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B90" s="73"/>
-      <c r="C90" s="74"/>
-      <c r="D90" s="74"/>
-      <c r="E90" s="74"/>
-      <c r="F90" s="74"/>
-      <c r="G90" s="74"/>
-      <c r="H90" s="75"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="79" t="s">
         <v>133</v>
+      </c>
+      <c r="B90" s="77"/>
+      <c r="C90" s="78"/>
+      <c r="D90" s="78"/>
+      <c r="E90" s="78"/>
+      <c r="F90" s="78"/>
+      <c r="G90" s="78"/>
+      <c r="H90" s="79"/>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="91" t="s">
+        <v>134</v>
       </c>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G91" s="1"/>
       <c r="H91" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="71"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A92" s="81"/>
       <c r="B92" s="10"/>
       <c r="C92" s="10"/>
       <c r="D92" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E92" s="10"/>
       <c r="F92" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G92" s="10"/>
       <c r="H92" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="70" t="s">
         <v>136</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="71" t="s">
+        <v>137</v>
       </c>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
       <c r="D93" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="7"/>
       <c r="G93" s="7"/>
       <c r="H93" s="8"/>
     </row>
-    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="71"/>
+    <row r="94" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A94" s="81"/>
       <c r="B94" s="10"/>
       <c r="C94" s="10"/>
       <c r="D94" s="24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E94" s="10"/>
       <c r="F94" s="10"/>
       <c r="G94" s="10"/>
       <c r="H94" s="11"/>
     </row>
-    <row r="95" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="72"/>
-      <c r="C95" s="72"/>
-      <c r="D95" s="72"/>
-      <c r="E95" s="72"/>
-      <c r="F95" s="72"/>
-      <c r="G95" s="72"/>
-      <c r="H95" s="72"/>
+    <row r="95" spans="1:8" ht="6.75" customHeight="1">
+      <c r="B95" s="87"/>
+      <c r="C95" s="87"/>
+      <c r="D95" s="87"/>
+      <c r="E95" s="87"/>
+      <c r="F95" s="87"/>
+      <c r="G95" s="87"/>
+      <c r="H95" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="B95:H95"/>
+    <mergeCell ref="B90:H90"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A52:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A79"/>
+    <mergeCell ref="A50:A51"/>
     <mergeCell ref="A26:A33"/>
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="A36:A45"/>
@@ -8594,21 +8609,6 @@
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B17:H17"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="B95:H95"/>
-    <mergeCell ref="B90:H90"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B48:H48"/>
-    <mergeCell ref="A80:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A52:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A79"/>
-    <mergeCell ref="A50:A51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="33" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -8619,49 +8619,49 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="B4" s="92" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C4" s="92"/>
       <c r="D4" s="92"/>
       <c r="E4" s="92"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="B5" s="93" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C5" s="93"/>
       <c r="D5" s="93"/>
       <c r="E5" s="93"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="53">
         <v>0</v>
@@ -8676,9 +8676,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="53">
         <v>0</v>
@@ -8693,9 +8693,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="53">
         <v>0</v>
@@ -8710,9 +8710,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="53">
         <v>0</v>
@@ -8727,9 +8727,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" s="20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="53">
         <v>0</v>
@@ -8744,9 +8744,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="53">
         <v>0</v>
@@ -8761,9 +8761,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" s="20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="53">
         <v>0</v>
@@ -8778,9 +8778,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" s="20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" s="53">
         <v>0</v>
@@ -8795,9 +8795,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B15" s="53">
         <v>0</v>
@@ -8812,9 +8812,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" s="20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" s="53">
         <v>3.9584000000000001E-2</v>
@@ -8829,9 +8829,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B17" s="53">
         <v>0</v>
@@ -8846,9 +8846,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" s="20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B18" s="53">
         <v>0</v>
@@ -8863,9 +8863,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" s="20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B19" s="53">
         <v>0</v>
@@ -8880,9 +8880,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" s="20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B20" s="53">
         <v>0</v>
@@ -8897,9 +8897,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" s="20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B21" s="53">
         <v>0</v>
@@ -8914,9 +8914,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B22" s="53">
         <v>0</v>
@@ -8931,9 +8931,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" s="20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B23" s="53">
         <v>0</v>
@@ -8948,9 +8948,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" s="20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" s="53">
         <v>0</v>
@@ -8965,9 +8965,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" s="20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" s="53">
         <v>0</v>
@@ -8982,9 +8982,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" s="20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B26" s="53">
         <v>0</v>
@@ -8999,9 +8999,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" s="20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B27" s="53">
         <v>0</v>
@@ -9016,9 +9016,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" s="20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B28" s="53">
         <v>0</v>
@@ -9033,9 +9033,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" s="20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B29" s="53">
         <v>0</v>
@@ -9050,9 +9050,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" s="20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B30" s="53">
         <v>0</v>
@@ -9067,9 +9067,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" s="20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B31" s="53">
         <v>0</v>
@@ -9084,9 +9084,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B32" s="53">
         <v>0</v>
@@ -9101,9 +9101,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" s="20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B33" s="53">
         <v>0</v>
@@ -9118,9 +9118,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B34" s="53">
         <v>0</v>
@@ -9135,7 +9135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="B35" s="54">
         <v>3.9584000000000001E-2</v>
       </c>
@@ -9161,49 +9161,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="55" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B5" s="56"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" s="55" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="55" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="55" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -9213,14 +9213,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3c298670-db79-47a5-968d-a4570c34317f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="17e8e7ea-beb0-4155-adc4-5bfa61f32508" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9369,54 +9367,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3c298670-db79-47a5-968d-a4570c34317f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="17e8e7ea-beb0-4155-adc4-5bfa61f32508" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B3E9373-21F1-472D-A1B7-AB92AB4BB0C0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE50E459-6C86-4FD6-AF9A-BF99153D4F10}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55258B40-0392-499F-BBA5-A4C6FB1ACB8A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
-    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55258B40-0392-499F-BBA5-A4C6FB1ACB8A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE50E459-6C86-4FD6-AF9A-BF99153D4F10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B3E9373-21F1-472D-A1B7-AB92AB4BB0C0}"/>
 </file>